--- a/creatable-services.xlsx
+++ b/creatable-services.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATP - Availability" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Basis - Fiori - Technical" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CO - Controlling" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defense (DFS)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EHS - Health &amp; Safety" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EWM - Warehouse" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FI - Finance" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HR - Payroll - Travel" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LE - Shipping" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legal - Trade - Compliance" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MM - Inventory" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MM - Purchasing" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master data - MDG" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PM - Maintenance" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PP - Production" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PS - Projects" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QM - Quality" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retail (RFM)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD - Sales" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATP - Availability" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Basis - Fiori - Technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CO - Controlling" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Defense (DFS)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EHS - Health &amp; Safety" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="EWM - Warehouse" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FI - Finance" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="HR - Payroll - Travel" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="LE - Shipping" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Legal - Trade - Compliance" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="MM - Inventory" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="MM - Purchasing" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Master data - MDG" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="PM - Maintenance" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="PP - Production" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="PS - Projects" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="QM - Quality" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Retail (RFM)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SD - Sales" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$J$496</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$J$497</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ATP - Availability'!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Basis - Fiori - Technical'!$A$1:$J$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CO - Controlling'!$A$1:$J$31</definedName>
@@ -43,7 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Legal - Trade - Compliance'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'MM - Inventory'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'MM - Purchasing'!$A$1:$J$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Master data - MDG'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Master data - MDG'!$A$1:$J$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'PM - Maintenance'!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'PP - Production'!$A$1:$J$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'PS - Projects'!$A$1:$J$4</definedName>
@@ -702,36 +702,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EWM - Warehouse</t>
+          <t>Master data - MDG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EWM - Warehouse</t>
+          <t>Master data - MDG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Master data - MDG</t>
+          <t>EWM - Warehouse</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Master data - MDG</t>
+          <t>EWM - Warehouse</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>catalog-creatable.csv (live $metadata scan, DS4 client 220), file date 2026-09-19</t>
+          <t>catalog-creatable.csv (live $metadata scan, DS4 client 220), file date 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-19 by tools/build-creatable-xlsx.py</t>
+          <t>2026-09-23 by tools/build-creatable-xlsx.py</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4965,17 +4965,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MD_QC_PRODUCT_SRV</t>
+          <t>MD_CUSTOMER_MASTER_SRV_01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZMD_QC_PRODUCT_SRV</t>
+          <t>MD_CUSTOMER_MASTER_SRV_01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Product Master - Odata for Quick Create</t>
+          <t>Customer Master Data Maintain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C_QuickCreateProduct, C_QuickCreateProductUoM</t>
+          <t>C_BPAdditionalCustomer, C_BPAddlCustCompanyCode, C_BPAddlCustDunning, C_BPAddlCustPartFunc, C_BPAddlCustSalesArea, C_BPAddlCustWhldgTax, C_BPAddrDepdntIntlLocNumber, C_BPContactAddress, C_BPContactEmlAddr, C_BPContactFaxNmbr, C_BPContactMblNmbr, C_BPContactTelNmbr, C_BPContactWbsteURL, C_BPCustAddrDepdntInformation, C_BPCustDepartmentAddrDepdnt, C_BPCustomerDunning, C_BPCustomerTaxGrouping, C_BPCustRcvgPtAddrDepdntInfo, C_BPCustSlsAddrDepdntTaxInfo, C_BPCustSlsAreaAddrDepdntInfo, C_BPCustUnldgPtAddrDepdntInfo, C_BPDataController, C_BPEmailAddress, C_BPFaxNumber, C_BPMobilePhoneNumber, C_BPSalesAreaText, C_BPSiteReceivingPoint, C_BPTelephoneNumber, C_BPUnloadingPoint, C_BPWebsiteURL, C_BuPaIdentification, C_BuPaIndustry, C_BusinessPartner, C_BusinessPartnerAddress, C_Businesspartneraddrusage, C_BusinessPartnerBank, C_BusinessPartnerContact, C_BusinessPartnerCust, C_BusinessPartnerCustCo, C_BusinessPartnerCustCoText, C_BusinessPartnerCustomer, C_BusinessPartnerCustomerRole, C_BusinessPartnerCustomerTxt, C_BusinessPartnerCustWhdgTax, C_BusinessPartnerPartFunc, C_BusinessPartnerSalesArea, C_BusinessPartnerSupplier, C_Businesspartnertaxnumber, C_BusPartAddrDepdntTaxNmbr, C_CustAddrDepdntExtIdentifier, C_CustomerDepartment, C_PaymentCard, C_PaymentCardMaster, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MD_QC_PRODUCT_SRV</t>
+          <t>/sap/opu/odata/sap/MD_CUSTOMER_MASTER_SRV_01</t>
         </is>
       </c>
     </row>
@@ -5011,43 +5011,89 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>MD_QC_PRODUCT_SRV</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ZMD_QC_PRODUCT_SRV</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Product Master - Odata for Quick Create</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C_QuickCreateProduct, C_QuickCreateProductUoM</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>/sap/opu/odata/sap/MD_QC_PRODUCT_SRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Master data - MDG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>UI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ZUI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Model Product Specification - UI Service Binding</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Fiori app service</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
         <v>18</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>C_ModelProductSpecificationTP</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>/sap/opu/odata/sap/UI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9514,7 +9560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J496"/>
+  <dimension ref="A1:J497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26106,17 +26152,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>MD_QC_PRODUCT_SRV</t>
+          <t>MD_CUSTOMER_MASTER_SRV_01</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>ZMD_QC_PRODUCT_SRV</t>
+          <t>MD_CUSTOMER_MASTER_SRV_01</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Product Master - Odata for Quick Create</t>
+          <t>Customer Master Data Maintain</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -26125,19 +26171,19 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="H361" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>C_QuickCreateProduct, C_QuickCreateProductUoM</t>
+          <t>C_BPAdditionalCustomer, C_BPAddlCustCompanyCode, C_BPAddlCustDunning, C_BPAddlCustPartFunc, C_BPAddlCustSalesArea, C_BPAddlCustWhldgTax, C_BPAddrDepdntIntlLocNumber, C_BPContactAddress, C_BPContactEmlAddr, C_BPContactFaxNmbr, C_BPContactMblNmbr, C_BPContactTelNmbr, C_BPContactWbsteURL, C_BPCustAddrDepdntInformation, C_BPCustDepartmentAddrDepdnt, C_BPCustomerDunning, C_BPCustomerTaxGrouping, C_BPCustRcvgPtAddrDepdntInfo, C_BPCustSlsAddrDepdntTaxInfo, C_BPCustSlsAreaAddrDepdntInfo, C_BPCustUnldgPtAddrDepdntInfo, C_BPDataController, C_BPEmailAddress, C_BPFaxNumber, C_BPMobilePhoneNumber, C_BPSalesAreaText, C_BPSiteReceivingPoint, C_BPTelephoneNumber, C_BPUnloadingPoint, C_BPWebsiteURL, C_BuPaIdentification, C_BuPaIndustry, C_BusinessPartner, C_BusinessPartnerAddress, C_Businesspartneraddrusage, C_BusinessPartnerBank, C_BusinessPartnerContact, C_BusinessPartnerCust, C_BusinessPartnerCustCo, C_BusinessPartnerCustCoText, C_BusinessPartnerCustomer, C_BusinessPartnerCustomerRole, C_BusinessPartnerCustomerTxt, C_BusinessPartnerCustWhdgTax, C_BusinessPartnerPartFunc, C_BusinessPartnerSalesArea, C_BusinessPartnerSupplier, C_Businesspartnertaxnumber, C_BusPartAddrDepdntTaxNmbr, C_CustAddrDepdntExtIdentifier, C_CustomerDepartment, C_PaymentCard, C_PaymentCardMaster, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MD_QC_PRODUCT_SRV</t>
+          <t>/sap/opu/odata/sap/MD_CUSTOMER_MASTER_SRV_01</t>
         </is>
       </c>
     </row>
@@ -26152,17 +26198,17 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>UI_MODPRODSPEC_MANAGE</t>
+          <t>MD_QC_PRODUCT_SRV</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>ZUI_MODPRODSPEC_MANAGE</t>
+          <t>ZMD_QC_PRODUCT_SRV</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Model Product Specification - UI Service Binding</t>
+          <t>Product Master - Odata for Quick Create</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -26171,19 +26217,19 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H362" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>C_ModelProductSpecificationTP</t>
+          <t>C_QuickCreateProduct, C_QuickCreateProductUoM</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_MODPRODSPEC_MANAGE</t>
+          <t>/sap/opu/odata/sap/MD_QC_PRODUCT_SRV</t>
         </is>
       </c>
     </row>
@@ -26193,43 +26239,43 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PM - Maintenance</t>
+          <t>Master data - MDG</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>API_MAINTNOTIFICATION</t>
+          <t>UI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>API_MAINTNOTIFICATION</t>
+          <t>ZUI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Maintenance Notification</t>
+          <t>Model Product Specification - UI Service Binding</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Released API</t>
+          <t>Fiori app service</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H363" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>MaintenanceNotification, MaintNotificationEffectCode, MaintenanceNotificationItem, MaintenanceNotificationPartner, MaintNotificationItemActivity, MaintNotificationItemCause</t>
+          <t>C_ModelProductSpecificationTP</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/API_MAINTNOTIFICATION</t>
+          <t>/sap/opu/odata/sap/UI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
     </row>
@@ -26244,17 +26290,17 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>API_MAINTORDERCONFIRMATION</t>
+          <t>API_MAINTNOTIFICATION</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>API_MAINTORDERCONFIRMATION</t>
+          <t>API_MAINTNOTIFICATION</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Service Binding for Maint. Order Confirmation</t>
+          <t>Maintenance Notification</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -26263,19 +26309,19 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>MaintOrderConfirmation</t>
+          <t>MaintenanceNotification, MaintNotificationEffectCode, MaintenanceNotificationItem, MaintenanceNotificationPartner, MaintNotificationItemActivity, MaintNotificationItemCause</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/API_MAINTORDERCONFIRMATION</t>
+          <t>/sap/opu/odata/sap/API_MAINTNOTIFICATION</t>
         </is>
       </c>
     </row>
@@ -26290,38 +26336,38 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>DFS_MAINT_NOTIFICATION_SRV</t>
+          <t>API_MAINTORDERCONFIRMATION</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>DFS_MAINT_NOTIFICATION_SRV</t>
+          <t>API_MAINTORDERCONFIRMATION</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Extension for EAM_OBJPG_MAINTNOTIFICATION</t>
+          <t>Service Binding for Maint. Order Confirmation</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Fiori app service</t>
+          <t>Released API</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H365" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
+          <t>MaintOrderConfirmation</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_NOTIFICATION_SRV</t>
+          <t>/sap/opu/odata/sap/API_MAINTORDERCONFIRMATION</t>
         </is>
       </c>
     </row>
@@ -26336,17 +26382,17 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
+          <t>DFS_MAINT_NOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
+          <t>DFS_MAINT_NOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Extention of EAM_OBJPG_MAINTORDANDOPERATION</t>
+          <t>Extension for EAM_OBJPG_MAINTNOTIFICATION</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -26355,19 +26401,19 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H366" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
+          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_ORDANDOPERATION_SRV</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_NOTIFICATION_SRV</t>
         </is>
       </c>
     </row>
@@ -26382,17 +26428,17 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDER_SRV</t>
+          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDER_SRV</t>
+          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Extension for EAM_OBJPG_MAINTENANCEORDER</t>
+          <t>Extention of EAM_OBJPG_MAINTORDANDOPERATION</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -26401,19 +26447,19 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H367" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintOrder</t>
+          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_ORDER_SRV</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_ORDANDOPERATION_SRV</t>
         </is>
       </c>
     </row>
@@ -26428,17 +26474,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
+          <t>DFS_MAINT_ORDER_SRV</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
+          <t>DFS_MAINT_ORDER_SRV</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Extension project for EAM_OBJPG_TECHNICALOBJECT</t>
+          <t>Extension for EAM_OBJPG_MAINTENANCEORDER</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -26447,19 +26493,19 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H368" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ObjPgMaintOrder</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_TECHNICALOBJECT_SRV</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_ORDER_SRV</t>
         </is>
       </c>
     </row>
@@ -26474,17 +26520,17 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>EAM_MALFUNCTION_MANAGE</t>
+          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>EAM_MALFUNCTION_MANAGE</t>
+          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>F2023 "Respond to Breakdown" FIORI app</t>
+          <t>Extension project for EAM_OBJPG_TECHNICALOBJECT</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -26493,19 +26539,19 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H369" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>EmptyNotification, C_MaintNotifActivityTP, C_MaintNotificationCauseTP, C_MaintNotificationItemTP, C_MaintNotificationTP, C_MaintNotifLongTextTP, C_MaintOrderComponentTP, C_MaintOrderConfirmationTP, C_MaintOrderOperationTP, C_MaintOrderSubOperationTP, C_MaintOrderTP</t>
+          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_MALFUNCTION_MANAGE</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
     </row>
@@ -26520,17 +26566,17 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>EAM_NTF_CREATE</t>
+          <t>EAM_MALFUNCTION_MANAGE</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>EAM_NTF_CREATE</t>
+          <t>EAM_MALFUNCTION_MANAGE</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>EAM Notification Creation</t>
+          <t>F2023 "Respond to Breakdown" FIORI app</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -26539,19 +26585,19 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H370" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>NotificationHeaderSet, NotificationImageTypeCollection, LongTextSet</t>
+          <t>EmptyNotification, C_MaintNotifActivityTP, C_MaintNotificationCauseTP, C_MaintNotificationItemTP, C_MaintNotificationTP, C_MaintNotifLongTextTP, C_MaintOrderComponentTP, C_MaintOrderConfirmationTP, C_MaintOrderOperationTP, C_MaintOrderSubOperationTP, C_MaintOrderTP</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_NTF_CREATE</t>
+          <t>/sap/opu/odata/sap/EAM_MALFUNCTION_MANAGE</t>
         </is>
       </c>
     </row>
@@ -26566,17 +26612,17 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
+          <t>EAM_NTF_CREATE</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
+          <t>EAM_NTF_CREATE</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>F2175: Find Maintenance Order</t>
+          <t>EAM Notification Creation</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -26585,19 +26631,19 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H371" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>CreateWorkPackInput, C_ObjPgMaintOrder</t>
+          <t>NotificationHeaderSet, NotificationImageTypeCollection, LongTextSet</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTENANCEORDER_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_NTF_CREATE</t>
         </is>
       </c>
     </row>
@@ -26612,17 +26658,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTITEM_SRV</t>
+          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTITEM_SRV</t>
+          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Maintenance Item for Object Page</t>
+          <t>F2175: Find Maintenance Order</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -26631,19 +26677,19 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H372" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>C_MaintenanceItemObjPg</t>
+          <t>CreateWorkPackInput, C_ObjPgMaintOrder</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTITEM_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTENANCEORDER_SRV</t>
         </is>
       </c>
     </row>
@@ -26658,17 +26704,17 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
+          <t>EAM_OBJPG_MAINTITEM_SRV</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
+          <t>EAM_OBJPG_MAINTITEM_SRV</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Maintenance Notification for Object Page</t>
+          <t>Maintenance Item for Object Page</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -26677,19 +26723,19 @@
         </is>
       </c>
       <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="n">
         <v>2</v>
       </c>
-      <c r="H373" t="n">
-        <v>16</v>
-      </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
+          <t>C_MaintenanceItemObjPg</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTITEM_SRV</t>
         </is>
       </c>
     </row>
@@ -26704,17 +26750,17 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
+          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
+          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>F2173: Find Maintenance Orders and Operations</t>
+          <t>Maintenance Notification for Object Page</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -26723,19 +26769,19 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H374" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
+          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTORDANDOPER_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
         </is>
       </c>
     </row>
@@ -26750,17 +26796,17 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
+          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
+          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>OData service for EAM Technical Object Object Page</t>
+          <t>F2173: Find Maintenance Orders and Operations</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -26772,16 +26818,16 @@
         <v>4</v>
       </c>
       <c r="H375" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_TECHNICALOBJECT_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTORDANDOPER_SRV</t>
         </is>
       </c>
     </row>
@@ -26796,17 +26842,17 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
+          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>ZFAC_GL_MAINT_POSTING_PERIOD_SRV</t>
+          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Maintain Posting Period</t>
+          <t>OData service for EAM Technical Object Object Page</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -26815,19 +26861,19 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H376" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>PostingPeriodScheduledJobsSet, PostingPeriodSet, PostingPeriodInCoCdSet</t>
+          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
     </row>
@@ -26842,17 +26888,17 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
+          <t>FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
+          <t>ZFAC_GL_MAINT_POSTING_PERIOD_SRV</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>chart of account smaintainance</t>
+          <t>Maintain Posting Period</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -26868,12 +26914,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>ProposedFSVParamSet, CopyGLAccountInCOAParamSet, CopyGLAccountInCOCDParamSet</t>
+          <t>PostingPeriodScheduledJobsSet, PostingPeriodSet, PostingPeriodInCoCdSet</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
+          <t>/sap/opu/odata/sap/FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
         </is>
       </c>
     </row>
@@ -26888,17 +26934,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ICA_MATCH_METHOD_SRV</t>
+          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>ZICA_MATCH_METHOD_SRV</t>
+          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Inter-Company Match Method Maintenance</t>
+          <t>chart of account smaintainance</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -26907,19 +26953,19 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H378" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>MatchingMethodSet</t>
+          <t>ProposedFSVParamSet, CopyGLAccountInCOAParamSet, CopyGLAccountInCOCDParamSet</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/ICA_MATCH_METHOD_SRV</t>
+          <t>/sap/opu/odata/sap/FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
         </is>
       </c>
     </row>
@@ -26934,17 +26980,17 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
+          <t>ICA_MATCH_METHOD_SRV</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_GROUP_MAINTAIN_SRV</t>
+          <t>ZICA_MATCH_METHOD_SRV</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Variant Configuration Characteristic Group Maintenance</t>
+          <t>Inter-Company Match Method Maintenance</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -26953,19 +26999,19 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H379" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>C_ConfignCharcGroupAllocTP, C_ConfignCharcGroupDescTP, C_ConfignCharcGroupTP</t>
+          <t>MatchingMethodSet</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/ICA_MATCH_METHOD_SRV</t>
         </is>
       </c>
     </row>
@@ -26980,17 +27026,17 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>MMIM_PI_CYC_MAINT_SRV</t>
+          <t>LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>ZMMIM_PI_CYC_MAINT_SRV</t>
+          <t>ZLO_VCHCLF_GROUP_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>OData Service of app Cycle Counting - Classification</t>
+          <t>Variant Configuration Characteristic Group Maintenance</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -26999,19 +27045,19 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H380" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>ClassificationReturnSet</t>
+          <t>C_ConfignCharcGroupAllocTP, C_ConfignCharcGroupDescTP, C_ConfignCharcGroupTP</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMIM_PI_CYC_MAINT_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -27026,17 +27072,17 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>MMPUR_PROC_CAT_MAINT_SRV</t>
+          <t>MMIM_PI_CYC_MAINT_SRV</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>ZMMPUR_PROC_CAT_MAINT_SRV</t>
+          <t>ZMMIM_PI_CYC_MAINT_SRV</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Maintian procurement catalog call structure</t>
+          <t>OData Service of app Cycle Counting - Classification</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -27045,19 +27091,19 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H381" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>C_Proccatalogcalldetails, C_Proccatalogcallstruct</t>
+          <t>ClassificationReturnSet</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMPUR_PROC_CAT_MAINT_SRV</t>
+          <t>/sap/opu/odata/sap/MMIM_PI_CYC_MAINT_SRV</t>
         </is>
       </c>
     </row>
@@ -27072,17 +27118,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>MM_PUR_PO_MAINT_V2_SRV</t>
+          <t>MMPUR_PROC_CAT_MAINT_SRV</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>MM_PUR_PO_MAINT_V2_SRV</t>
+          <t>ZMMPUR_PROC_CAT_MAINT_SRV</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Manage Purchase Orders (SmartTemplate)</t>
+          <t>Maintian procurement catalog call structure</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -27091,19 +27137,19 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H382" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>C_POSubcontractingComponentTP, C_PurchaseOrderItemNoteTP, C_PurchaseOrderItemReturnTP, C_PurchaseOrderItemSet, C_PurchaseOrderItemTP, C_PurchaseOrderNoteTP, C_PurchaseOrderPartnerTP, C_PurchaseOrderTP, C_PurOrdAcctAssignmentTP, C_PurOrdItmRetProcNxtPlantTP, C_PurOrdPricingElementTP, C_PurOrdScheduleLineTP, I_SeasonBasic</t>
+          <t>C_Proccatalogcalldetails, C_Proccatalogcallstruct</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PO_MAINT_V2_SRV</t>
+          <t>/sap/opu/odata/sap/MMPUR_PROC_CAT_MAINT_SRV</t>
         </is>
       </c>
     </row>
@@ -27118,17 +27164,17 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
+          <t>MM_PUR_PO_MAINT_V2_SRV</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
+          <t>MM_PUR_PO_MAINT_V2_SRV</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Profnl Purchase Requisition maintan</t>
+          <t>Manage Purchase Orders (SmartTemplate)</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -27137,19 +27183,19 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H383" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>C_PurchaseReqnAcctAssgmt, C_PurchaseReqnDelivAdd, C_PurchaseReqnHeader, C_PurchaseReqnHeaderNotes, C_PurchaseReqnItem, C_PurchaseReqnItemHierTP, C_PurchaseReqnItemText, I_Proccatalogcalldetails</t>
+          <t>C_POSubcontractingComponentTP, C_PurchaseOrderItemNoteTP, C_PurchaseOrderItemReturnTP, C_PurchaseOrderItemSet, C_PurchaseOrderItemTP, C_PurchaseOrderNoteTP, C_PurchaseOrderPartnerTP, C_PurchaseOrderTP, C_PurOrdAcctAssignmentTP, C_PurOrdItmRetProcNxtPlantTP, C_PurOrdPricingElementTP, C_PurOrdScheduleLineTP, I_SeasonBasic</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PO_MAINT_V2_SRV</t>
         </is>
       </c>
     </row>
@@ -27164,17 +27210,17 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>PP_DD_MASSMAINTPROD_SRV</t>
+          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>ZPP_DD_MASSMAINTPROD_SRV</t>
+          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Odata DDR: Mass Maintenance: Products (DD)</t>
+          <t>Profnl Purchase Requisition maintan</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -27183,19 +27229,19 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H384" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>MassEditActionSet, ChangeDDScopeActnSet, C_DemandDrivenProductTP</t>
+          <t>C_PurchaseReqnAcctAssgmt, C_PurchaseReqnDelivAdd, C_PurchaseReqnHeader, C_PurchaseReqnHeaderNotes, C_PurchaseReqnItem, C_PurchaseReqnItemHierTP, C_PurchaseReqnItemText, I_Proccatalogcalldetails</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_MASSMAINTPROD_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -27210,17 +27256,17 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>PP_FCDM_MASS_MAINT</t>
+          <t>PP_DD_MASSMAINTPROD_SRV</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>ZPP_FCDM_MASS_MAINT</t>
+          <t>ZPP_DD_MASSMAINTPROD_SRV</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Demand Forecast Keyfigures and Mass Maintenance</t>
+          <t>Odata DDR: Mass Maintenance: Products (DD)</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -27229,19 +27275,19 @@
         </is>
       </c>
       <c r="G385" t="n">
+        <v>3</v>
+      </c>
+      <c r="H385" t="n">
         <v>2</v>
       </c>
-      <c r="H385" t="n">
-        <v>0</v>
-      </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>PlannedIndepRqmtItem, PlannedIndepRqmt</t>
+          <t>MassEditActionSet, ChangeDDScopeActnSet, C_DemandDrivenProductTP</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_FCDM_MASS_MAINT</t>
+          <t>/sap/opu/odata/sap/PP_DD_MASSMAINTPROD_SRV</t>
         </is>
       </c>
     </row>
@@ -27256,17 +27302,17 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>RSH_EAM_ANALYZE_SRV</t>
+          <t>PP_FCDM_MASS_MAINT</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>RSH_EAM_ANALYZE_SRV</t>
+          <t>ZPP_FCDM_MASS_MAINT</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Resource Scheduling for EAM</t>
+          <t>Demand Forecast Keyfigures and Mass Maintenance</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -27275,19 +27321,19 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H386" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>GlobalFilterTypeCollection, C_RSHEAMUserVariant, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
+          <t>PlannedIndepRqmtItem, PlannedIndepRqmt</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_ANALYZE_SRV</t>
+          <t>/sap/opu/odata/sap/PP_FCDM_MASS_MAINT</t>
         </is>
       </c>
     </row>
@@ -27302,17 +27348,17 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
+          <t>RSH_EAM_ANALYZE_SRV</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>ZRSH_EAM_MAINT_ASSET_BOARD_SRV</t>
+          <t>RSH_EAM_ANALYZE_SRV</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Maintenance Asset Board</t>
+          <t>Resource Scheduling for EAM</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -27321,19 +27367,19 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H387" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintOrder, C_RSHMaintenanceRevisionList</t>
+          <t>GlobalFilterTypeCollection, C_RSHEAMUserVariant, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_ANALYZE_SRV</t>
         </is>
       </c>
     </row>
@@ -27348,17 +27394,17 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
+          <t>RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
+          <t>ZRSH_EAM_MAINT_ASSET_BOARD_SRV</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Maintenance Scheduling Simulation</t>
+          <t>Maintenance Asset Board</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -27367,19 +27413,19 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H388" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>C_RSHEAMUserVariant, C_RSHMaintSchedActivityLog, C_RSHMaintSchedCollaborators, C_RSHMaintSchedRescheduledOp, C_RSHMaintSchedReviewers, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHMaintSchedSmltdOrdAndOp, C_RSHUserVariantWithTeam</t>
+          <t>C_ObjPgMaintOrder, C_RSHMaintenanceRevisionList</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
         </is>
       </c>
     </row>
@@ -27394,17 +27440,17 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>RSH_EAM_ORDER_GANTT_SRV</t>
+          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>ZRSH_EAM_ORDER_GANTT_SRV</t>
+          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Maintenance Order Operation Gantt</t>
+          <t>Maintenance Scheduling Simulation</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -27413,19 +27459,19 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H389" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintOrder, C_RSHEAMUserVariant, C_RSHMaintenanceRevisionList, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
+          <t>C_RSHEAMUserVariant, C_RSHMaintSchedActivityLog, C_RSHMaintSchedCollaborators, C_RSHMaintSchedRescheduledOp, C_RSHMaintSchedReviewers, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHMaintSchedSmltdOrdAndOp, C_RSHUserVariantWithTeam</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_ORDER_GANTT_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
         </is>
       </c>
     </row>
@@ -27440,17 +27486,17 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>RSH_EAM_RES_ASSIGNMENT_SRV</t>
+          <t>RSH_EAM_ORDER_GANTT_SRV</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>ZRSH_EAM_RES_ASSIGNMENT_SRV</t>
+          <t>ZRSH_EAM_ORDER_GANTT_SRV</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Resource Assignment</t>
+          <t>Maintenance Order Operation Gantt</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -27459,19 +27505,19 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H390" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>FEATURECollection, C_RSHEAMUserVariant, C_RSHMaintOpAssgmtResList, C_RSHMaintOperationAssignment, C_RSHUserVariantWithTeam</t>
+          <t>C_ObjPgMaintOrder, C_RSHEAMUserVariant, C_RSHMaintenanceRevisionList, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_RES_ASSIGNMENT_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_ORDER_GANTT_SRV</t>
         </is>
       </c>
     </row>
@@ -27486,17 +27532,17 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>RSH_SB_MAINTENANCE_ORDER</t>
+          <t>RSH_EAM_RES_ASSIGNMENT_SRV</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>ZRSH_SB_MAINTENANCE_ORDER</t>
+          <t>ZRSH_EAM_RES_ASSIGNMENT_SRV</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Service Binding for Maintenance Order</t>
+          <t>Resource Assignment</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -27505,19 +27551,19 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H391" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>C_RSHMaintenanceOrderTP, C_RSHMaintenanceOrdOperationTP, C_RSHMaintenanceOrdOpRelshpTP</t>
+          <t>FEATURECollection, C_RSHEAMUserVariant, C_RSHMaintOpAssgmtResList, C_RSHMaintOperationAssignment, C_RSHUserVariantWithTeam</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_SB_MAINTENANCE_ORDER</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_RES_ASSIGNMENT_SRV</t>
         </is>
       </c>
     </row>
@@ -27532,17 +27578,17 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>UI_C_DFS_MAINT_PLATFORM</t>
+          <t>RSH_SB_MAINTENANCE_ORDER</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>ZUI_C_DFS_MAINT_PLATFORM</t>
+          <t>ZRSH_SB_MAINTENANCE_ORDER</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Service Binding for Platform Code</t>
+          <t>Service Binding for Maintenance Order</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -27551,19 +27597,19 @@
         </is>
       </c>
       <c r="G392" t="n">
+        <v>3</v>
+      </c>
+      <c r="H392" t="n">
         <v>1</v>
       </c>
-      <c r="H392" t="n">
-        <v>9</v>
-      </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>C_DFS_MaintPlatform</t>
+          <t>C_RSHMaintenanceOrderTP, C_RSHMaintenanceOrdOperationTP, C_RSHMaintenanceOrdOpRelshpTP</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_C_DFS_MAINT_PLATFORM</t>
+          <t>/sap/opu/odata/sap/RSH_SB_MAINTENANCE_ORDER</t>
         </is>
       </c>
     </row>
@@ -27578,17 +27624,17 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>UI_MAINTJOBPCKGBUILD_MNG</t>
+          <t>UI_C_DFS_MAINT_PLATFORM</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>UI_MAINTJOBPCKGBUILD_MNG</t>
+          <t>ZUI_C_DFS_MAINT_PLATFORM</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Maintenance Job Package Build Service OData v2</t>
+          <t>Service Binding for Platform Code</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -27600,16 +27646,16 @@
         <v>1</v>
       </c>
       <c r="H393" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>C_MaintJobPackageOperationTP</t>
+          <t>C_DFS_MaintPlatform</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_MAINTJOBPCKGBUILD_MNG</t>
+          <t>/sap/opu/odata/sap/UI_C_DFS_MAINT_PLATFORM</t>
         </is>
       </c>
     </row>
@@ -27619,22 +27665,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PP - Production</t>
+          <t>PM - Maintenance</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BILLOFMATERIALV2_SRV</t>
+          <t>UI_MAINTJOBPCKGBUILD_MNG</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>ZBILLOFMATERIALV2_SRV</t>
+          <t>UI_MAINTJOBPCKGBUILD_MNG</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>BOM Service for Draft 2.0</t>
+          <t>Maintenance Job Package Build Service OData v2</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -27643,19 +27689,19 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H394" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>C_BillOfMaterialItemTP, C_BillOfMaterialSubItemsTP, C_BillOfMaterialTP, C_MngUnassgdEngBOMChgRecd, I_ChangeRecordBsc</t>
+          <t>C_MaintJobPackageOperationTP</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/BILLOFMATERIALV2_SRV</t>
+          <t>/sap/opu/odata/sap/UI_MAINTJOBPCKGBUILD_MNG</t>
         </is>
       </c>
     </row>
@@ -27670,17 +27716,17 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BOMWHEREUSED_SRV</t>
+          <t>BILLOFMATERIALV2_SRV</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>ZBOMWHEREUSED_SRV</t>
+          <t>ZBILLOFMATERIALV2_SRV</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>BOM where used</t>
+          <t>BOM Service for Draft 2.0</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -27689,19 +27735,19 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H395" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>VersionBillOfMaterial, MRPAvailabilitySet, AdditionalControlDataCollection, C_BOMWhereUsedHeader</t>
+          <t>C_BillOfMaterialItemTP, C_BillOfMaterialSubItemsTP, C_BillOfMaterialTP, C_MngUnassgdEngBOMChgRecd, I_ChangeRecordBsc</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/BOMWHEREUSED_SRV</t>
+          <t>/sap/opu/odata/sap/BILLOFMATERIALV2_SRV</t>
         </is>
       </c>
     </row>
@@ -27716,17 +27762,17 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>C_MRPCTRLRBYAOR_SRV</t>
+          <t>BOMWHEREUSED_SRV</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>ZC_MRPCTRLRBYAOR_SRV</t>
+          <t>ZBOMWHEREUSED_SRV</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Service Binding C_MRPCtrlrByAreaOfRespy</t>
+          <t>BOM where used</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -27735,19 +27781,19 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H396" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>I_MRPAreaOfResponsibilityTP</t>
+          <t>VersionBillOfMaterial, MRPAvailabilitySet, AdditionalControlDataCollection, C_BOMWhereUsedHeader</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/C_MRPCTRLRBYAOR_SRV</t>
+          <t>/sap/opu/odata/sap/BOMWHEREUSED_SRV</t>
         </is>
       </c>
     </row>
@@ -27762,17 +27808,17 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>C_WORKCNTRGRPBYAOR_SRV</t>
+          <t>C_MRPCTRLRBYAOR_SRV</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>ZC_WORKCNTRGRPBYAOR_SRV</t>
+          <t>ZC_MRPCTRLRBYAOR_SRV</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Service Binding for WorkCenter Groups AOR</t>
+          <t>Service Binding C_MRPCtrlrByAreaOfRespy</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -27784,16 +27830,16 @@
         <v>1</v>
       </c>
       <c r="H397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>I_WorkCtrGrpByAreaOfRespyTP</t>
+          <t>I_MRPAreaOfResponsibilityTP</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/C_WORKCNTRGRPBYAOR_SRV</t>
+          <t>/sap/opu/odata/sap/C_MRPCTRLRBYAOR_SRV</t>
         </is>
       </c>
     </row>
@@ -27808,17 +27854,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
+          <t>C_WORKCNTRGRPBYAOR_SRV</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
+          <t>ZC_WORKCNTRGRPBYAOR_SRV</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Manage Event-Based Posting Errors</t>
+          <t>Service Binding for WorkCenter Groups AOR</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -27827,19 +27873,19 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H398" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>AnalysisResultCollection, PostingResultCollection</t>
+          <t>I_WorkCtrGrpByAreaOfRespyTP</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_EB_PRODN_COST_ERROR_SRV</t>
+          <t>/sap/opu/odata/sap/C_WORKCNTRGRPBYAOR_SRV</t>
         </is>
       </c>
     </row>
@@ -27854,17 +27900,17 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
+          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>ZFCO_PRODUCTION_COST_ANALYSIS_SRV</t>
+          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Production Cost Analysis</t>
+          <t>Manage Event-Based Posting Errors</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -27873,19 +27919,19 @@
         </is>
       </c>
       <c r="G399" t="n">
+        <v>2</v>
+      </c>
+      <c r="H399" t="n">
         <v>5</v>
       </c>
-      <c r="H399" t="n">
-        <v>0</v>
-      </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>FilterBarCollection, FiscalYearPeriodCollection, ContactInformationCollection, FeatureToggleStatusCollection, C_ExceptionBaseRule</t>
+          <t>AnalysisResultCollection, PostingResultCollection</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
+          <t>/sap/opu/odata/sap/FCO_EB_PRODN_COST_ERROR_SRV</t>
         </is>
       </c>
     </row>
@@ -27900,17 +27946,17 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>FCO_WORKCENTER_COST_SRV</t>
+          <t>FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>ZFCO_WORKCENTER_COST_SRV</t>
+          <t>ZFCO_PRODUCTION_COST_ANALYSIS_SRV</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Analyze Cost by Work Center/Operation</t>
+          <t>Production Cost Analysis</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -27919,19 +27965,19 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>FiscalYearPeriodCollection, LaunchpadKPICollection</t>
+          <t>FilterBarCollection, FiscalYearPeriodCollection, ContactInformationCollection, FeatureToggleStatusCollection, C_ExceptionBaseRule</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_WORKCENTER_COST_SRV</t>
+          <t>/sap/opu/odata/sap/FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
         </is>
       </c>
     </row>
@@ -27946,17 +27992,17 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>LO_VCHCLF</t>
+          <t>FCO_WORKCENTER_COST_SRV</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF</t>
+          <t>ZFCO_WORKCENTER_COST_SRV</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Variant Configuration and Classification Service</t>
+          <t>Analyze Cost by Work Center/Operation</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -27965,19 +28011,19 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H401" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>FiscalYearPeriodCollection, LaunchpadKPICollection</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF</t>
+          <t>/sap/opu/odata/sap/FCO_WORKCENTER_COST_SRV</t>
         </is>
       </c>
     </row>
@@ -27992,17 +28038,17 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
+          <t>LO_VCHCLF</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
+          <t>ZLO_VCHCLF</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Project for Key User Application</t>
+          <t>Variant Configuration and Classification Service</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -28011,19 +28057,19 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H402" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>C_ChFiExCharcAllocTP</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF</t>
         </is>
       </c>
     </row>
@@ -28038,17 +28084,17 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
+          <t>LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
+          <t>ZLO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Legacy appl. integration helper service for VCHCLF</t>
+          <t>Project for Key User Application</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -28057,19 +28103,19 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H403" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ChFiExCharcAllocTP</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
         </is>
       </c>
     </row>
@@ -28084,17 +28130,17 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
+          <t>LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
+          <t>ZLO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Variant Configuration Assign Characteristic Group to Profile</t>
+          <t>Legacy appl. integration helper service for VCHCLF</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -28103,19 +28149,19 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H404" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>C_ConfignPrflCharcGroupAllocTP, C_ConfigurationProfileTP</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
         </is>
       </c>
     </row>
@@ -28130,17 +28176,17 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_SIMULATION_SRV</t>
+          <t>LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_SIMULATION_SRV</t>
+          <t>ZLO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>VCH Simulation Environment</t>
+          <t>Variant Configuration Assign Characteristic Group to Profile</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -28149,19 +28195,19 @@
         </is>
       </c>
       <c r="G405" t="n">
+        <v>2</v>
+      </c>
+      <c r="H405" t="n">
         <v>4</v>
       </c>
-      <c r="H405" t="n">
-        <v>38</v>
-      </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>C_VariantConfigurationSimlnTP, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ConfignPrflCharcGroupAllocTP, C_ConfigurationProfileTP</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_SIMULATION_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
         </is>
       </c>
     </row>
@@ -28176,17 +28222,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>MPEACTIONSETTING_SRV</t>
+          <t>LO_VCHCLF_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>ZMPEACTIONSETTING_SRV</t>
+          <t>ZLO_VCHCLF_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>MPE Action Setting</t>
+          <t>VCH Simulation Environment</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -28195,19 +28241,19 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H406" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>C_AddlRsnCodeGrpForMfgActnTP, C_MfgActionSettingTP, C_MfgActnHandlerToActnSttgTP</t>
+          <t>C_VariantConfigurationSimlnTP, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPEACTIONSETTING_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_SIMULATION_SRV</t>
         </is>
       </c>
     </row>
@@ -28222,17 +28268,17 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>MPE_BUYOFFCYCLE_SRV</t>
+          <t>MPEACTIONSETTING_SRV</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>ZMPE_BUYOFFCYCLE_SRV</t>
+          <t>ZMPEACTIONSETTING_SRV</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>oData service for Buy Off Cycle</t>
+          <t>MPE Action Setting</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -28241,19 +28287,19 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H407" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>C_MfgBuyOffList</t>
+          <t>C_AddlRsnCodeGrpForMfgActnTP, C_MfgActionSettingTP, C_MfgActnHandlerToActnSttgTP</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_BUYOFFCYCLE_SRV</t>
+          <t>/sap/opu/odata/sap/MPEACTIONSETTING_SRV</t>
         </is>
       </c>
     </row>
@@ -28268,17 +28314,17 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>MPE_EXEC_RR_SRV</t>
+          <t>MPE_BUYOFFCYCLE_SRV</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>ZMPE_EXEC_RR_SRV</t>
+          <t>ZMPE_BUYOFFCYCLE_SRV</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Odata Service for Result Recording</t>
+          <t>oData service for Buy Off Cycle</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -28287,19 +28333,19 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H408" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>C_MfgOrdInspCharResultRec, C_MfgOrdPlanInspCharInfo, C_OpActyInstceInspCharcInfo, C_OpActyInstceInspCharcSqnc, C_SFIAtOpActyInspCharcInfo, C_SFIPlanInspCharInfo, C_SFIPlanInspCharResultRec</t>
+          <t>C_MfgBuyOffList</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_EXEC_RR_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_BUYOFFCYCLE_SRV</t>
         </is>
       </c>
     </row>
@@ -28314,17 +28360,17 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>MPE_MANAGE_PRODVER_SRV</t>
+          <t>MPE_EXEC_RR_SRV</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>ZMPE_MANAGE_PRODVER_SRV</t>
+          <t>ZMPE_EXEC_RR_SRV</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Manage Production Version</t>
+          <t>Odata Service for Result Recording</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -28333,19 +28379,19 @@
         </is>
       </c>
       <c r="G409" t="n">
+        <v>7</v>
+      </c>
+      <c r="H409" t="n">
         <v>2</v>
       </c>
-      <c r="H409" t="n">
-        <v>7</v>
-      </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>C_ProdnVersObjPgTP, C_ProdnVersRtgBOMVersObjPgTP</t>
+          <t>C_MfgOrdInspCharResultRec, C_MfgOrdPlanInspCharInfo, C_OpActyInstceInspCharcInfo, C_OpActyInstceInspCharcSqnc, C_SFIAtOpActyInspCharcInfo, C_SFIPlanInspCharInfo, C_SFIPlanInspCharResultRec</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_MANAGE_PRODVER_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_EXEC_RR_SRV</t>
         </is>
       </c>
     </row>
@@ -28360,17 +28406,17 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>MPE_OA_EXECUTION_SRV</t>
+          <t>MPE_MANAGE_PRODVER_SRV</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>ZMPE_OA_EXECUTION_SRV</t>
+          <t>ZMPE_MANAGE_PRODVER_SRV</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Operation Activity Execution</t>
+          <t>Manage Production Version</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -28379,19 +28425,19 @@
         </is>
       </c>
       <c r="G410" t="n">
+        <v>2</v>
+      </c>
+      <c r="H410" t="n">
         <v>7</v>
       </c>
-      <c r="H410" t="n">
-        <v>69</v>
-      </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>C_MfgOrderDefect, C_MfgOrderDefectRecord, UnplannedInspectionCharHtmlReturnCollect, UnplannedCompHtmlReturnCollection, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ProdnVersObjPgTP, C_ProdnVersRtgBOMVersObjPgTP</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_OA_EXECUTION_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_MANAGE_PRODVER_SRV</t>
         </is>
       </c>
     </row>
@@ -28406,17 +28452,17 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>MPE_PRODORDER_OBJPG_SRV</t>
+          <t>MPE_OA_EXECUTION_SRV</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>ZMPE_PRODORDER_OBJPG_SRV</t>
+          <t>ZMPE_OA_EXECUTION_SRV</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Production Order Object Page SEGW Project</t>
+          <t>Operation Activity Execution</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -28425,19 +28471,19 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H411" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_MfgOrderDefect, C_MfgOrderDefectRecord, UnplannedInspectionCharHtmlReturnCollect, UnplannedCompHtmlReturnCollection, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_PRODORDER_OBJPG_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_OA_EXECUTION_SRV</t>
         </is>
       </c>
     </row>
@@ -28452,17 +28498,17 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>MPE_QUALIFICATIONS_SRV</t>
+          <t>MPE_PRODORDER_OBJPG_SRV</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>ZMPE_QUALIFICATIONS_SRV</t>
+          <t>ZMPE_PRODORDER_OBJPG_SRV</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>oData for HR Qualification Assignment</t>
+          <t>Production Order Object Page SEGW Project</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -28471,19 +28517,19 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H412" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>C_MfgQualifnMaterialAssgmtTP, C_MfgQualifnWrkCtrAssgmtTP</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_QUALIFICATIONS_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_PRODORDER_OBJPG_SRV</t>
         </is>
       </c>
     </row>
@@ -28498,17 +28544,17 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>PLMI_PROCESS_ROUTE</t>
+          <t>MPE_QUALIFICATIONS_SRV</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>ZPLMI_PROCESS_ROUTE</t>
+          <t>ZMPE_QUALIFICATIONS_SRV</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Service for Process Route</t>
+          <t>oData for HR Qualification Assignment</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -28517,19 +28563,19 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H413" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>ProcessRouteDdlnRecipient, ProcessRouteObjAssignment, ProcessRouteTask, ProcessRouteTaskDcsnDSgntr, ProcessRouteTaskDecision, ProcessRouteTaskNote</t>
+          <t>C_MfgQualifnMaterialAssgmtTP, C_MfgQualifnWrkCtrAssgmtTP</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PLMI_PROCESS_ROUTE</t>
+          <t>/sap/opu/odata/sap/MPE_QUALIFICATIONS_SRV</t>
         </is>
       </c>
     </row>
@@ -28544,17 +28590,17 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PLMI_RECIPE_FINDER</t>
+          <t>PLMI_PROCESS_ROUTE</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>ZPLMI_RECIPE_FINDER</t>
+          <t>ZPLMI_PROCESS_ROUTE</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Recipe Finder</t>
+          <t>Service for Process Route</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -28563,19 +28609,19 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H414" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>RecipeFinderCaches</t>
+          <t>ProcessRouteDdlnRecipient, ProcessRouteObjAssignment, ProcessRouteTask, ProcessRouteTaskDcsnDSgntr, ProcessRouteTaskDecision, ProcessRouteTaskNote</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PLMI_RECIPE_FINDER</t>
+          <t>/sap/opu/odata/sap/PLMI_PROCESS_ROUTE</t>
         </is>
       </c>
     </row>
@@ -28590,17 +28636,17 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>PLMI_SYNCUNITR2B_MANAGE</t>
+          <t>PLMI_RECIPE_FINDER</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>ZPLMI_SYNCUNITR2B_MANAGE</t>
+          <t>ZPLMI_RECIPE_FINDER</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Manage R2B Synchronization Units</t>
+          <t>Recipe Finder</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -28612,16 +28658,16 @@
         <v>1</v>
       </c>
       <c r="H415" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>I_BillOfMaterialTP</t>
+          <t>RecipeFinderCaches</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PLMI_SYNCUNITR2B_MANAGE</t>
+          <t>/sap/opu/odata/sap/PLMI_RECIPE_FINDER</t>
         </is>
       </c>
     </row>
@@ -28636,17 +28682,17 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>PMRP_FLXBLCSTRT_UI_SERVICE</t>
+          <t>PLMI_SYNCUNITR2B_MANAGE</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>ZPMRP_FLXBLCSTRT_UI_SERVICE</t>
+          <t>ZPLMI_SYNCUNITR2B_MANAGE</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Service for Flexible Constraint</t>
+          <t>Manage R2B Synchronization Units</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -28655,19 +28701,19 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H416" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>C_PMRPFlexibleConstraintPeriod, C_PMRPFlexibleConstraintText, C_PMRPFlxblConstraintProduct</t>
+          <t>I_BillOfMaterialTP</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PMRP_FLXBLCSTRT_UI_SERVICE</t>
+          <t>/sap/opu/odata/sap/PLMI_SYNCUNITR2B_MANAGE</t>
         </is>
       </c>
     </row>
@@ -28682,17 +28728,17 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>PMRP_RECEIPT_SERVICE</t>
+          <t>PMRP_FLXBLCSTRT_UI_SERVICE</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>ZPMRP_RECEIPT_SERVICE</t>
+          <t>ZPMRP_FLXBLCSTRT_UI_SERVICE</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>RAP: PMRP_RECEIPT_SERVICE generated at 20190415</t>
+          <t>Service for Flexible Constraint</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -28701,19 +28747,19 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H417" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>PMRPReceiptItem</t>
+          <t>C_PMRPFlexibleConstraintPeriod, C_PMRPFlexibleConstraintText, C_PMRPFlxblConstraintProduct</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PMRP_RECEIPT_SERVICE</t>
+          <t>/sap/opu/odata/sap/PMRP_FLXBLCSTRT_UI_SERVICE</t>
         </is>
       </c>
     </row>
@@ -28728,17 +28774,17 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>PMRP_SIMULATION_SERVICE</t>
+          <t>PMRP_RECEIPT_SERVICE</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>ZPMRP_SIMULATION_SERVICE</t>
+          <t>ZPMRP_RECEIPT_SERVICE</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>RAP: PMRP_SIMULATION_SERVICE generated at 20181203</t>
+          <t>RAP: PMRP_RECEIPT_SERVICE generated at 20190415</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -28750,16 +28796,16 @@
         <v>1</v>
       </c>
       <c r="H418" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>PMRPSimulationText</t>
+          <t>PMRPReceiptItem</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PMRP_SIMULATION_SERVICE</t>
+          <t>/sap/opu/odata/sap/PMRP_RECEIPT_SERVICE</t>
         </is>
       </c>
     </row>
@@ -28774,17 +28820,17 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>PPDS_CAPA_UTIL_OBJ_SRV</t>
+          <t>PMRP_SIMULATION_SERVICE</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>ZPPDS_CAPA_UTIL_OBJ_SRV</t>
+          <t>ZPMRP_SIMULATION_SERVICE</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Capacity Utilization Object Page</t>
+          <t>RAP: PMRP_SIMULATION_SERVICE generated at 20181203</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -28796,16 +28842,16 @@
         <v>1</v>
       </c>
       <c r="H419" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>DowntimesSet</t>
+          <t>PMRPSimulationText</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PPDS_CAPA_UTIL_OBJ_SRV</t>
+          <t>/sap/opu/odata/sap/PMRP_SIMULATION_SERVICE</t>
         </is>
       </c>
     </row>
@@ -28820,17 +28866,17 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PP_CFS_CAPEVAL_SRV</t>
+          <t>PPDS_CAPA_UTIL_OBJ_SRV</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>ZPP_CFS_CAPEVAL_SRV</t>
+          <t>ZPPDS_CAPA_UTIL_OBJ_SRV</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Production Planning: Capacity Evaluation App</t>
+          <t>Capacity Utilization Object Page</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -28839,19 +28885,19 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H420" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>RescheduleCollection, C_WorkCenterCapOverviewTP, C_WrkCtrAvailableCapacityTP, C_WrkCtrCapShiftIntervalTP</t>
+          <t>DowntimesSet</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_CFS_CAPEVAL_SRV</t>
+          <t>/sap/opu/odata/sap/PPDS_CAPA_UTIL_OBJ_SRV</t>
         </is>
       </c>
     </row>
@@ -28866,17 +28912,17 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>PP_DD_BUFPOS_SRV</t>
+          <t>PP_CFS_CAPEVAL_SRV</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>ZPP_DD_BUFPOS_SRV</t>
+          <t>ZPP_CFS_CAPEVAL_SRV</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>OData DDR: Buffer Positioning</t>
+          <t>Production Planning: Capacity Evaluation App</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -28885,19 +28931,19 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H421" t="n">
         <v>9</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>MassActionCollection, ChangeDDScopeActnSet, C_ProdBufPositioningTP</t>
+          <t>RescheduleCollection, C_WorkCenterCapOverviewTP, C_WrkCtrAvailableCapacityTP, C_WrkCtrCapShiftIntervalTP</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_BUFPOS_SRV</t>
+          <t>/sap/opu/odata/sap/PP_CFS_CAPEVAL_SRV</t>
         </is>
       </c>
     </row>
@@ -28912,17 +28958,17 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PP_DD_MASSADJBUF_SRV</t>
+          <t>PP_DD_BUFPOS_SRV</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>ZPP_DD_MASSADJBUF_SRV</t>
+          <t>ZPP_DD_BUFPOS_SRV</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>OData PP: Mass Adjust Buffers</t>
+          <t>OData DDR: Buffer Positioning</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -28931,19 +28977,19 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H422" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>MassAdjiustActionSet</t>
+          <t>MassActionCollection, ChangeDDScopeActnSet, C_ProdBufPositioningTP</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_MASSADJBUF_SRV</t>
+          <t>/sap/opu/odata/sap/PP_DD_BUFPOS_SRV</t>
         </is>
       </c>
     </row>
@@ -28958,17 +29004,17 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PP_DD_STLM_SRV</t>
+          <t>PP_DD_MASSADJBUF_SRV</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>ZPP_DD_STLM_SRV</t>
+          <t>ZPP_DD_MASSADJBUF_SRV</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Odata DDR: Manage Buffer Levels</t>
+          <t>OData PP: Mass Adjust Buffers</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -28977,19 +29023,19 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H423" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>MassAdjiustActionSet, BufLvlActionsCollection, C_ProdBufLvlDmndAdjmtFctrTP, C_ProdBufLvlZnAdjmtFctrTP, C_ProductBufferLevelChartTP, C_ProductBufferLevelMgmtTP, C_ProductDailyDemandChartTP</t>
+          <t>MassAdjiustActionSet</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_STLM_SRV</t>
+          <t>/sap/opu/odata/sap/PP_DD_MASSADJBUF_SRV</t>
         </is>
       </c>
     </row>
@@ -29004,17 +29050,17 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PP_MNTR_WRKCTR_SRV</t>
+          <t>PP_DD_STLM_SRV</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>ZPP_MNTR_WRKCTR_SRV</t>
+          <t>ZPP_DD_STLM_SRV</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Monitor Work Center Schedules</t>
+          <t>Odata DDR: Manage Buffer Levels</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -29023,19 +29069,19 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H424" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
+          <t>MassAdjiustActionSet, BufLvlActionsCollection, C_ProdBufLvlDmndAdjmtFctrTP, C_ProdBufLvlZnAdjmtFctrTP, C_ProductBufferLevelChartTP, C_ProductBufferLevelMgmtTP, C_ProductDailyDemandChartTP</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MNTR_WRKCTR_SRV</t>
+          <t>/sap/opu/odata/sap/PP_DD_STLM_SRV</t>
         </is>
       </c>
     </row>
@@ -29050,17 +29096,17 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PP_MPE_OPER_MANAGE</t>
+          <t>PP_MNTR_WRKCTR_SRV</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>ZPP_MPE_OPER_MANAGE</t>
+          <t>ZPP_MNTR_WRKCTR_SRV</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Manage Operations</t>
+          <t>Monitor Work Center Schedules</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -29069,19 +29115,19 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H425" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>C_MfgOrderDefectRecord</t>
+          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MPE_OPER_MANAGE</t>
+          <t>/sap/opu/odata/sap/PP_MNTR_WRKCTR_SRV</t>
         </is>
       </c>
     </row>
@@ -29096,17 +29142,17 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PP_MPE_ORDER_MANAGE</t>
+          <t>PP_MPE_OPER_MANAGE</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>ZPP_MPE_ORDER_MANAGE</t>
+          <t>ZPP_MPE_OPER_MANAGE</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Manage Orders</t>
+          <t>Manage Operations</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -29115,19 +29161,19 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H426" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_MfgOrderDefectRecord</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MPE_ORDER_MANAGE</t>
+          <t>/sap/opu/odata/sap/PP_MPE_OPER_MANAGE</t>
         </is>
       </c>
     </row>
@@ -29142,17 +29188,17 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PP_MRP_COCKPIT_SRV</t>
+          <t>PP_MPE_ORDER_MANAGE</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>ZPP_MRP_COCKPIT_SRV</t>
+          <t>ZPP_MPE_ORDER_MANAGE</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>MRP Cockpit</t>
+          <t>Manage Orders</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -29161,19 +29207,19 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H427" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>ChangeRequestProposals, ChangeRequestEMailTextCollection, ChangeRequests, SchedAgmtReleaseListItems, MMPurchaseOrderScheduleLines</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MRP_COCKPIT_SRV</t>
+          <t>/sap/opu/odata/sap/PP_MPE_ORDER_MANAGE</t>
         </is>
       </c>
     </row>
@@ -29188,17 +29234,17 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PP_PROCESS_ORDER_MANAGE_SRV</t>
+          <t>PP_MRP_COCKPIT_SRV</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>ZPP_PROCESS_ORDER_MANAGE_SRV</t>
+          <t>ZPP_MRP_COCKPIT_SRV</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Manage Process Orders</t>
+          <t>MRP Cockpit</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -29207,19 +29253,19 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H428" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>C_PROC_ORD_MNG_GET_ENTITYSET</t>
+          <t>ChangeRequestProposals, ChangeRequestEMailTextCollection, ChangeRequests, SchedAgmtReleaseListItems, MMPurchaseOrderScheduleLines</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_PROCESS_ORDER_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/PP_MRP_COCKPIT_SRV</t>
         </is>
       </c>
     </row>
@@ -29234,17 +29280,17 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PP_SCHEDULEPRODUCTION_SRV</t>
+          <t>PP_PROCESS_ORDER_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>ZPP_SCHEDULEPRODUCTION_SRV</t>
+          <t>ZPP_PROCESS_ORDER_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Schedule Production</t>
+          <t>Manage Process Orders</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -29253,19 +29299,19 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H429" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
+          <t>C_PROC_ORD_MNG_GET_ENTITYSET</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_SCHEDULEPRODUCTION_SRV</t>
+          <t>/sap/opu/odata/sap/PP_PROCESS_ORDER_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -29280,17 +29326,17 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PP_WORKCENTER_GROUP_SRV</t>
+          <t>PP_SCHEDULEPRODUCTION_SRV</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>ZPP_WORKCENTER_GROUP_SRV</t>
+          <t>ZPP_SCHEDULEPRODUCTION_SRV</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Manage Work Center Groups</t>
+          <t>Schedule Production</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -29299,19 +29345,19 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H430" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>WRKCTRGRPEDITFLAGCollection</t>
+          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_WORKCENTER_GROUP_SRV</t>
+          <t>/sap/opu/odata/sap/PP_SCHEDULEPRODUCTION_SRV</t>
         </is>
       </c>
     </row>
@@ -29326,17 +29372,17 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>UI_PRODUCTIONVERSION</t>
+          <t>PP_WORKCENTER_GROUP_SRV</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>ZUI_PRODUCTIONVERSION</t>
+          <t>ZPP_WORKCENTER_GROUP_SRV</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Odata Service for Production Version</t>
+          <t>Manage Work Center Groups</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -29345,19 +29391,19 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H431" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>ProdnVersConsistencyLog, ProductionVersion, RecmddProductionVersion</t>
+          <t>WRKCTRGRPEDITFLAGCollection</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_PRODUCTIONVERSION</t>
+          <t>/sap/opu/odata/sap/PP_WORKCENTER_GROUP_SRV</t>
         </is>
       </c>
     </row>
@@ -29372,17 +29418,17 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>UI_VARCNFCHARCEXCLMAN</t>
+          <t>UI_PRODUCTIONVERSION</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>ZUI_VARCNFCHARCEXCLMAN</t>
+          <t>ZUI_PRODUCTIONVERSION</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Manage Cstic Exclusion App V2</t>
+          <t>Odata Service for Production Version</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -29391,19 +29437,19 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H432" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>C_VarCnfExclCharcDetail</t>
+          <t>ProdnVersConsistencyLog, ProductionVersion, RecmddProductionVersion</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_VARCNFCHARCEXCLMAN</t>
+          <t>/sap/opu/odata/sap/UI_PRODUCTIONVERSION</t>
         </is>
       </c>
     </row>
@@ -29418,17 +29464,17 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>UI_WORKCENTERCAPLIST_02</t>
+          <t>UI_VARCNFCHARCEXCLMAN</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>ZUI_WORKCENTERCAPLIST_02</t>
+          <t>ZUI_VARCNFCHARCEXCLMAN</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Odata Service for Work Center Capacity</t>
+          <t>Manage Cstic Exclusion App V2</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -29437,19 +29483,19 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>CapCtrlrCapacityHeader, CapCtrlrCapacityList, CapCtrlrIntervalShifts</t>
+          <t>C_VarCnfExclCharcDetail</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_WORKCENTERCAPLIST_02</t>
+          <t>/sap/opu/odata/sap/UI_VARCNFCHARCEXCLMAN</t>
         </is>
       </c>
     </row>
@@ -29459,22 +29505,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PS - Projects</t>
+          <t>PP - Production</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>CA_RSM_TEAM_ACTION_SRV</t>
+          <t>UI_WORKCENTERCAPLIST_02</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>ZCA_RSM_TEAM_ACTION_SRV</t>
+          <t>ZUI_WORKCENTERCAPLIST_02</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Project for Manage Teams And Responsibilities</t>
+          <t>Odata Service for Work Center Capacity</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -29483,19 +29529,19 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H434" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>RSM_SEARCHSet</t>
+          <t>CapCtrlrCapacityHeader, CapCtrlrCapacityList, CapCtrlrIntervalShifts</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CA_RSM_TEAM_ACTION_SRV</t>
+          <t>/sap/opu/odata/sap/UI_WORKCENTERCAPLIST_02</t>
         </is>
       </c>
     </row>
@@ -29510,17 +29556,17 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>CA_RSM_TEAM_SRV</t>
+          <t>CA_RSM_TEAM_ACTION_SRV</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>ZCA_RSM_TEAM_SRV</t>
+          <t>ZCA_RSM_TEAM_ACTION_SRV</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Project for Maintain Teams as Responsible</t>
+          <t>Project for Manage Teams And Responsibilities</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -29529,19 +29575,19 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H435" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>MASS_MEMBER_CHANGESet, C_RespyMgmtTeamAttributeTP, C_RespyMgmtTeamHeaderTP, C_RespyMgmtTeamMbrFuncTP, C_RespyMgmtTeamMemberTP, C_RespyMgmtTeamOrgUnitTP, C_RespyMgmtTeamOwnerTP</t>
+          <t>RSM_SEARCHSet</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CA_RSM_TEAM_SRV</t>
+          <t>/sap/opu/odata/sap/CA_RSM_TEAM_ACTION_SRV</t>
         </is>
       </c>
     </row>
@@ -29556,17 +29602,17 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
+          <t>CA_RSM_TEAM_SRV</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
+          <t>ZCA_RSM_TEAM_SRV</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Master Project Overview</t>
+          <t>Project for Maintain Teams as Responsible</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -29575,19 +29621,19 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H436" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>I_ServiceEntrySheetItem</t>
+          <t>MASS_MEMBER_CHANGESet, C_RespyMgmtTeamAttributeTP, C_RespyMgmtTeamHeaderTP, C_RespyMgmtTeamMbrFuncTP, C_RespyMgmtTeamMemberTP, C_RespyMgmtTeamOrgUnitTP, C_RespyMgmtTeamOwnerTP</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CPD_MASTERPROJECT_OVERVIEW_SRV</t>
+          <t>/sap/opu/odata/sap/CA_RSM_TEAM_SRV</t>
         </is>
       </c>
     </row>
@@ -29597,22 +29643,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>QM - Quality</t>
+          <t>PS - Projects</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>CMD_QLTY_MANAGE_IMPORTS</t>
+          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>ZCMD_QLTY_MANAGE_IMPORTS</t>
+          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Master Data Quality - oData Service for Manage Imports</t>
+          <t>Master Project Overview</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -29628,12 +29674,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>ImportUUIDsTypeCollection</t>
+          <t>I_ServiceEntrySheetItem</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CMD_QLTY_MANAGE_IMPORTS</t>
+          <t>/sap/opu/odata/sap/CPD_MASTERPROJECT_OVERVIEW_SRV</t>
         </is>
       </c>
     </row>
@@ -29648,17 +29694,17 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
+          <t>CMD_QLTY_MANAGE_IMPORTS</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
+          <t>ZCMD_QLTY_MANAGE_IMPORTS</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Inspect WIP/Variance Posting</t>
+          <t>Master Data Quality - oData Service for Manage Imports</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -29667,19 +29713,19 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H438" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>ErrorNumberCollection, PostingResultCollection, FiscalYearPeriodCollection, DateCollection</t>
+          <t>ImportUUIDsTypeCollection</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_EBW_ORDER_INSPECTOR_SRV</t>
+          <t>/sap/opu/odata/sap/CMD_QLTY_MANAGE_IMPORTS</t>
         </is>
       </c>
     </row>
@@ -29694,17 +29740,17 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>MPE_EXEC_NON_CONFORMANCE_SRV</t>
+          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>ZMPE_EXEC_NON_CONFORMANCE_SRV</t>
+          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>oData service for defect recording</t>
+          <t>Inspect WIP/Variance Posting</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -29713,19 +29759,19 @@
         </is>
       </c>
       <c r="G439" t="n">
+        <v>4</v>
+      </c>
+      <c r="H439" t="n">
         <v>2</v>
       </c>
-      <c r="H439" t="n">
-        <v>1</v>
-      </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>AttachmentContentSet, C_MfgOrderDefect</t>
+          <t>ErrorNumberCollection, PostingResultCollection, FiscalYearPeriodCollection, DateCollection</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_EXEC_NON_CONFORMANCE_SRV</t>
+          <t>/sap/opu/odata/sap/FCO_EBW_ORDER_INSPECTOR_SRV</t>
         </is>
       </c>
     </row>
@@ -29740,17 +29786,17 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>QM_DEFECT_RECORD_SRV</t>
+          <t>MPE_EXEC_NON_CONFORMANCE_SRV</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>ZQM_DEFECT_RECORD_SRV</t>
+          <t>ZMPE_EXEC_NON_CONFORMANCE_SRV</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Record Defects</t>
+          <t>oData service for defect recording</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -29759,19 +29805,19 @@
         </is>
       </c>
       <c r="G440" t="n">
+        <v>2</v>
+      </c>
+      <c r="H440" t="n">
         <v>1</v>
       </c>
-      <c r="H440" t="n">
-        <v>43</v>
-      </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>C_DefectRecord</t>
+          <t>AttachmentContentSet, C_MfgOrderDefect</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_DEFECT_RECORD_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_EXEC_NON_CONFORMANCE_SRV</t>
         </is>
       </c>
     </row>
@@ -29786,17 +29832,17 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>QM_FMEA_MNG_SRV</t>
+          <t>QM_DEFECT_RECORD_SRV</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>ZQM_FMEA_MNG_SRV</t>
+          <t>ZQM_DEFECT_RECORD_SRV</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Manage FMEA</t>
+          <t>Record Defects</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -29805,19 +29851,19 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H441" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>C_FMEAMng, C_FMEAMngCauseTask, C_FMEAMngNode, C_FMEAMngNodeText</t>
+          <t>C_DefectRecord</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_FMEA_MNG_SRV</t>
+          <t>/sap/opu/odata/sap/QM_DEFECT_RECORD_SRV</t>
         </is>
       </c>
     </row>
@@ -29832,17 +29878,17 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>QM_INFOREC_PROC_MANAGE_SRV</t>
+          <t>QM_FMEA_MNG_SRV</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>ZQM_INFOREC_PROC_MANAGE_SRV</t>
+          <t>ZQM_FMEA_MNG_SRV</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>OData QM: Manage Quality Info Records</t>
+          <t>Manage FMEA</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -29851,19 +29897,19 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H442" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>C_QltyFirstArticleInsp, C_QltyInProcurementManage</t>
+          <t>C_FMEAMng, C_FMEAMngCauseTask, C_FMEAMngNode, C_FMEAMngNodeText</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INFOREC_PROC_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_FMEA_MNG_SRV</t>
         </is>
       </c>
     </row>
@@ -29878,17 +29924,17 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>QM_INSPMETHOD_OBJECTPAGE_SRV</t>
+          <t>QM_INFOREC_PROC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>ZQM_INSPMETHOD_OBJECTPAGE_SRV</t>
+          <t>ZQM_INFOREC_PROC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>OData QM: Inspection Specification Object Page OData Service</t>
+          <t>OData QM: Manage Quality Info Records</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -29897,19 +29943,19 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H443" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_QltyFirstArticleInsp, C_QltyInProcurementManage</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSPMETHOD_OBJECTPAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INFOREC_PROC_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -29924,12 +29970,12 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>QM_INSPSPEC_OBJECTPAGE_SRV</t>
+          <t>QM_INSPMETHOD_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>ZQM_INSPSPEC_OBJECTPAGE_SRV</t>
+          <t>ZQM_INSPMETHOD_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -29955,7 +30001,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSPSPEC_OBJECTPAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSPMETHOD_OBJECTPAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -29970,17 +30016,17 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>QM_INSPUSGDSC_MANAGE_SRV</t>
+          <t>QM_INSPSPEC_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>ZQM_INSPUSGDSC_MANAGE_SRV</t>
+          <t>ZQM_INSPSPEC_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>OData QM: Manage Usage Decision</t>
+          <t>OData QM: Inspection Specification Object Page OData Service</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -29989,19 +30035,19 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H445" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>C_InspUsgDesc</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSPUSGDSC_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSPSPEC_OBJECTPAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30016,17 +30062,17 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>QM_INSP_PLAN_SRV</t>
+          <t>QM_INSPUSGDSC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>ZQM_INSP_PLAN_SRV</t>
+          <t>ZQM_INSPUSGDSC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Inspection Plan</t>
+          <t>OData QM: Manage Usage Decision</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -30035,19 +30081,19 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H446" t="n">
         <v>11</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>C_InspectionPlan, C_InspPlanDpndantCharc, C_InspPlanMatlAssgmt, C_InspPlanOpCharc, C_InspPlanOperation</t>
+          <t>C_InspUsgDesc</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSP_PLAN_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSPUSGDSC_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30062,17 +30108,17 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>QM_MLTPLRR_SRV</t>
+          <t>QM_INSP_PLAN_SRV</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>ZQM_MLTPLRR_SRV</t>
+          <t>ZQM_INSP_PLAN_SRV</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Record Multiple Results</t>
+          <t>Inspection Plan</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -30081,19 +30127,19 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H447" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>C_InspResultMltplRsltRec, C_InspRsltValueMltplRsltRec</t>
+          <t>C_InspectionPlan, C_InspPlanDpndantCharc, C_InspPlanMatlAssgmt, C_InspPlanOpCharc, C_InspPlanOperation</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_MLTPLRR_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSP_PLAN_SRV</t>
         </is>
       </c>
     </row>
@@ -30108,17 +30154,17 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>QM_QTASK_PROC_SRV</t>
+          <t>QM_MLTPLRR_SRV</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>ZQM_QTASK_PROC_SRV</t>
+          <t>ZQM_MLTPLRR_SRV</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Process Quality Tasks</t>
+          <t>Record Multiple Results</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -30127,19 +30173,19 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H448" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>C_QltyTskProcFllwActnTblParam, C_QualityTaskProcess, I_ChangeRecordBsc, I_ProbSolvingProcTP</t>
+          <t>C_InspResultMltplRsltRec, C_InspRsltValueMltplRsltRec</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_QTASK_PROC_SRV</t>
+          <t>/sap/opu/odata/sap/QM_MLTPLRR_SRV</t>
         </is>
       </c>
     </row>
@@ -30154,17 +30200,17 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>QM_RR_SRV</t>
+          <t>QM_QTASK_PROC_SRV</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>ZQM_RR_SRV</t>
+          <t>ZQM_QTASK_PROC_SRV</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>OData QM: Inspection Results Recording OData Service</t>
+          <t>Process Quality Tasks</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -30173,19 +30219,19 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H449" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>C_UnplndInspCharcRsltRecg, CharResultDetailsSet</t>
+          <t>C_QltyTskProcFllwActnTblParam, C_QualityTaskProcess, I_ChangeRecordBsc, I_ProbSolvingProcTP</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_RR_SRV</t>
+          <t>/sap/opu/odata/sap/QM_QTASK_PROC_SRV</t>
         </is>
       </c>
     </row>
@@ -30200,17 +30246,17 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>QM_SUBSET_RR_SRV</t>
+          <t>QM_RR_SRV</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>ZQM_SUBSET_RR_SRV</t>
+          <t>ZQM_RR_SRV</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Record Results for Inspection Points</t>
+          <t>OData QM: Inspection Results Recording OData Service</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -30219,19 +30265,19 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H450" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>C_InspSubsetCharcResult, C_InspSubsetResultValue, C_InspSubsetRsltRec</t>
+          <t>C_UnplndInspCharcRsltRecg, CharResultDetailsSet</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_SUBSET_RR_SRV</t>
+          <t>/sap/opu/odata/sap/QM_RR_SRV</t>
         </is>
       </c>
     </row>
@@ -30246,17 +30292,17 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>SIMDQ_SERVICES_SRV</t>
+          <t>QM_SUBSET_RR_SRV</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>ZSIMDQ_SERVICES_SRV</t>
+          <t>ZQM_SUBSET_RR_SRV</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Data Quality related services</t>
+          <t>Record Results for Inspection Points</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -30265,19 +30311,19 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H451" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>dqmmConfigCompleteResponseCollection, setCountryActiveCollection</t>
+          <t>C_InspSubsetCharcResult, C_InspSubsetResultValue, C_InspSubsetRsltRec</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SIMDQ_SERVICES_SRV</t>
+          <t>/sap/opu/odata/sap/QM_SUBSET_RR_SRV</t>
         </is>
       </c>
     </row>
@@ -30292,17 +30338,17 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>UI_INSPLOT_RSLTRECG</t>
+          <t>SIMDQ_SERVICES_SRV</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>ZUI_INSPLOT_RSLTRECG</t>
+          <t>ZSIMDQ_SERVICES_SRV</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Service Binding for inspection lot Result Recording</t>
+          <t>Data Quality related services</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -30311,19 +30357,19 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>InspChar, UnplannedCharacteristic, InspectionResultValue, InspectionLot</t>
+          <t>dqmmConfigCompleteResponseCollection, setCountryActiveCollection</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_INSPLOT_RSLTRECG</t>
+          <t>/sap/opu/odata/sap/SIMDQ_SERVICES_SRV</t>
         </is>
       </c>
     </row>
@@ -30333,22 +30379,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail (RFM)</t>
+          <t>QM - Quality</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>UI_RFM_ASSIGN_PROD_TO_DCS</t>
+          <t>UI_INSPLOT_RSLTRECG</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>ZUI_RFM_ASSIGN_PROD_TO_DCS</t>
+          <t>ZUI_INSPLOT_RSLTRECG</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Assign Product to Distribution Centers</t>
+          <t>Service Binding for inspection lot Result Recording</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -30357,19 +30403,19 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H453" t="n">
         <v>1</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>ProductDistrCtrListing</t>
+          <t>InspChar, UnplannedCharacteristic, InspectionResultValue, InspectionLot</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_ASSIGN_PROD_TO_DCS</t>
+          <t>/sap/opu/odata/sap/UI_INSPLOT_RSLTRECG</t>
         </is>
       </c>
     </row>
@@ -30384,17 +30430,17 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>UI_RFM_MNG_ASSTMT_MODULES</t>
+          <t>UI_RFM_ASSIGN_PROD_TO_DCS</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>ZUI_RFM_MNG_ASSTMT_MODULES</t>
+          <t>ZUI_RFM_ASSIGN_PROD_TO_DCS</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Manage Assortment Modules</t>
+          <t>Assign Product to Distribution Centers</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -30403,19 +30449,19 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H454" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>AssortmentModuleVersionText, AssortmentModuleText, AssortmentModule, AssortmentModuleVersion, AssortmentModuleUser, ProductToAssortmentModuleVers</t>
+          <t>ProductDistrCtrListing</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_MNG_ASSTMT_MODULES</t>
+          <t>/sap/opu/odata/sap/UI_RFM_ASSIGN_PROD_TO_DCS</t>
         </is>
       </c>
     </row>
@@ -30430,17 +30476,17 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>UI_RFM_POCNSLDTNRULE</t>
+          <t>UI_RFM_MNG_ASSTMT_MODULES</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>ZUI_RFM_POCNSLDTNRULE</t>
+          <t>ZUI_RFM_MNG_ASSTMT_MODULES</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Purchase Order Consolidation Rule</t>
+          <t>Manage Assortment Modules</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -30449,19 +30495,19 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H455" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>C_RFM_POCnsldtnRuleTP</t>
+          <t>AssortmentModuleVersionText, AssortmentModuleText, AssortmentModule, AssortmentModuleVersion, AssortmentModuleUser, ProductToAssortmentModuleVers</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_POCNSLDTNRULE</t>
+          <t>/sap/opu/odata/sap/UI_RFM_MNG_ASSTMT_MODULES</t>
         </is>
       </c>
     </row>
@@ -30476,17 +30522,17 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>UI_RFM_PROD_ASSGN_EXPL_ASM</t>
+          <t>UI_RFM_POCNSLDTNRULE</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>ZUI_RFM_PROD_ASSGN_EXPL_ASM</t>
+          <t>ZUI_RFM_POCNSLDTNRULE</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Service Binding for UI_RFM_PROD_ASSIGN_EXPL_ASM</t>
+          <t>Purchase Order Consolidation Rule</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -30498,16 +30544,16 @@
         <v>1</v>
       </c>
       <c r="H456" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>ProdToExplicitAsstmtMdl</t>
+          <t>C_RFM_POCnsldtnRuleTP</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_PROD_ASSGN_EXPL_ASM</t>
+          <t>/sap/opu/odata/sap/UI_RFM_POCNSLDTNRULE</t>
         </is>
       </c>
     </row>
@@ -30522,17 +30568,17 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>UI_RFM_SUPPLY_SORTRULE</t>
+          <t>UI_RFM_PROD_ASSGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>ZUI_RFM_SUPPLY_SORTRULE</t>
+          <t>ZUI_RFM_PROD_ASSGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>RAP: UI_RFM_SUPPLY_SORTRULE generated at 20190314</t>
+          <t>Service Binding for UI_RFM_PROD_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -30541,19 +30587,19 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H457" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>ArunStockSortDynAttrib, ARunSupplySortRule, ArunStockSortStaticAttrib, ArunStockSortStaticAtribVal</t>
+          <t>ProdToExplicitAsstmtMdl</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_SUPPLY_SORTRULE</t>
+          <t>/sap/opu/odata/sap/UI_RFM_PROD_ASSGN_EXPL_ASM</t>
         </is>
       </c>
     </row>
@@ -30568,17 +30614,17 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>UI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>UI_RFM_SUPPLY_SORTRULE</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>ZUI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>ZUI_RFM_SUPPLY_SORTRULE</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Service Binding for UI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>RAP: UI_RFM_SUPPLY_SORTRULE generated at 20190314</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -30587,19 +30633,19 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H458" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>UserToExplicitAsstmtMdl</t>
+          <t>ArunStockSortDynAttrib, ARunSupplySortRule, ArunStockSortStaticAttrib, ArunStockSortStaticAtribVal</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>/sap/opu/odata/sap/UI_RFM_SUPPLY_SORTRULE</t>
         </is>
       </c>
     </row>
@@ -30609,22 +30655,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>SD - Sales</t>
+          <t>Retail (RFM)</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>FINS_TRR_PECRUN_SALES_SRV</t>
+          <t>UI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>ZFINS_TRR_PECRUN_SALES_SRV</t>
+          <t>ZUI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Odata service for Manage Revenue Recognition - sales</t>
+          <t>Service Binding for UI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -30636,16 +30682,16 @@
         <v>1</v>
       </c>
       <c r="H459" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>ErrorNumberCollection</t>
+          <t>UserToExplicitAsstmtMdl</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FINS_TRR_PECRUN_SALES_SRV</t>
+          <t>/sap/opu/odata/sap/UI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
     </row>
@@ -30660,17 +30706,17 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>LORD_ODATA_ORDER_SRV</t>
+          <t>FINS_TRR_PECRUN_SALES_SRV</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>LORD_ODATA_ORDER_SRV</t>
+          <t>ZFINS_TRR_PECRUN_SALES_SRV</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>OData Service for Sales Order</t>
+          <t>Odata service for Manage Revenue Recognition - sales</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -30682,16 +30728,16 @@
         <v>1</v>
       </c>
       <c r="H460" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>HeaderSet</t>
+          <t>ErrorNumberCollection</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LORD_ODATA_ORDER_SRV</t>
+          <t>/sap/opu/odata/sap/FINS_TRR_PECRUN_SALES_SRV</t>
         </is>
       </c>
     </row>
@@ -30706,17 +30752,17 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>SD_BIL_DOC_LIST_MANAGE_SRV</t>
+          <t>LORD_ODATA_ORDER_SRV</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>ZSD_BIL_DOC_LIST_MANAGE_SRV</t>
+          <t>LORD_ODATA_ORDER_SRV</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Manage billing documents lists / invoice lists</t>
+          <t>OData Service for Sales Order</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -30728,16 +30774,16 @@
         <v>1</v>
       </c>
       <c r="H461" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>dummyCollection</t>
+          <t>HeaderSet</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_BIL_DOC_LIST_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/LORD_ODATA_ORDER_SRV</t>
         </is>
       </c>
     </row>
@@ -30752,17 +30798,17 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SD_CRT_PROCFLOW_SRV</t>
+          <t>SD_BIL_DOC_LIST_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>ZSD_CRT_PROCFLOW_SRV</t>
+          <t>ZSD_BIL_DOC_LIST_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>SD Process Flow for Customer Return</t>
+          <t>Manage billing documents lists / invoice lists</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -30774,16 +30820,16 @@
         <v>1</v>
       </c>
       <c r="H462" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>C_InhRepairObjPg</t>
+          <t>dummyCollection</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_CRT_PROCFLOW_SRV</t>
+          <t>/sap/opu/odata/sap/SD_BIL_DOC_LIST_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30798,17 +30844,17 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>SD_CUSTOMER_INVOICES_MANAGE</t>
+          <t>SD_CRT_PROCFLOW_SRV</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>ZSD_CUSTOMER_INVOICES_MANAGE</t>
+          <t>ZSD_CRT_PROCFLOW_SRV</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Manage Customer Invoices</t>
+          <t>SD Process Flow for Customer Return</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -30817,19 +30863,19 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H463" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_InhRepairObjPg</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_CUSTOMER_INVOICES_MANAGE</t>
+          <t>/sap/opu/odata/sap/SD_CRT_PROCFLOW_SRV</t>
         </is>
       </c>
     </row>
@@ -30844,17 +30890,17 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>SD_F1814_SO_FS_SRV</t>
+          <t>SD_CUSTOMER_INVOICES_MANAGE</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>ZSD_F1814_SO_FS_SRV</t>
+          <t>ZSD_CUSTOMER_INVOICES_MANAGE</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Sales Orders FactSheets - S4H SD FIORI</t>
+          <t>Manage Customer Invoices</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -30866,7 +30912,7 @@
         <v>3</v>
       </c>
       <c r="H464" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -30875,7 +30921,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F1814_SO_FS_SRV</t>
+          <t>/sap/opu/odata/sap/SD_CUSTOMER_INVOICES_MANAGE</t>
         </is>
       </c>
     </row>
@@ -30890,17 +30936,17 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>SD_F1871_QUOT_FS_SRV</t>
+          <t>SD_F1814_SO_FS_SRV</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>ZSD_F1871_QUOT_FS_SRV</t>
+          <t>ZSD_F1814_SO_FS_SRV</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Quotation FactSheet - S4H SD FIORI</t>
+          <t>Sales Orders FactSheets - S4H SD FIORI</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -30921,7 +30967,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F1871_QUOT_FS_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F1814_SO_FS_SRV</t>
         </is>
       </c>
     </row>
@@ -30936,17 +30982,17 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>SD_F1873_SO_WL_SRV</t>
+          <t>SD_F1871_QUOT_FS_SRV</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>SD_F1873_SO_WL_SRV</t>
+          <t>ZSD_F1871_QUOT_FS_SRV</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Odata for Work list for Sales Order</t>
+          <t>Quotation FactSheet - S4H SD FIORI</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -30955,19 +31001,19 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H466" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>C_SalesOrderWl_F1873</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F1873_SO_WL_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F1871_QUOT_FS_SRV</t>
         </is>
       </c>
     </row>
@@ -30982,17 +31028,17 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>SD_F2187_CUST360_SRV</t>
+          <t>SD_F1873_SO_WL_SRV</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>ZSD_F2187_CUST360_SRV</t>
+          <t>SD_F1873_SO_WL_SRV</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Customer 360</t>
+          <t>Odata for Work list for Sales Order</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -31004,7 +31050,7 @@
         <v>1</v>
       </c>
       <c r="H467" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -31013,7 +31059,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2187_CUST360_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F1873_SO_WL_SRV</t>
         </is>
       </c>
     </row>
@@ -31028,17 +31074,17 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SD_F2499_CUSTOMER_MATERIAL_SRV</t>
+          <t>SD_F2187_CUST360_SRV</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>ZSD_F2499_CUSTOMER_MATERIAL_SRV</t>
+          <t>ZSD_F2187_CUST360_SRV</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Customer Material</t>
+          <t>Customer 360</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -31047,19 +31093,19 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H468" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>C_AdditionalCustomerMaterialTP, C_CustMatlAddrDepdntInfoTP, C_CustomerMaterialLongTextTP, C_CustomerMaterial_F2499, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_SalesOrderWl_F1873</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2499_CUSTOMER_MATERIAL_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2187_CUST360_SRV</t>
         </is>
       </c>
     </row>
@@ -31074,17 +31120,17 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>SD_F2583_SLSITMPRPSL_SRV</t>
+          <t>SD_F2499_CUSTOMER_MATERIAL_SRV</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>ZSD_F2583_SLSITMPRPSL_SRV</t>
+          <t>ZSD_F2499_CUSTOMER_MATERIAL_SRV</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>OData Service for Sales Item Proposals</t>
+          <t>Customer Material</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -31093,19 +31139,19 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H469" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>C_SalesItemProposalItemTP, C_SalesItemProposalTP</t>
+          <t>C_AdditionalCustomerMaterialTP, C_CustMatlAddrDepdntInfoTP, C_CustomerMaterialLongTextTP, C_CustomerMaterial_F2499, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2583_SLSITMPRPSL_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2499_CUSTOMER_MATERIAL_SRV</t>
         </is>
       </c>
     </row>
@@ -31120,17 +31166,17 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>SD_F2650_CRT_EDIT_SRV</t>
+          <t>SD_F2583_SLSITMPRPSL_SRV</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>ZSD_F2650_CRT_EDIT_SRV</t>
+          <t>ZSD_F2583_SLSITMPRPSL_SRV</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>OData for Customer Returns Edit</t>
+          <t>OData Service for Sales Item Proposals</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -31139,19 +31185,19 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H470" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg, C_CustomerReturnSerialNumber</t>
+          <t>C_SalesItemProposalItemTP, C_SalesItemProposalTP</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2650_CRT_EDIT_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2583_SLSITMPRPSL_SRV</t>
         </is>
       </c>
     </row>
@@ -31166,17 +31212,17 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>SD_F2651_CRT_CREATE_SRV</t>
+          <t>SD_F2650_CRT_EDIT_SRV</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>ZSD_F2651_CRT_CREATE_SRV</t>
+          <t>ZSD_F2650_CRT_EDIT_SRV</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>OData for Create Customer Returns</t>
+          <t>OData for Customer Returns Edit</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -31185,19 +31231,19 @@
         </is>
       </c>
       <c r="G471" t="n">
+        <v>3</v>
+      </c>
+      <c r="H471" t="n">
         <v>2</v>
       </c>
-      <c r="H471" t="n">
-        <v>0</v>
-      </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg</t>
+          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg, C_CustomerReturnSerialNumber</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2651_CRT_CREATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2650_CRT_EDIT_SRV</t>
         </is>
       </c>
     </row>
@@ -31212,17 +31258,17 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SD_F2652_CRT_REFUND_SRV</t>
+          <t>SD_F2651_CRT_CREATE_SRV</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>ZSD_F2652_CRT_REFUND_SRV</t>
+          <t>ZSD_F2651_CRT_CREATE_SRV</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>OData for Customer Returns Refund</t>
+          <t>OData for Create Customer Returns</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -31243,7 +31289,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2652_CRT_REFUND_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2651_CRT_CREATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31258,17 +31304,17 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>SD_MANAGE_SADVTNPRFL</t>
+          <t>SD_F2652_CRT_REFUND_SRV</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>ZSD_MANAGE_SADVTNPRFL</t>
+          <t>ZSD_F2652_CRT_REFUND_SRV</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Manage Deviation Profile</t>
+          <t>OData for Customer Returns Refund</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -31277,19 +31323,19 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>C_SalesSchedgAgrmtDvtnPrflTP</t>
+          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MANAGE_SADVTNPRFL</t>
+          <t>/sap/opu/odata/sap/SD_F2652_CRT_REFUND_SRV</t>
         </is>
       </c>
     </row>
@@ -31304,17 +31350,17 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>SD_MCC_CCO_MASS_UPDATE_SRV</t>
+          <t>SD_MANAGE_SADVTNPRFL</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>ZSD_MCC_CCO_MASS_UPDATE_SRV</t>
+          <t>ZSD_MANAGE_SADVTNPRFL</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>OData for Mass Change Sales Contract</t>
+          <t>Manage Deviation Profile</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -31323,19 +31369,19 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>SlsDocReadReq, SlsDocReq</t>
+          <t>C_SalesSchedgAgrmtDvtnPrflTP</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_CCO_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MANAGE_SADVTNPRFL</t>
         </is>
       </c>
     </row>
@@ -31350,17 +31396,17 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>SD_MCC_CMR_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_CCO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>ZSD_MCC_CMR_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_CCO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Mass Change Credit Memo Request</t>
+          <t>OData for Mass Change Sales Contract</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -31381,7 +31427,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_CMR_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_CCO_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31396,17 +31442,17 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>SD_MCC_CR_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_CMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>ZSD_MCC_CR_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_CMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Mass change for Customer Return</t>
+          <t>Mass Change Credit Memo Request</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -31427,7 +31473,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_CR_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_CMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31442,17 +31488,17 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>SD_MCC_DMR_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_CR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>ZSD_MCC_DMR_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_CR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Debit Memo Requests OData Service</t>
+          <t>Mass change for Customer Return</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -31473,7 +31519,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_DMR_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_CR_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31488,17 +31534,17 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>SD_MCC_DOC_CAT_AUTH_SRV</t>
+          <t>SD_MCC_DMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>ZSD_MCC_DOC_CAT_AUTH_SRV</t>
+          <t>ZSD_MCC_DMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Authorization for Document Categories in Mass Change Cockpit</t>
+          <t>Debit Memo Requests OData Service</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -31507,19 +31553,19 @@
         </is>
       </c>
       <c r="G478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>DocCategoryAuthSet</t>
+          <t>SlsDocReadReq, SlsDocReq</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_DOC_CAT_AUTH_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_DMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31534,17 +31580,17 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>SD_MCC_SCH_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_DOC_CAT_AUTH_SRV</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SCH_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_DOC_CAT_AUTH_SRV</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Sales Order Scheduling Agreement</t>
+          <t>Authorization for Document Categories in Mass Change Cockpit</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -31553,19 +31599,19 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>SlsDocReadReq, SlsDocReq</t>
+          <t>DocCategoryAuthSet</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SCH_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_DOC_CAT_AUTH_SRV</t>
         </is>
       </c>
     </row>
@@ -31580,17 +31626,17 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>SD_MCC_SD_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SCH_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SD_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SCH_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Mass Change of Sales Document</t>
+          <t>Sales Order Scheduling Agreement</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -31611,7 +31657,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SD_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SCH_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31626,17 +31672,17 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>SD_MCC_SOW_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SD_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SOW_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SD_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Sales Order Without Charge</t>
+          <t>Mass Change of Sales Document</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -31657,7 +31703,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SOW_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SD_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31672,17 +31718,17 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>SD_MCC_SO_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SOW_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SO_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SOW_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Change cockpit for mass update sales order</t>
+          <t>Sales Order Without Charge</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -31703,7 +31749,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SO_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SOW_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31718,17 +31764,17 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>SD_MCC_SQ_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SQ_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Mass Change Sales Quotations</t>
+          <t>Change cockpit for mass update sales order</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -31749,7 +31795,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SQ_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SO_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31764,17 +31810,17 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>SD_SALESPLAN</t>
+          <t>SD_MCC_SQ_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>ZSD_SALESPLAN</t>
+          <t>ZSD_MCC_SQ_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Odata Service for C_SalesPlanTP</t>
+          <t>Mass Change Sales Quotations</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -31783,19 +31829,19 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H484" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>C_SalesPlanDimnSelectionTP, C_SalesPlanItemTP, C_SalesPlanTP</t>
+          <t>SlsDocReadReq, SlsDocReq</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALESPLAN</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SQ_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31810,17 +31856,17 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>SD_SALES_DOC_IMPORT</t>
+          <t>SD_SALESPLAN</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>ZSD_SALES_DOC_IMPORT</t>
+          <t>ZSD_SALESPLAN</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Import Sales Documents</t>
+          <t>Odata Service for C_SalesPlanTP</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -31829,19 +31875,19 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H485" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>SetAsCompletedReturnMessageCollection</t>
+          <t>C_SalesPlanDimnSelectionTP, C_SalesPlanItemTP, C_SalesPlanTP</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_DOC_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALESPLAN</t>
         </is>
       </c>
     </row>
@@ -31856,17 +31902,17 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>SD_SALES_ORDER_FOC_IMPORT</t>
+          <t>SD_SALES_DOC_IMPORT</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>ZSD_SALES_ORDER_FOC_IMPORT</t>
+          <t>ZSD_SALES_DOC_IMPORT</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Import Sales Orders Without Charge</t>
+          <t>Import Sales Documents</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -31875,19 +31921,19 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H486" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
+          <t>SetAsCompletedReturnMessageCollection</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_ORDER_FOC_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_DOC_IMPORT</t>
         </is>
       </c>
     </row>
@@ -31902,17 +31948,17 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>SD_SALES_ORDER_IMPORT</t>
+          <t>SD_SALES_ORDER_FOC_IMPORT</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>ZSD_SALES_ORDER_IMPORT</t>
+          <t>ZSD_SALES_ORDER_FOC_IMPORT</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Import Sales Order Service Project</t>
+          <t>Import Sales Orders Without Charge</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -31928,12 +31974,12 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
+          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_ORDER_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_ORDER_FOC_IMPORT</t>
         </is>
       </c>
     </row>
@@ -31948,17 +31994,17 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>SD_SALES_QTN_IMPORT</t>
+          <t>SD_SALES_ORDER_IMPORT</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>ZSD_SALES_QTN_IMPORT</t>
+          <t>ZSD_SALES_ORDER_IMPORT</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Import Sales Quotations</t>
+          <t>Import Sales Order Service Project</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -31974,12 +32020,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
+          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_QTN_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_ORDER_IMPORT</t>
         </is>
       </c>
     </row>
@@ -31994,17 +32040,17 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>SD_SALES_SA_IMPORT</t>
+          <t>SD_SALES_QTN_IMPORT</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>ZSD_SALES_SA_IMPORT</t>
+          <t>ZSD_SALES_QTN_IMPORT</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Import Sales Scheduling Agreements</t>
+          <t>Import Sales Quotations</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -32020,12 +32066,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
+          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_SA_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_QTN_IMPORT</t>
         </is>
       </c>
     </row>
@@ -32040,17 +32086,17 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>SD_SA_EDIPROCGOPTN_WL</t>
+          <t>SD_SALES_SA_IMPORT</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>ZSD_SA_EDIPROCGOPTN_WL</t>
+          <t>ZSD_SALES_SA_IMPORT</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Manage EDI Processing Options</t>
+          <t>Import Sales Scheduling Agreements</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -32059,19 +32105,19 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H490" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>C_DelivSchedEDIProcgOptnTP</t>
+          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SA_EDIPROCGOPTN_WL</t>
+          <t>/sap/opu/odata/sap/SD_SALES_SA_IMPORT</t>
         </is>
       </c>
     </row>
@@ -32086,17 +32132,17 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>SD_SA_SOLDTOPARTYDETN_WL</t>
+          <t>SD_SA_EDIPROCGOPTN_WL</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>ZSD_SA_SOLDTOPARTYDETN_WL</t>
+          <t>ZSD_SA_EDIPROCGOPTN_WL</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Assign Sold-to Parties for Delivery Schedules</t>
+          <t>Manage EDI Processing Options</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -32112,12 +32158,12 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>C_DelivSchedSoldToPartyDetnTP</t>
+          <t>C_DelivSchedEDIProcgOptnTP</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SA_SOLDTOPARTYDETN_WL</t>
+          <t>/sap/opu/odata/sap/SD_SA_EDIPROCGOPTN_WL</t>
         </is>
       </c>
     </row>
@@ -32132,17 +32178,17 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>SD_SOF</t>
+          <t>SD_SA_SOLDTOPARTYDETN_WL</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>ZSD_SOF</t>
+          <t>ZSD_SA_SOLDTOPARTYDETN_WL</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Sales Order Fulfillment Reuse Component</t>
+          <t>Assign Sold-to Parties for Delivery Schedules</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -32158,12 +32204,12 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>C_DelivSchedSoldToPartyDetnTP</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SOF</t>
+          <t>/sap/opu/odata/sap/SD_SA_SOLDTOPARTYDETN_WL</t>
         </is>
       </c>
     </row>
@@ -32178,17 +32224,17 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
+          <t>SD_SOF</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
+          <t>ZSD_SOF</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Resolve Credit Block in Sales Orders</t>
+          <t>Sales Order Fulfillment Reuse Component</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -32197,19 +32243,19 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H493" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>SalesOrderCollection, DeliveryCollection</t>
+          <t>ItemCollection</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SOFM_CREDIT_BLOCK_SRV</t>
+          <t>/sap/opu/odata/sap/SD_SOF</t>
         </is>
       </c>
     </row>
@@ -32224,17 +32270,17 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>UI_CUSTOMER_CONTACT_MANAGE</t>
+          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>ZUI_CUSTOMER_CONTACT_MANAGE</t>
+          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Manage Customer Contacts</t>
+          <t>Resolve Credit Block in Sales Orders</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -32246,16 +32292,16 @@
         <v>2</v>
       </c>
       <c r="H494" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>CustomerContactAttribute, CustomerContactRelation</t>
+          <t>SalesOrderCollection, DeliveryCollection</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_CUSTOMER_CONTACT_MANAGE</t>
+          <t>/sap/opu/odata/sap/SD_SOFM_CREDIT_BLOCK_SRV</t>
         </is>
       </c>
     </row>
@@ -32270,17 +32316,17 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>UI_MANAGEINHREPAIRS</t>
+          <t>UI_CUSTOMER_CONTACT_MANAGE</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>ZUI_MANAGEINHREPAIRS</t>
+          <t>ZUI_CUSTOMER_CONTACT_MANAGE</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>RAP: UI_MANAGEINHREPAIRS generated at 20190313</t>
+          <t>Manage Customer Contacts</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -32292,16 +32338,16 @@
         <v>2</v>
       </c>
       <c r="H495" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>C_InhRepairObjPg, C_InhRepairObjPgItem</t>
+          <t>CustomerContactAttribute, CustomerContactRelation</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_MANAGEINHREPAIRS</t>
+          <t>/sap/opu/odata/sap/UI_CUSTOMER_CONTACT_MANAGE</t>
         </is>
       </c>
     </row>
@@ -32316,43 +32362,89 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
+          <t>UI_MANAGEINHREPAIRS</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ZUI_MANAGEINHREPAIRS</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>RAP: UI_MANAGEINHREPAIRS generated at 20190313</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>2</v>
+      </c>
+      <c r="H496" t="n">
+        <v>11</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>C_InhRepairObjPg, C_InhRepairObjPgItem</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>/sap/opu/odata/sap/UI_MANAGEINHREPAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>SD - Sales</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
           <t>UI_RETURNPROCESSING</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr">
+      <c r="D497" t="inlineStr">
         <is>
           <t>ZUI_RETURNPROCESSING</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr">
+      <c r="E497" t="inlineStr">
         <is>
           <t>Return Processing Service</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>Fiori app service</t>
-        </is>
-      </c>
-      <c r="G496" t="n">
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
         <v>3</v>
       </c>
-      <c r="H496" t="n">
+      <c r="H497" t="n">
         <v>34</v>
       </c>
-      <c r="I496" t="inlineStr">
+      <c r="I497" t="inlineStr">
         <is>
           <t>CtnItem, RcvdPackggItem, RcvdPackggInCtn</t>
         </is>
       </c>
-      <c r="J496" t="inlineStr">
+      <c r="J497" t="inlineStr">
         <is>
           <t>/sap/opu/odata/sap/UI_RETURNPROCESSING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J496"/>
+  <autoFilter ref="A1:J497"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/creatable-services.xlsx
+++ b/creatable-services.xlsx
@@ -30,7 +30,7 @@
     <sheet name="SD - Sales" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$J$497</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All'!$A$1:$J$498</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ATP - Availability'!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Basis - Fiori - Technical'!$A$1:$J$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CO - Controlling'!$A$1:$J$31</definedName>
@@ -39,7 +39,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'EWM - Warehouse'!$A$1:$J$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'FI - Finance'!$A$1:$J$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'HR - Payroll - Travel'!$A$1:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'LE - Shipping'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'LE - Shipping'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Legal - Trade - Compliance'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'MM - Inventory'!$A$1:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'MM - Purchasing'!$A$1:$J$46</definedName>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
     </row>
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1383,38 +1383,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LE_SHP_QC_DLVNOREF_SRV</t>
+          <t>API_PACKINGINSTRUCTION</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ZLE_SHP_QC_DLVNOREF_SRV</t>
+          <t>API_PACKINGINSTRUCTION</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quick Create: Delivery without ref</t>
+          <t>Packing Instruction API</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiori app service</t>
+          <t>Released API</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C_DelivItmWthoutRefQuickCrte, C_DelivWthoutRefQuickCreate</t>
+          <t>PackingInstructionHeader</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVNOREF_SRV</t>
+          <t>/sap/opu/odata/sap/API_PACKINGINSTRUCTION</t>
         </is>
       </c>
     </row>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LE_SHP_QC_DLVREF_SRV</t>
+          <t>LE_SHP_QC_DLVNOREF_SRV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ZLE_SHP_QC_DLVREF_SRV</t>
+          <t>ZLE_SHP_QC_DLVNOREF_SRV</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quick Create: Delivery with ref.</t>
+          <t>Quick Create: Delivery without ref</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1448,19 +1448,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C_DelivWthRefQuickCreate</t>
+          <t>C_DelivItmWthoutRefQuickCrte, C_DelivWthoutRefQuickCreate</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVREF_SRV</t>
+          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVNOREF_SRV</t>
         </is>
       </c>
     </row>
@@ -1475,17 +1475,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UI_SHIPMENTCONTAINER</t>
+          <t>LE_SHP_QC_DLVREF_SRV</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ZUI_SHIPMENTCONTAINER</t>
+          <t>ZLE_SHP_QC_DLVREF_SRV</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shipment container service binding</t>
+          <t>Quick Create: Delivery with ref.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Container, Packaging, Certificate</t>
+          <t>C_DelivWthRefQuickCreate</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINER</t>
+          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVREF_SRV</t>
         </is>
       </c>
     </row>
@@ -1521,43 +1521,89 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>UI_SHIPMENTCONTAINER</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ZUI_SHIPMENTCONTAINER</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Shipment container service binding</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Container, Packaging, Certificate</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LE - Shipping</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>UI_SHIPMENTCONTAINERPACKG</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>ZUI_SHIPMENTCONTAINERPACKG</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Shipment Container Packing</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fiori app service</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>7</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>39</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>C_FieldLogisticsKitItemTP, C_FldLogsShptCtnUnitTP, C_FldLogsShptItemsTP, C_FldLogsShptPackggItemTP, C_FldLogsShptPackggUnitTP, C_FldLogsShptStageAssgmtCtnTP, C_FldLogsShptStgeAssgPackggTP</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINERPACKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9514,7 +9560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J497"/>
+  <dimension ref="A1:J498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22886,38 +22932,38 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LE_SHP_QC_DLVNOREF_SRV</t>
+          <t>API_PACKINGINSTRUCTION</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ZLE_SHP_QC_DLVNOREF_SRV</t>
+          <t>API_PACKINGINSTRUCTION</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Quick Create: Delivery without ref</t>
+          <t>Packing Instruction API</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Fiori app service</t>
+          <t>Released API</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>C_DelivItmWthoutRefQuickCrte, C_DelivWthoutRefQuickCreate</t>
+          <t>PackingInstructionHeader</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVNOREF_SRV</t>
+          <t>/sap/opu/odata/sap/API_PACKINGINSTRUCTION</t>
         </is>
       </c>
     </row>
@@ -22932,17 +22978,17 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>LE_SHP_QC_DLVREF_SRV</t>
+          <t>LE_SHP_QC_DLVNOREF_SRV</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ZLE_SHP_QC_DLVREF_SRV</t>
+          <t>ZLE_SHP_QC_DLVNOREF_SRV</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Quick Create: Delivery with ref.</t>
+          <t>Quick Create: Delivery without ref</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -22951,19 +22997,19 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>C_DelivWthRefQuickCreate</t>
+          <t>C_DelivItmWthoutRefQuickCrte, C_DelivWthoutRefQuickCreate</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVREF_SRV</t>
+          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVNOREF_SRV</t>
         </is>
       </c>
     </row>
@@ -22978,17 +23024,17 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>UI_SHIPMENTCONTAINER</t>
+          <t>LE_SHP_QC_DLVREF_SRV</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ZUI_SHIPMENTCONTAINER</t>
+          <t>ZLE_SHP_QC_DLVREF_SRV</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Shipment container service binding</t>
+          <t>Quick Create: Delivery with ref.</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -22997,19 +23043,19 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Container, Packaging, Certificate</t>
+          <t>C_DelivWthRefQuickCreate</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINER</t>
+          <t>/sap/opu/odata/sap/LE_SHP_QC_DLVREF_SRV</t>
         </is>
       </c>
     </row>
@@ -23024,17 +23070,17 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>UI_SHIPMENTCONTAINERPACKG</t>
+          <t>UI_SHIPMENTCONTAINER</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ZUI_SHIPMENTCONTAINERPACKG</t>
+          <t>ZUI_SHIPMENTCONTAINER</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Shipment Container Packing</t>
+          <t>Shipment container service binding</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -23043,19 +23089,19 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H294" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>C_FieldLogisticsKitItemTP, C_FldLogsShptCtnUnitTP, C_FldLogsShptItemsTP, C_FldLogsShptPackggItemTP, C_FldLogsShptPackggUnitTP, C_FldLogsShptStageAssgmtCtnTP, C_FldLogsShptStgeAssgPackggTP</t>
+          <t>Container, Packaging, Certificate</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINERPACKG</t>
+          <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINER</t>
         </is>
       </c>
     </row>
@@ -23065,22 +23111,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Legal - Trade - Compliance</t>
+          <t>LE - Shipping</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>LCM_CONTENT_REQUEST</t>
+          <t>UI_SHIPMENTCONTAINERPACKG</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ZLCM_CONTENT_REQUEST</t>
+          <t>ZUI_SHIPMENTCONTAINERPACKG</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Legal Transaction Management Content Request</t>
+          <t>Shipment Container Packing</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -23089,19 +23135,19 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H295" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>LglCntntMStepSequenceCollection, LglCntntMActiveLglTransUUIDCollection, LglCntntMActivateAttachDocCollection, LglCntntMDatePeriodCollection, LglCntntMCrCrteDocumentCollection, LinkedObjDescrCollection, LglCntntMAreaCodeValidationCollection, LglCntntMTechEntTypeCollection, C_LCMContextTP, C_LegalContentRequest, C_LegalTransactionCategory, C_LegalTransactionDate, C_LegalTransactionEntity, C_LegalTransactionExtContact, C_LegalTransactionIntContact, C_LegalTrLinkedObjects, C_LegalTrRelationShip, C_LglTransParentCategory, C_LglTransReqLglCntntDoc</t>
+          <t>C_FieldLogisticsKitItemTP, C_FldLogsShptCtnUnitTP, C_FldLogsShptItemsTP, C_FldLogsShptPackggItemTP, C_FldLogsShptPackggUnitTP, C_FldLogsShptStageAssgmtCtnTP, C_FldLogsShptStgeAssgPackggTP</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LCM_CONTENT_REQUEST</t>
+          <t>/sap/opu/odata/sap/UI_SHIPMENTCONTAINERPACKG</t>
         </is>
       </c>
     </row>
@@ -23116,17 +23162,17 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>LCM_CONTEXT_MANAGE_SRV</t>
+          <t>LCM_CONTENT_REQUEST</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ZLCM_CONTEXT_MANAGE_SRV</t>
+          <t>ZLCM_CONTENT_REQUEST</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Context Manage</t>
+          <t>Legal Transaction Management Content Request</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -23135,19 +23181,19 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H296" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>LglCntntMTechEntTypeCollection, LglCntntMIsCrtnAllowedCollection, C_LCMContextTP</t>
+          <t>LglCntntMStepSequenceCollection, LglCntntMActiveLglTransUUIDCollection, LglCntntMActivateAttachDocCollection, LglCntntMDatePeriodCollection, LglCntntMCrCrteDocumentCollection, LinkedObjDescrCollection, LglCntntMAreaCodeValidationCollection, LglCntntMTechEntTypeCollection, C_LCMContextTP, C_LegalContentRequest, C_LegalTransactionCategory, C_LegalTransactionDate, C_LegalTransactionEntity, C_LegalTransactionExtContact, C_LegalTransactionIntContact, C_LegalTrLinkedObjects, C_LegalTrRelationShip, C_LglTransParentCategory, C_LglTransReqLglCntntDoc</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LCM_CONTEXT_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/LCM_CONTENT_REQUEST</t>
         </is>
       </c>
     </row>
@@ -23162,17 +23208,17 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>LCM_DOCUMENT_MANAGE</t>
+          <t>LCM_CONTEXT_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ZLCM_DOCUMENT_MANAGE</t>
+          <t>ZLCM_CONTEXT_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Manage Legal Content Documents</t>
+          <t>Context Manage</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -23181,19 +23227,19 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H297" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>C_LglCntntMDocAgreementTP, C_LglCntntMDocCategoryTP, C_LglCntntMDocOblgnEntityTP, C_LglCntntMDocOblgnRcpntTP, C_LglCntntMDocOblgnRemTP, C_LglCntntMDocObligationTP, C_LglCntntMDocParCategoryTP, C_LglCntntMDocStatusChgsTP, C_LglCntntMDocTemplateInfoTP, C_LglCntntMDocumentStampTP</t>
+          <t>LglCntntMTechEntTypeCollection, LglCntntMIsCrtnAllowedCollection, C_LCMContextTP</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LCM_DOCUMENT_MANAGE</t>
+          <t>/sap/opu/odata/sap/LCM_CONTEXT_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -23208,17 +23254,17 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>LCM_LEGALTR_MANAGE</t>
+          <t>LCM_DOCUMENT_MANAGE</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LCM_LEGALTR_MANAGE</t>
+          <t>ZLCM_DOCUMENT_MANAGE</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Manage Legal Transaction</t>
+          <t>Manage Legal Content Documents</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -23227,19 +23273,19 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H298" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>LglCntntMDocMarkedForSendCollection, LglCntntMDatePeriodCollection, LglTransWrkFlwModCollection, LglCntntMTechEntTypeCollection, LglCntntMTaskCollection, C_LegalTransactionCategoryTP, C_LegalTransactionDateTP, C_LegalTransactionDocLinkTP, C_LegalTransactionEntityTP, C_LegalTransactionExtContactTP, C_LegalTransactionIntContactTP, C_LegalTransactionReminderTP, C_LegalTransRnwlAndTermnTP, C_LegalTrLinkedObjectsTP, C_LegalTrParentCategoryTP, C_LegalTrRelationshipTP, C_LglCntntMTaskGroupTP</t>
+          <t>C_LglCntntMDocAgreementTP, C_LglCntntMDocCategoryTP, C_LglCntntMDocOblgnEntityTP, C_LglCntntMDocOblgnRcpntTP, C_LglCntntMDocOblgnRemTP, C_LglCntntMDocObligationTP, C_LglCntntMDocParCategoryTP, C_LglCntntMDocStatusChgsTP, C_LglCntntMDocTemplateInfoTP, C_LglCntntMDocumentStampTP</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LCM_LEGALTR_MANAGE</t>
+          <t>/sap/opu/odata/sap/LCM_DOCUMENT_MANAGE</t>
         </is>
       </c>
     </row>
@@ -23254,17 +23300,17 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>LCM_TASK_MANAGE</t>
+          <t>LCM_LEGALTR_MANAGE</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ZLCM_TASK_MANAGE</t>
+          <t>LCM_LEGALTR_MANAGE</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Manage LCM Tasks</t>
+          <t>Manage Legal Transaction</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -23273,19 +23319,19 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H299" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>SuccessCollection, C_LglCntntMManageTask</t>
+          <t>LglCntntMDocMarkedForSendCollection, LglCntntMDatePeriodCollection, LglTransWrkFlwModCollection, LglCntntMTechEntTypeCollection, LglCntntMTaskCollection, C_LegalTransactionCategoryTP, C_LegalTransactionDateTP, C_LegalTransactionDocLinkTP, C_LegalTransactionEntityTP, C_LegalTransactionExtContactTP, C_LegalTransactionIntContactTP, C_LegalTransactionReminderTP, C_LegalTransRnwlAndTermnTP, C_LegalTrLinkedObjectsTP, C_LegalTrParentCategoryTP, C_LegalTrRelationshipTP, C_LglCntntMTaskGroupTP</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LCM_TASK_MANAGE</t>
+          <t>/sap/opu/odata/sap/LCM_LEGALTR_MANAGE</t>
         </is>
       </c>
     </row>
@@ -23300,17 +23346,17 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>SLL_CTRLCL_MANAGE</t>
+          <t>LCM_TASK_MANAGE</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>SLL_CTRLCL_MANAGE</t>
+          <t>ZLCM_TASK_MANAGE</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Manage Control Classes</t>
+          <t>Manage LCM Tasks</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -23319,19 +23365,19 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>C_ControlClassByLanguage</t>
+          <t>SuccessCollection, C_LglCntntMManageTask</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SLL_CTRLCL_MANAGE</t>
+          <t>/sap/opu/odata/sap/LCM_TASK_MANAGE</t>
         </is>
       </c>
     </row>
@@ -23341,43 +23387,43 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MM - Inventory</t>
+          <t>Legal - Trade - Compliance</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>API_MATERIAL_DOCUMENT_SRV</t>
+          <t>SLL_CTRLCL_MANAGE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>API_MATERIAL_DOCUMENT_SRV</t>
+          <t>SLL_CTRLCL_MANAGE</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>OData Service for Material Document API</t>
+          <t>Manage Control Classes</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Released API</t>
+          <t>Fiori app service</t>
         </is>
       </c>
       <c r="G301" t="n">
         <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>A_MaterialDocumentHeader</t>
+          <t>C_ControlClassByLanguage</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/API_MATERIAL_DOCUMENT_SRV</t>
+          <t>/sap/opu/odata/sap/SLL_CTRLCL_MANAGE</t>
         </is>
       </c>
     </row>
@@ -23392,38 +23438,38 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LO_BM_BATCH_SRV</t>
+          <t>API_MATERIAL_DOCUMENT_SRV</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LO_BM_BATCH_SRV</t>
+          <t>API_MATERIAL_DOCUMENT_SRV</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Batch: Object Page, List Report</t>
+          <t>OData Service for Material Document API</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Fiori app service</t>
+          <t>Released API</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H302" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>C_BatchTP, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>A_MaterialDocumentHeader</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_BM_BATCH_SRV</t>
+          <t>/sap/opu/odata/sap/API_MATERIAL_DOCUMENT_SRV</t>
         </is>
       </c>
     </row>
@@ -23438,17 +23484,17 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>MM_IM_PHYS_INV_MASS_CREATE_SRV_01</t>
+          <t>LO_BM_BATCH_SRV</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ZMM_IM_PHYS_INV_MASS_CREATE_SRV_01</t>
+          <t>LO_BM_BATCH_SRV</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>OData Service for Mass Creation UI</t>
+          <t>Batch: Object Page, List Report</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -23457,19 +23503,19 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>C_PhysInvtryDocItmCreate</t>
+          <t>C_BatchTP, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_IM_PHYS_INV_MASS_CREATE_SRV_01</t>
+          <t>/sap/opu/odata/sap/LO_BM_BATCH_SRV</t>
         </is>
       </c>
     </row>
@@ -23484,17 +23530,17 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>UI_PI_MANAGE_COUNT_V2</t>
+          <t>MM_IM_PHYS_INV_MASS_CREATE_SRV_01</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ZUI_PI_MANAGE_COUNT_V2</t>
+          <t>ZMM_IM_PHYS_INV_MASS_CREATE_SRV_01</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>OData V2 Ui Service for app manage PI count</t>
+          <t>OData Service for Mass Creation UI</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -23503,19 +23549,19 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H304" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>C_PhysInvtryDocItemMngCountTP, C_PhysInvtryDocManageCountTP, C_PInvCountSrlNmbrMngCountTP</t>
+          <t>C_PhysInvtryDocItmCreate</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_PI_MANAGE_COUNT_V2</t>
+          <t>/sap/opu/odata/sap/MM_IM_PHYS_INV_MASS_CREATE_SRV_01</t>
         </is>
       </c>
     </row>
@@ -23530,17 +23576,17 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>UI_RESERVATION_HDR_MNG_V2</t>
+          <t>UI_PI_MANAGE_COUNT_V2</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>UI_RESERVATION_HDR_MNG_V2</t>
+          <t>ZUI_PI_MANAGE_COUNT_V2</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Manage Manual Reservations Service</t>
+          <t>OData V2 Ui Service for app manage PI count</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -23549,19 +23595,19 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H305" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>C_ReservationDocItemTP_F4839</t>
+          <t>C_PhysInvtryDocItemMngCountTP, C_PhysInvtryDocManageCountTP, C_PInvCountSrlNmbrMngCountTP</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RESERVATION_HDR_MNG_V2</t>
+          <t>/sap/opu/odata/sap/UI_PI_MANAGE_COUNT_V2</t>
         </is>
       </c>
     </row>
@@ -23576,17 +23622,17 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>UI_STOCKREPPROC_O2</t>
+          <t>UI_RESERVATION_HDR_MNG_V2</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ZUI_STOCKREPPROC_O2</t>
+          <t>UI_RESERVATION_HDR_MNG_V2</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Manage Manual Reservations Service</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -23598,16 +23644,16 @@
         <v>1</v>
       </c>
       <c r="H306" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>C_MatlStockReportProcedureTP</t>
+          <t>C_ReservationDocItemTP_F4839</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_STOCKREPPROC_O2</t>
+          <t>/sap/opu/odata/sap/UI_RESERVATION_HDR_MNG_V2</t>
         </is>
       </c>
     </row>
@@ -23622,17 +23668,17 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>UI_STOCKREPSUBS_O2</t>
+          <t>UI_STOCKREPPROC_O2</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ZUI_STOCKREPSUBS_O2</t>
+          <t>ZUI_STOCKREPPROC_O2</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>UI_STOCKREPSUBS_O2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -23641,19 +23687,19 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H307" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>C_MatlStkSubscrpnHeaderTP, C_MatlStkSubscrpnItemTP</t>
+          <t>C_MatlStockReportProcedureTP</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_STOCKREPSUBS_O2</t>
+          <t>/sap/opu/odata/sap/UI_STOCKREPPROC_O2</t>
         </is>
       </c>
     </row>
@@ -23663,22 +23709,22 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MM - Purchasing</t>
+          <t>MM - Inventory</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>FAC_POAC_RVW_WF_SRV</t>
+          <t>UI_STOCKREPSUBS_O2</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ZFAC_POAC_RVW_WF_SRV</t>
+          <t>ZUI_STOCKREPSUBS_O2</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>oData Purchase Order Accruals for Review via WF</t>
+          <t>UI_STOCKREPSUBS_O2</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -23687,19 +23733,19 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H308" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>RVW_POAC_WRKFLW_CNDN_PARAM</t>
+          <t>C_MatlStkSubscrpnHeaderTP, C_MatlStkSubscrpnItemTP</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FAC_POAC_RVW_WF_SRV</t>
+          <t>/sap/opu/odata/sap/UI_STOCKREPSUBS_O2</t>
         </is>
       </c>
     </row>
@@ -23714,17 +23760,17 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>FAP_PAYMENT_POST_SRV</t>
+          <t>FAC_POAC_RVW_WF_SRV</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ZFAP_PAYMENT_POST_SRV</t>
+          <t>ZFAC_POAC_RVW_WF_SRV</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Post Outgoing Supplier Payment</t>
+          <t>oData Purchase Order Accruals for Review via WF</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -23733,19 +23779,19 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H309" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>FinsPostingAPARItems, FinsPostingPaymentDifferences, FinsPostingWithholdingTaxes, FinsPostingAPARItemsToBeClrd, Notes, FinsPostingGLItems, FinsPostingPartnerAndPaymentsData, VHLockboxNumberCollection, FinsPostingLBItemHeaders, FinsPostingPaymentAdviceSubItems, FinsPostingPaymentAdviceItems, C_FinPostingTemplate</t>
+          <t>RVW_POAC_WRKFLW_CNDN_PARAM</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FAP_PAYMENT_POST_SRV</t>
+          <t>/sap/opu/odata/sap/FAC_POAC_RVW_WF_SRV</t>
         </is>
       </c>
     </row>
@@ -23760,17 +23806,17 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>MATPLANTPURSOURCELIST_SRV</t>
+          <t>FAP_PAYMENT_POST_SRV</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ZMATPLANTPURSOURCELIST_SRV</t>
+          <t>ZFAP_PAYMENT_POST_SRV</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Maintain Source List Application</t>
+          <t>Post Outgoing Supplier Payment</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -23779,19 +23825,19 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H310" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>C_MPPurchasingSource, C_Mppurchasingsourceitem</t>
+          <t>FinsPostingAPARItems, FinsPostingPaymentDifferences, FinsPostingWithholdingTaxes, FinsPostingAPARItemsToBeClrd, Notes, FinsPostingGLItems, FinsPostingPartnerAndPaymentsData, VHLockboxNumberCollection, FinsPostingLBItemHeaders, FinsPostingPaymentAdviceSubItems, FinsPostingPaymentAdviceItems, C_FinPostingTemplate</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MATPLANTPURSOURCELIST_SRV</t>
+          <t>/sap/opu/odata/sap/FAP_PAYMENT_POST_SRV</t>
         </is>
       </c>
     </row>
@@ -23806,17 +23852,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>MMIM_GR4PO_DL_SRV</t>
+          <t>MATPLANTPURSOURCELIST_SRV</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>MMIM_GR4PO_DL_SRV</t>
+          <t>ZMATPLANTPURSOURCELIST_SRV</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>oData Service Goods receipt Purchase Order/Del.</t>
+          <t>Maintain Source List Application</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -23825,19 +23871,19 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H311" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>C_BatchTP, GR4PO_DL_Headers, GR4PO_DL_Items, GR4PO_DOC_Refs, GR4PO_DL_SubItems, GR4PO_DL_SerialNumbers, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_MPPurchasingSource, C_Mppurchasingsourceitem</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMIM_GR4PO_DL_SRV</t>
+          <t>/sap/opu/odata/sap/MATPLANTPURSOURCELIST_SRV</t>
         </is>
       </c>
     </row>
@@ -23852,17 +23898,17 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>MMPUR_AUTOMATION_PROCESS_SRV</t>
+          <t>MMIM_GR4PO_DL_SRV</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>ZMMPUR_AUTOMATION_PROCESS_SRV</t>
+          <t>MMIM_GR4PO_DL_SRV</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Automation Process</t>
+          <t>oData Service Goods receipt Purchase Order/Del.</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -23871,19 +23917,19 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H312" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>PRAutoRuleSet</t>
+          <t>C_BatchTP, GR4PO_DL_Headers, GR4PO_DL_Items, GR4PO_DOC_Refs, GR4PO_DL_SubItems, GR4PO_DL_SerialNumbers, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMPUR_AUTOMATION_PROCESS_SRV</t>
+          <t>/sap/opu/odata/sap/MMIM_GR4PO_DL_SRV</t>
         </is>
       </c>
     </row>
@@ -23898,17 +23944,17 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>MMPUR_REL_STRAT_CLASS_SRV</t>
+          <t>MMPUR_AUTOMATION_PROCESS_SRV</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ZMMPUR_REL_STRAT_CLASS_SRV</t>
+          <t>ZMMPUR_AUTOMATION_PROCESS_SRV</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Gateway project for Manage Class</t>
+          <t>Automation Process</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -23917,19 +23963,19 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H313" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>C_Relstratchar, C_Relstratclass, I_ReleaseStrategyCharClassTP, I_ReleaseStrategyClassTP</t>
+          <t>PRAutoRuleSet</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMPUR_REL_STRAT_CLASS_SRV</t>
+          <t>/sap/opu/odata/sap/MMPUR_AUTOMATION_PROCESS_SRV</t>
         </is>
       </c>
     </row>
@@ -23944,17 +23990,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>MMPUR_REQ_SSP_MAINTAIN_SRV</t>
+          <t>MMPUR_REL_STRAT_CLASS_SRV</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>MMPUR_REQ_SSP_MAINTAIN_SRV</t>
+          <t>ZMMPUR_REL_STRAT_CLASS_SRV</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>SSP Requisition</t>
+          <t>Gateway project for Manage Class</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -23963,19 +24009,19 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H314" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>DraftExistsCollection, GetIsScopedCollection, NAVIGATION_TARGETCollection, WorkflowScenarioDetailsCollection, C_Sspprmaint_Accassign, C_Sspprmaint_Hdr, C_Sspprmaint_Itm, C_Sspprmaint_Itmtext, I_Purchaserequisitionitem_Wd, I_Purchaserequisition_Wd</t>
+          <t>C_Relstratchar, C_Relstratclass, I_ReleaseStrategyCharClassTP, I_ReleaseStrategyClassTP</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMPUR_REQ_SSP_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MMPUR_REL_STRAT_CLASS_SRV</t>
         </is>
       </c>
     </row>
@@ -23990,17 +24036,17 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>MM_PRC_SEV_CONFIG</t>
+          <t>MMPUR_REQ_SSP_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ZMM_PRC_SEV_CONFIG</t>
+          <t>MMPUR_REQ_SSP_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Suplier Evaluation Weighting and Scoring</t>
+          <t>SSP Requisition</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -24009,19 +24055,19 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H315" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>C_SuplrEvalCriteria, C_SuplrEvaluationCriteria, C_SuplrEvaluationPctToScore</t>
+          <t>DraftExistsCollection, GetIsScopedCollection, NAVIGATION_TARGETCollection, WorkflowScenarioDetailsCollection, C_Sspprmaint_Accassign, C_Sspprmaint_Hdr, C_Sspprmaint_Itm, C_Sspprmaint_Itmtext, I_Purchaserequisitionitem_Wd, I_Purchaserequisition_Wd</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PRC_SEV_CONFIG</t>
+          <t>/sap/opu/odata/sap/MMPUR_REQ_SSP_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -24036,17 +24082,17 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>MM_PUR_ANA_SUPLR_SCOREOUTPUT_SRV</t>
+          <t>MM_PRC_SEV_CONFIG</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ZMM_PUR_ANA_SUPLR_SCOREOUTPUT_SRV</t>
+          <t>ZMM_PRC_SEV_CONFIG</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Supplier Score Output Management</t>
+          <t>Suplier Evaluation Weighting and Scoring</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -24058,16 +24104,16 @@
         <v>3</v>
       </c>
       <c r="H316" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>CurrencyCollection, ActiveScoresCollection, GUIDCollection</t>
+          <t>C_SuplrEvalCriteria, C_SuplrEvaluationCriteria, C_SuplrEvaluationPctToScore</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_ANA_SUPLR_SCOREOUTPUT_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PRC_SEV_CONFIG</t>
         </is>
       </c>
     </row>
@@ -24082,17 +24128,17 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>MM_PUR_CATALOGITEMS_MNG_SRV</t>
+          <t>MM_PUR_ANA_SUPLR_SCOREOUTPUT_SRV</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ZMM_PUR_CATALOGITEMS_MNG_SRV</t>
+          <t>ZMM_PUR_ANA_SUPLR_SCOREOUTPUT_SRV</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Manage Catalog Items</t>
+          <t>Supplier Score Output Management</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -24101,19 +24147,19 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H317" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>C_CatalogItemDescTP, C_CatalogItemMngTP</t>
+          <t>CurrencyCollection, ActiveScoresCollection, GUIDCollection</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CATALOGITEMS_MNG_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_ANA_SUPLR_SCOREOUTPUT_SRV</t>
         </is>
       </c>
     </row>
@@ -24128,17 +24174,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>MM_PUR_CNTRLCTRMASS_UPDT_SRV</t>
+          <t>MM_PUR_CATALOGITEMS_MNG_SRV</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>ZMM_PUR_CNTRLCTRMASS_UPDT_SRV</t>
+          <t>ZMM_PUR_CATALOGITEMS_MNG_SRV</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Mass Changes to Central Purchase Contracts</t>
+          <t>Manage Catalog Items</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -24147,19 +24193,19 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H318" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>C_CntrlPurContrHdrDistr, C_CntrlPurContrHierItmMassUpdt, C_CntrlPurContrHierMassUpdt, C_CntrlPurContrItmDistr, C_CPurConHierHdrDistrMassUpdt, C_CPurConHierItmDistrMassUpdt, C_PurCntrlContrItmMassUpdt, C_PurCntrlContrMassUpdt</t>
+          <t>C_CatalogItemDescTP, C_CatalogItemMngTP</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CNTRLCTRMASS_UPDT_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CATALOGITEMS_MNG_SRV</t>
         </is>
       </c>
     </row>
@@ -24174,17 +24220,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>MM_PUR_CNTRL_CTR_MAINTAIN_SRV</t>
+          <t>MM_PUR_CNTRLCTRMASS_UPDT_SRV</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>MM_PUR_CNTRL_CTR_MAINTAIN_SRV</t>
+          <t>ZMM_PUR_CNTRLCTRMASS_UPDT_SRV</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Manage Central Purchase Contracts</t>
+          <t>Mass Changes to Central Purchase Contracts</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -24193,19 +24239,19 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H319" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>MaterialExtrafieldsCollection, NavigationTargetCollection, RetriggerSrceListChangeCollection, C_CentralPurchaseContractTP, C_CntrlPurchaseContractItemTP, C_CntrlPurContrDistributionTP, C_CntrlPurContrHdrCndnAmount, C_CntrlPurContrHdrCndnScalesTP, C_CntrlPurContrHdrCndnValdty, C_CntrlPurContrHdrDistrAddrTP, C_CntrlPurContrHdrDistrTP, C_CntrlPurContrHdrPartnerTP, C_CntrlPurContrHierHdrDistrTP, C_CntrlPurContrHierHdrTP, C_CntrlPurContrHierItemDistrTP, C_CntrlPurContrHierItemTP, C_CntrlPurContrItemHierarchyTP, C_CntrlPurContrItemPartnerTP, C_CntrlPurContrItmCmmdtyQtyTP, C_CntrlPurContrItmCndnAmountTP, C_CntrlPurContrItmCndnScalesTP, C_CntrlPurContrItmCndnValdtyTP, C_CntrlPurContrItmDistrAddrTP, C_CPurConHierHdrCndnAmountTP, C_CPurConHierHdrCndnScalesTP, C_CPurConHierHdrCndnValdtyTP, C_CPurConHierItmCmmdtyQtyTP, C_CPurConHierItmCndnAmountTP, C_CPurConHierItmCndnScalesTP, C_CPurConHierItmCndnValdtyTP</t>
+          <t>C_CntrlPurContrHdrDistr, C_CntrlPurContrHierItmMassUpdt, C_CntrlPurContrHierMassUpdt, C_CntrlPurContrItmDistr, C_CPurConHierHdrDistrMassUpdt, C_CPurConHierItmDistrMassUpdt, C_PurCntrlContrItmMassUpdt, C_PurCntrlContrMassUpdt</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CNTRL_CTR_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CNTRLCTRMASS_UPDT_SRV</t>
         </is>
       </c>
     </row>
@@ -24220,17 +24266,17 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>MM_PUR_CQTN_MAINTAIN_SRV</t>
+          <t>MM_PUR_CNTRL_CTR_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ZMM_PUR_CQTN_MAINTAIN_SRV</t>
+          <t>MM_PUR_CNTRL_CTR_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Central Supplier Quotation</t>
+          <t>Manage Central Purchase Contracts</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -24239,19 +24285,19 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H320" t="n">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>HubScenarioStatusCollection, C_AddressTP, C_CentralSupplierQuotationTP, C_CntrlSuplrQtanItemPricingTP, C_CntrlSupplierQtanItemDistrTP, C_CntrlSupplierQuotationItemTP</t>
+          <t>MaterialExtrafieldsCollection, NavigationTargetCollection, RetriggerSrceListChangeCollection, C_CentralPurchaseContractTP, C_CntrlPurchaseContractItemTP, C_CntrlPurContrDistributionTP, C_CntrlPurContrHdrCndnAmount, C_CntrlPurContrHdrCndnScalesTP, C_CntrlPurContrHdrCndnValdty, C_CntrlPurContrHdrDistrAddrTP, C_CntrlPurContrHdrDistrTP, C_CntrlPurContrHdrPartnerTP, C_CntrlPurContrHierHdrDistrTP, C_CntrlPurContrHierHdrTP, C_CntrlPurContrHierItemDistrTP, C_CntrlPurContrHierItemTP, C_CntrlPurContrItemHierarchyTP, C_CntrlPurContrItemPartnerTP, C_CntrlPurContrItmCmmdtyQtyTP, C_CntrlPurContrItmCndnAmountTP, C_CntrlPurContrItmCndnScalesTP, C_CntrlPurContrItmCndnValdtyTP, C_CntrlPurContrItmDistrAddrTP, C_CPurConHierHdrCndnAmountTP, C_CPurConHierHdrCndnScalesTP, C_CPurConHierHdrCndnValdtyTP, C_CPurConHierItmCmmdtyQtyTP, C_CPurConHierItmCndnAmountTP, C_CPurConHierItmCndnScalesTP, C_CPurConHierItmCndnValdtyTP</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CQTN_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CNTRL_CTR_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -24266,17 +24312,17 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>MM_PUR_CREATE_FOD_FROM_CQTN_SRV</t>
+          <t>MM_PUR_CQTN_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ZMM_PUR_CREATE_FOD_FROM_CQTN_SRV</t>
+          <t>ZMM_PUR_CQTN_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Create purchase orders from central quotation</t>
+          <t>Central Supplier Quotation</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -24285,19 +24331,19 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H321" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>ReturnCollection, ResultCollection</t>
+          <t>HubScenarioStatusCollection, C_AddressTP, C_CentralSupplierQuotationTP, C_CntrlSuplrQtanItemPricingTP, C_CntrlSupplierQtanItemDistrTP, C_CntrlSupplierQuotationItemTP</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CREATE_FOD_FROM_CQTN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CQTN_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -24312,17 +24358,17 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>MM_PUR_CREATE_FOD_FROM_PR_SRV</t>
+          <t>MM_PUR_CREATE_FOD_FROM_CQTN_SRV</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ZMM_PUR_CREATE_FOD_FROM_PR_SRV</t>
+          <t>ZMM_PUR_CREATE_FOD_FROM_CQTN_SRV</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Create Follow on Document from the PR</t>
+          <t>Create purchase orders from central quotation</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -24331,19 +24377,19 @@
         </is>
       </c>
       <c r="G322" t="n">
+        <v>2</v>
+      </c>
+      <c r="H322" t="n">
         <v>3</v>
       </c>
-      <c r="H322" t="n">
-        <v>4</v>
-      </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>TargetDestinationCollection, ReturnCollection, ExpertModeCollection</t>
+          <t>ReturnCollection, ResultCollection</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CREATE_FOD_FROM_PR_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CREATE_FOD_FROM_CQTN_SRV</t>
         </is>
       </c>
     </row>
@@ -24358,17 +24404,17 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>MM_PUR_CRFQ_MAINTAIN_SRV</t>
+          <t>MM_PUR_CREATE_FOD_FROM_PR_SRV</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>MM_PUR_CRFQ_MAINTAIN_SRV</t>
+          <t>ZMM_PUR_CREATE_FOD_FROM_PR_SRV</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Central Request For Quotation</t>
+          <t>Create Follow on Document from the PR</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -24377,19 +24423,19 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H323" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>C_AddressTP, C_CentralReqForQuotationItemTP, C_CentralRequestForQuotationTP, C_CentralRFQItemDistributionTP, C_CntrlReqForQuotationBidderTP</t>
+          <t>TargetDestinationCollection, ReturnCollection, ExpertModeCollection</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CRFQ_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CREATE_FOD_FROM_PR_SRV</t>
         </is>
       </c>
     </row>
@@ -24404,17 +24450,17 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>MM_PUR_CTRMASS_UPDATE_SRV</t>
+          <t>MM_PUR_CRFQ_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ZMM_PUR_CTRMASS_UPDATE_SRV</t>
+          <t>MM_PUR_CRFQ_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Mass Changes to Purchase Contracts</t>
+          <t>Central Request For Quotation</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -24423,19 +24469,19 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H324" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>C_PurchaseContractMassUpdt, C_PurContractItemMassUpdt</t>
+          <t>C_AddressTP, C_CentralReqForQuotationItemTP, C_CentralRequestForQuotationTP, C_CentralRFQItemDistributionTP, C_CntrlReqForQuotationBidderTP</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_CTRMASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CRFQ_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -24450,17 +24496,17 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>MM_PUR_INFO_RECORDS_MANAGE_SRV</t>
+          <t>MM_PUR_CTRMASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>MM_PUR_INFO_RECORDS_MANAGE_SRV</t>
+          <t>ZMM_PUR_CTRMASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Manage Purchasing Info Records</t>
+          <t>Mass Changes to Purchase Contracts</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -24472,16 +24518,16 @@
         <v>2</v>
       </c>
       <c r="H325" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>C_PurInfCondPeriod, C_PurInfoRecordWithOrg</t>
+          <t>C_PurchaseContractMassUpdt, C_PurContractItemMassUpdt</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_INFO_RECORDS_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_CTRMASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -24496,17 +24542,17 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>MM_PUR_INFO_RECORD_UPDATE_SRV</t>
+          <t>MM_PUR_INFO_RECORDS_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>ZMM_PUR_INFO_RECORD_UPDATE_SRV</t>
+          <t>MM_PUR_INFO_RECORDS_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Mass Changes to Purchasing Info Records</t>
+          <t>Manage Purchasing Info Records</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -24518,16 +24564,16 @@
         <v>2</v>
       </c>
       <c r="H326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>C_PurgOrgLvlInfoRecdMassUpdt, C_PurInfoRecdPrcgCndn</t>
+          <t>C_PurInfCondPeriod, C_PurInfoRecordWithOrg</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_INFO_RECORD_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_INFO_RECORDS_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -24542,17 +24588,17 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>MM_PUR_MANAGE_BUS_AUTOMN_RULES_SRV</t>
+          <t>MM_PUR_INFO_RECORD_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ZMM_PUR_MANAGE_BUS_AUTOMN_RULES_SRV</t>
+          <t>ZMM_PUR_INFO_RECORD_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Manage Business rules for Process automation</t>
+          <t>Mass Changes to Purchasing Info Records</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -24561,19 +24607,19 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H327" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>C_ProcmtAutomnActionInputTP, C_ProcmtAutomnActionParamTP, C_ProcmtAutomnActionPreqtTP, C_ProcmtAutomnRuleActionTP, C_ProcmtAutomnRuleActivityTP, C_ProcmtAutomnRuleConncdSystTP, C_ProcmtAutomnRuleCriteriaTP, C_ProcmtAutomnRuleDefinitionTP</t>
+          <t>C_PurgOrgLvlInfoRecdMassUpdt, C_PurInfoRecdPrcgCndn</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_MANAGE_BUS_AUTOMN_RULES_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_INFO_RECORD_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -24588,17 +24634,17 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>MM_PUR_OA_MAINTAIN_SRV</t>
+          <t>MM_PUR_MANAGE_BUS_AUTOMN_RULES_SRV</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>MM_PUR_OA_MAINTAIN_SRV</t>
+          <t>ZMM_PUR_MANAGE_BUS_AUTOMN_RULES_SRV</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Maintain Outline Agreements</t>
+          <t>Manage Business rules for Process automation</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -24607,19 +24653,19 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H328" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>C_ContractMaintain, C_ContractMaintainItem, C_Contractnotes, C_PurchaseContrItemHierarchyTP, C_PurContrHdrCndnAmountTP, C_PurContrHdrCndnScaleTP, C_PurContrHdrCndnValdtyTP, C_PurContrItmCndnAmountTP, C_PurContrItmCndnScalesTP, C_PurContrItmCndnValdtyTP, C_Purctraccassign, C_PurCtrItemAddress, C_PurCtrItemnotes, C_PurCtrPartners</t>
+          <t>C_ProcmtAutomnActionInputTP, C_ProcmtAutomnActionParamTP, C_ProcmtAutomnActionPreqtTP, C_ProcmtAutomnRuleActionTP, C_ProcmtAutomnRuleActivityTP, C_ProcmtAutomnRuleConncdSystTP, C_ProcmtAutomnRuleCriteriaTP, C_ProcmtAutomnRuleDefinitionTP</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_OA_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_MANAGE_BUS_AUTOMN_RULES_SRV</t>
         </is>
       </c>
     </row>
@@ -24634,17 +24680,17 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>MM_PUR_OCI_SRV</t>
+          <t>MM_PUR_OA_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>ZMM_PUR_OCI_SRV</t>
+          <t>MM_PUR_OA_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>OCI reuse</t>
+          <t>Maintain Outline Agreements</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -24653,19 +24699,19 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H329" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>I_Proccatalogcalldetails</t>
+          <t>C_ContractMaintain, C_ContractMaintainItem, C_Contractnotes, C_PurchaseContrItemHierarchyTP, C_PurContrHdrCndnAmountTP, C_PurContrHdrCndnScaleTP, C_PurContrHdrCndnValdtyTP, C_PurContrItmCndnAmountTP, C_PurContrItmCndnScalesTP, C_PurContrItmCndnValdtyTP, C_Purctraccassign, C_PurCtrItemAddress, C_PurCtrItemnotes, C_PurCtrPartners</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_OCI_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_OA_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -24680,17 +24726,17 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>MM_PUR_POMASS_UPDATE_SRV</t>
+          <t>MM_PUR_OCI_SRV</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ZMM_PUR_POMASS_UPDATE_SRV</t>
+          <t>ZMM_PUR_OCI_SRV</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Service for Mass Update</t>
+          <t>OCI reuse</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -24699,19 +24745,19 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>C_PurchaseOrderItemMassUpdate, C_PurchaseOrderMassUpdate</t>
+          <t>I_Proccatalogcalldetails</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_POMASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_OCI_SRV</t>
         </is>
       </c>
     </row>
@@ -24726,17 +24772,17 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>MM_PUR_PRMASS_UPDATE_SRV</t>
+          <t>MM_PUR_POMASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>ZMM_PUR_PRMASS_UPDATE_SRV</t>
+          <t>ZMM_PUR_POMASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Mass Update of Purchase Requisition</t>
+          <t>Service for Mass Update</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -24745,19 +24791,19 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>C_PurchaseReqMassUpdate</t>
+          <t>C_PurchaseOrderItemMassUpdate, C_PurchaseOrderMassUpdate</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PRMASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_POMASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -24772,17 +24818,17 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>MM_PUR_PROCMT_HUB_ITF_MONITOR_SRV</t>
+          <t>MM_PUR_PRMASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>ZMM_PUR_PROCMT_HUB_ITF_MONITOR_SRV</t>
+          <t>ZMM_PUR_PRMASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Procurement Hub Interface Monitor</t>
+          <t>Mass Update of Purchase Requisition</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -24791,19 +24837,19 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>SubscriptionCollection, NavigationTargetCollection, DismissCollection</t>
+          <t>C_PurchaseReqMassUpdate</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PROCMT_HUB_ITF_MONITOR_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PRMASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -24818,17 +24864,17 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>MM_PUR_PR_PROCESS_SRV</t>
+          <t>MM_PUR_PROCMT_HUB_ITF_MONITOR_SRV</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>MM_PUR_PR_PROCESS_SRV</t>
+          <t>ZMM_PUR_PROCMT_HUB_ITF_MONITOR_SRV</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Purchase Requisition Processing</t>
+          <t>Procurement Hub Interface Monitor</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -24837,19 +24883,19 @@
         </is>
       </c>
       <c r="G333" t="n">
+        <v>3</v>
+      </c>
+      <c r="H333" t="n">
         <v>1</v>
       </c>
-      <c r="H333" t="n">
-        <v>5</v>
-      </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>DraftsPRCollection</t>
+          <t>SubscriptionCollection, NavigationTargetCollection, DismissCollection</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PR_PROCESS_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PROCMT_HUB_ITF_MONITOR_SRV</t>
         </is>
       </c>
     </row>
@@ -24864,17 +24910,17 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>MM_PUR_QA_MAINTAIN</t>
+          <t>MM_PUR_PR_PROCESS_SRV</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>ZMM_PUR_QA_MAINTAIN</t>
+          <t>MM_PUR_PR_PROCESS_SRV</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Service Quota Arrangements</t>
+          <t>Purchase Requisition Processing</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -24883,19 +24929,19 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H334" t="n">
         <v>5</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>C_PurgQuotaArrgmtItemWD, C_PurgQuotaArrgmtWithDraft</t>
+          <t>DraftsPRCollection</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_QA_MAINTAIN</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PR_PROCESS_SRV</t>
         </is>
       </c>
     </row>
@@ -24910,17 +24956,17 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>MM_PUR_QTN_COMPARE_SRV</t>
+          <t>MM_PUR_QA_MAINTAIN</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>ZMM_PUR_QTN_COMPARE_SRV</t>
+          <t>ZMM_PUR_QA_MAINTAIN</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Supplier Quotation Compare</t>
+          <t>Service Quota Arrangements</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -24929,19 +24975,19 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H335" t="n">
         <v>5</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>C_RequestForQuotationCompare, C_SupplierQuotationCompare, C_SupplierQuotationItemCompare</t>
+          <t>C_PurgQuotaArrgmtItemWD, C_PurgQuotaArrgmtWithDraft</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_QTN_COMPARE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_QA_MAINTAIN</t>
         </is>
       </c>
     </row>
@@ -24956,17 +25002,17 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>MM_PUR_QTN_MAINTAIN_SRV</t>
+          <t>MM_PUR_QTN_COMPARE_SRV</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>MM_PUR_QTN_MAINTAIN_SRV</t>
+          <t>ZMM_PUR_QTN_COMPARE_SRV</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Supplier Quotation</t>
+          <t>Supplier Quotation Compare</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -24975,19 +25021,19 @@
         </is>
       </c>
       <c r="G336" t="n">
+        <v>3</v>
+      </c>
+      <c r="H336" t="n">
         <v>5</v>
       </c>
-      <c r="H336" t="n">
-        <v>13</v>
-      </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>C_AddressTP, C_QTNPricingElementWD, C_SuplrQtnItemHierarchyTP, C_SuplrQuotationEnhWD, C_SuplrQuotationItemEnhWD</t>
+          <t>C_RequestForQuotationCompare, C_SupplierQuotationCompare, C_SupplierQuotationItemCompare</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_QTN_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_QTN_COMPARE_SRV</t>
         </is>
       </c>
     </row>
@@ -25002,17 +25048,17 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>MM_PUR_REL_STRATEGY_SRV</t>
+          <t>MM_PUR_QTN_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>ZMM_PUR_REL_STRATEGY_SRV</t>
+          <t>MM_PUR_QTN_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Release Strategy</t>
+          <t>Supplier Quotation</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -25021,19 +25067,19 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H337" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>C_PurReleaseCode, C_ReleaseGroup, C_ReleaseStrategy, C_RS_Classification, C_RS_Prereq_Status, I_Relstratclass</t>
+          <t>C_AddressTP, C_QTNPricingElementWD, C_SuplrQtnItemHierarchyTP, C_SuplrQuotationEnhWD, C_SuplrQuotationItemEnhWD</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_REL_STRATEGY_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_QTN_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -25048,17 +25094,17 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>MM_PUR_REQ_APPROVAL_COMPLETION_SRV</t>
+          <t>MM_PUR_REL_STRATEGY_SRV</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>ZMM_PUR_REQ_APPROVAL_COMPLETION_SRV</t>
+          <t>ZMM_PUR_REL_STRATEGY_SRV</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>PR Completion</t>
+          <t>Release Strategy</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -25067,19 +25113,19 @@
         </is>
       </c>
       <c r="G338" t="n">
+        <v>6</v>
+      </c>
+      <c r="H338" t="n">
         <v>5</v>
       </c>
-      <c r="H338" t="n">
-        <v>17</v>
-      </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>C_PurReqnAcctAssignmentWrkItm, C_PurReqnHdrItmAcAsWrkItm, C_WrkItmPurReqnHdrItemText, C_WrkItmPurRequisitionHdrText, C_WrkItmPurRequisitionText</t>
+          <t>C_PurReleaseCode, C_ReleaseGroup, C_ReleaseStrategy, C_RS_Classification, C_RS_Prereq_Status, I_Relstratclass</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_REQ_APPROVAL_COMPLETION_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_REL_STRATEGY_SRV</t>
         </is>
       </c>
     </row>
@@ -25094,17 +25140,17 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>MM_PUR_REQ_EXT_MANAGE_SRV</t>
+          <t>MM_PUR_REQ_APPROVAL_COMPLETION_SRV</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>MM_PUR_REQ_EXT_MANAGE_SRV</t>
+          <t>ZMM_PUR_REQ_APPROVAL_COMPLETION_SRV</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Manage Central Purchase Requisitions</t>
+          <t>PR Completion</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -25113,19 +25159,19 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H339" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>PRGroupingCollection, RefreshCollection, NAVIGATION_TARGETCollection, FollowOnDocumentCollection, HubScenarioStatusCollection, POSearchDefaultCriteriaCollection, CentralContractCollection, SourcingProjectCollection, SPSearchDefaultCriteriaCollection, CCTRSearchDefaultCriteriaCollection</t>
+          <t>C_PurReqnAcctAssignmentWrkItm, C_PurReqnHdrItmAcAsWrkItm, C_WrkItmPurReqnHdrItemText, C_WrkItmPurRequisitionHdrText, C_WrkItmPurRequisitionText</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_REQ_EXT_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_REQ_APPROVAL_COMPLETION_SRV</t>
         </is>
       </c>
     </row>
@@ -25140,17 +25186,17 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>MM_PUR_REQ_SSP_V2_MAINTAIN_SRV</t>
+          <t>MM_PUR_REQ_EXT_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>ZMM_PUR_REQ_SSP_V2_MAINTAIN_SRV</t>
+          <t>MM_PUR_REQ_EXT_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Odata for SSP modernization</t>
+          <t>Manage Central Purchase Requisitions</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -25159,19 +25205,19 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H340" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>WorkflowScenarioDetailsCollection, PRDocDataCollection, C_SSPPurchaseReqnAcctAssgmtTP, C_SSPPurchaseReqnHdrTextTP, C_SSPPurchaseReqnHdrTP, C_SSPPurchaseReqnItemTextTP, C_SSPPurchaseReqnItemTP</t>
+          <t>PRGroupingCollection, RefreshCollection, NAVIGATION_TARGETCollection, FollowOnDocumentCollection, HubScenarioStatusCollection, POSearchDefaultCriteriaCollection, CentralContractCollection, SourcingProjectCollection, SPSearchDefaultCriteriaCollection, CCTRSearchDefaultCriteriaCollection</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_REQ_SSP_V2_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_REQ_EXT_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -25186,17 +25232,17 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>MM_PUR_RFQ_MAINTAIN_SRV</t>
+          <t>MM_PUR_REQ_SSP_V2_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>MM_PUR_RFQ_MAINTAIN_SRV</t>
+          <t>ZMM_PUR_REQ_SSP_V2_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Maintain RFQ Project</t>
+          <t>Odata for SSP modernization</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -25205,19 +25251,19 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H341" t="n">
         <v>19</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>BidderProposalTypeCollection, C_AddressTP, C_RequestForQuotationEnhWD, C_RFQBidderEnhWD, C_RFQItemEnhWD, C_RFQItemHierarchyTP</t>
+          <t>WorkflowScenarioDetailsCollection, PRDocDataCollection, C_SSPPurchaseReqnAcctAssgmtTP, C_SSPPurchaseReqnHdrTextTP, C_SSPPurchaseReqnHdrTP, C_SSPPurchaseReqnItemTextTP, C_SSPPurchaseReqnItemTP</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_RFQ_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_REQ_SSP_V2_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -25232,17 +25278,17 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>MM_PUR_SCHEDG_AGRMT_SRV</t>
+          <t>MM_PUR_RFQ_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>ZMM_PUR_SCHEDG_AGRMT_SRV</t>
+          <t>MM_PUR_RFQ_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Scheduling Agreement</t>
+          <t>Maintain RFQ Project</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -25251,19 +25297,19 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H342" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>C_Schagmtdelivaddress, C_Schedagrmtacct, C_Schedgagrmntitmcnd, C_Schedgagrmthdr, C_SchedgAgrmtHeaderNotesTP, C_SchedgAgrmtItemNotesTP, C_Schedgagrmtitm, C_SchedgAgrmtPartner, C_SchedgAgrmtSubcontrgComp, C_Schedgline</t>
+          <t>BidderProposalTypeCollection, C_AddressTP, C_RequestForQuotationEnhWD, C_RFQBidderEnhWD, C_RFQItemEnhWD, C_RFQItemHierarchyTP</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_SCHEDG_AGRMT_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_RFQ_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -25278,17 +25324,17 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>MM_PUR_SCH_AGMT_MASS_UPDATE_SRV</t>
+          <t>MM_PUR_SCHEDG_AGRMT_SRV</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>ZMM_PUR_SCH_AGMT_MASS_UPDATE_SRV</t>
+          <t>ZMM_PUR_SCHEDG_AGRMT_SRV</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>mass changes to scheduling agreement</t>
+          <t>Scheduling Agreement</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -25297,19 +25343,19 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H343" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>C_SchedgAgrmtItmMassUpdt, C_SchedgAgrmtMassUpdt</t>
+          <t>C_Schagmtdelivaddress, C_Schedagrmtacct, C_Schedgagrmntitmcnd, C_Schedgagrmthdr, C_SchedgAgrmtHeaderNotesTP, C_SchedgAgrmtItemNotesTP, C_Schedgagrmtitm, C_SchedgAgrmtPartner, C_SchedgAgrmtSubcontrgComp, C_Schedgline</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_SCH_AGMT_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_SCHEDG_AGRMT_SRV</t>
         </is>
       </c>
     </row>
@@ -25324,17 +25370,17 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>MM_PUR_SES_MAINTAIN_SRV</t>
+          <t>MM_PUR_SCH_AGMT_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>ZMM_PUR_SES_MAINTAIN_SRV</t>
+          <t>ZMM_PUR_SCH_AGMT_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Maintain Service Entry Sheet</t>
+          <t>mass changes to scheduling agreement</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -25343,19 +25389,19 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H344" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>C_ServiceEntrySheetItemWD, C_ServiceEntrySheetWD, C_SESAccountAssignmentWD, C_SESPricingElementTP</t>
+          <t>C_SchedgAgrmtItmMassUpdt, C_SchedgAgrmtMassUpdt</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_SES_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_SCH_AGMT_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -25370,17 +25416,17 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>MM_PUR_SUBCONTRACTING_COCKPIT_SRV</t>
+          <t>MM_PUR_SES_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>MM_PUR_SUBCONTRACTING_COCKPIT_SRV</t>
+          <t>ZMM_PUR_SES_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Subcontracting Cockpit</t>
+          <t>Maintain Service Entry Sheet</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -25389,19 +25435,19 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H345" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>C_SubcontrgCockpitDeliverySet, C_SubcontrgCockpitGoodsIssSet</t>
+          <t>C_ServiceEntrySheetItemWD, C_ServiceEntrySheetWD, C_SESAccountAssignmentWD, C_SESPricingElementTP</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_SUBCONTRACTING_COCKPIT_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_SES_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -25416,17 +25462,17 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>MM_SUPPLIER_INVOICE_LIST_ENH_SRV</t>
+          <t>MM_PUR_SUBCONTRACTING_COCKPIT_SRV</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>MM_SUPPLIER_INVOICE_LIST_ENH_SRV</t>
+          <t>MM_PUR_SUBCONTRACTING_COCKPIT_SRV</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Supplier Invoices List Enhanced</t>
+          <t>Subcontracting Cockpit</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -25435,19 +25481,19 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>C_SupplierInvoiceList</t>
+          <t>C_SubcontrgCockpitDeliverySet, C_SubcontrgCockpitGoodsIssSet</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_SUPPLIER_INVOICE_LIST_ENH_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_SUBCONTRACTING_COCKPIT_SRV</t>
         </is>
       </c>
     </row>
@@ -25462,17 +25508,17 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>MM_SUPPLIER_INVOICE_UPLOAD_SRV</t>
+          <t>MM_SUPPLIER_INVOICE_LIST_ENH_SRV</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>ZMM_SUPPLIER_INVOICE_UPLOAD_SRV</t>
+          <t>MM_SUPPLIER_INVOICE_LIST_ENH_SRV</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Supplier Invoice Upload</t>
+          <t>Supplier Invoices List Enhanced</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -25481,19 +25527,19 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>C_SupplierInvoiceUpload, C_SupplierInvoiceUploadHistory</t>
+          <t>C_SupplierInvoiceList</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_SUPPLIER_INVOICE_UPLOAD_SRV</t>
+          <t>/sap/opu/odata/sap/MM_SUPPLIER_INVOICE_LIST_ENH_SRV</t>
         </is>
       </c>
     </row>
@@ -25508,17 +25554,17 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>OCI_ITEM_PROPOSAL_SRV</t>
+          <t>MM_SUPPLIER_INVOICE_UPLOAD_SRV</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>ZOCI_ITEM_PROPOSAL_SRV</t>
+          <t>ZMM_SUPPLIER_INVOICE_UPLOAD_SRV</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Service for OCI Item Proposal</t>
+          <t>Supplier Invoice Upload</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -25530,16 +25576,16 @@
         <v>2</v>
       </c>
       <c r="H348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>ItmRecommendationStatusCollection, CatalogItemURLCollection</t>
+          <t>C_SupplierInvoiceUpload, C_SupplierInvoiceUploadHistory</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/OCI_ITEM_PROPOSAL_SRV</t>
+          <t>/sap/opu/odata/sap/MM_SUPPLIER_INVOICE_UPLOAD_SRV</t>
         </is>
       </c>
     </row>
@@ -25554,17 +25600,17 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PP_MRP_PR_HANDOVER_SRV</t>
+          <t>OCI_ITEM_PROPOSAL_SRV</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>ZPP_MRP_PR_HANDOVER_SRV</t>
+          <t>ZOCI_ITEM_PROPOSAL_SRV</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Hand over Purchase Requisition</t>
+          <t>Service for OCI Item Proposal</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -25573,19 +25619,19 @@
         </is>
       </c>
       <c r="G349" t="n">
+        <v>2</v>
+      </c>
+      <c r="H349" t="n">
         <v>1</v>
       </c>
-      <c r="H349" t="n">
-        <v>3</v>
-      </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>ActionResultCollection</t>
+          <t>ItmRecommendationStatusCollection, CatalogItemURLCollection</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MRP_PR_HANDOVER_SRV</t>
+          <t>/sap/opu/odata/sap/OCI_ITEM_PROPOSAL_SRV</t>
         </is>
       </c>
     </row>
@@ -25600,17 +25646,17 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>UI_SRCGPROJAWDSCEN_MANAGE</t>
+          <t>PP_MRP_PR_HANDOVER_SRV</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>ZUI_SRCGPROJAWDSCEN_MANAGE</t>
+          <t>ZPP_MRP_PR_HANDOVER_SRV</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Awarding Scenario</t>
+          <t>Hand over Purchase Requisition</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -25622,16 +25668,16 @@
         <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>SrcgProjAwardingScenQtn</t>
+          <t>ActionResultCollection</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_SRCGPROJAWDSCEN_MANAGE</t>
+          <t>/sap/opu/odata/sap/PP_MRP_PR_HANDOVER_SRV</t>
         </is>
       </c>
     </row>
@@ -25646,17 +25692,17 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>UI_SUPLRUSRDFNDCRITRA</t>
+          <t>UI_SRCGPROJAWDSCEN_MANAGE</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>ZUI_SUPLRUSRDFNDCRITRA</t>
+          <t>ZUI_SRCGPROJAWDSCEN_MANAGE</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Supplier Evaluation By User-Defined Criteria</t>
+          <t>Awarding Scenario</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -25668,16 +25714,16 @@
         <v>1</v>
       </c>
       <c r="H351" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>SupplierUsrDfndCritraScores</t>
+          <t>SrcgProjAwardingScenQtn</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_SUPLRUSRDFNDCRITRA</t>
+          <t>/sap/opu/odata/sap/UI_SRCGPROJAWDSCEN_MANAGE</t>
         </is>
       </c>
     </row>
@@ -25692,17 +25738,17 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>UI_SUPPLIERLIST_MANAGE</t>
+          <t>UI_SUPLRUSRDFNDCRITRA</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>ZUI_SUPPLIERLIST_MANAGE</t>
+          <t>ZUI_SUPLRUSRDFNDCRITRA</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Service Binding for UI_SupplierList_Manage</t>
+          <t>Supplier Evaluation By User-Defined Criteria</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -25711,19 +25757,19 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>SuplrListBusinessPartner, SuplrListMaterialGroup, SuplrListPurgCategory, SuplrListPurgOrganization, SupplierListCompanyCode, SupplierList</t>
+          <t>SupplierUsrDfndCritraScores</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_SUPPLIERLIST_MANAGE</t>
+          <t>/sap/opu/odata/sap/UI_SUPLRUSRDFNDCRITRA</t>
         </is>
       </c>
     </row>
@@ -25733,22 +25779,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Master data - MDG</t>
+          <t>MM - Purchasing</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>MDC_CUSTMIZING</t>
+          <t>UI_SUPPLIERLIST_MANAGE</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>ZMDC_CUSTMIZING</t>
+          <t>ZUI_SUPPLIERLIST_MANAGE</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>MDC CUSTOMIZING</t>
+          <t>Service Binding for UI_SupplierList_Manage</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -25757,19 +25803,19 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H353" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>FuzzyConfigSet, FuzzyRuleSet, FuzzyAttributeSet, FuzzyConditionSet</t>
+          <t>SuplrListBusinessPartner, SuplrListMaterialGroup, SuplrListPurgCategory, SuplrListPurgOrganization, SupplierListCompanyCode, SupplierList</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_CUSTMIZING</t>
+          <t>/sap/opu/odata/sap/UI_SUPPLIERLIST_MANAGE</t>
         </is>
       </c>
     </row>
@@ -25784,17 +25830,17 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>MDC_CUSTOM_OBJECT_SRV</t>
+          <t>MDC_CUSTMIZING</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>ZMDC_CUSTOM_OBJECT_SRV</t>
+          <t>ZMDC_CUSTMIZING</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>MDC Custom Object</t>
+          <t>MDC CUSTOMIZING</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -25803,19 +25849,19 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H354" t="n">
         <v>2</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>CustObjectSet, CustObjectDetSet</t>
+          <t>FuzzyConfigSet, FuzzyRuleSet, FuzzyAttributeSet, FuzzyConditionSet</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_CUSTOM_OBJECT_SRV</t>
+          <t>/sap/opu/odata/sap/MDC_CUSTMIZING</t>
         </is>
       </c>
     </row>
@@ -25830,17 +25876,17 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>MDC_IMPORT_SRV</t>
+          <t>MDC_CUSTOM_OBJECT_SRV</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>ZMDC_IMPORT_SRV</t>
+          <t>ZMDC_CUSTOM_OBJECT_SRV</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Masterdata Import</t>
+          <t>MDC Custom Object</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -25849,19 +25895,19 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H355" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>C_MasterDataImport</t>
+          <t>CustObjectSet, CustObjectDetSet</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_IMPORT_SRV</t>
+          <t>/sap/opu/odata/sap/MDC_CUSTOM_OBJECT_SRV</t>
         </is>
       </c>
     </row>
@@ -25876,17 +25922,17 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>MDC_PROCESS_SRV__1405</t>
+          <t>MDC_IMPORT_SRV</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>ZMDC_PROCESS_SRV__1405</t>
+          <t>ZMDC_IMPORT_SRV</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Service for MDC business partner relationships</t>
+          <t>Masterdata Import</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -25895,19 +25941,19 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H356" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>SOURCESet, SelectionSet, ROOTSet</t>
+          <t>C_MasterDataImport</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__1405</t>
+          <t>/sap/opu/odata/sap/MDC_IMPORT_SRV</t>
         </is>
       </c>
     </row>
@@ -25922,17 +25968,17 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>MDC_PROCESS_SRV__147</t>
+          <t>MDC_PROCESS_SRV__1405</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>ZMDC_PROCESS_SRV__147</t>
+          <t>ZMDC_PROCESS_SRV__1405</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>MDC Process Object For BP</t>
+          <t>Service for MDC business partner relationships</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -25953,7 +25999,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__147</t>
+          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__1405</t>
         </is>
       </c>
     </row>
@@ -25968,17 +26014,17 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>MDC_PROCESS_SRV__194</t>
+          <t>MDC_PROCESS_SRV__147</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>ZMDC_PROCESS_SRV__194</t>
+          <t>ZMDC_PROCESS_SRV__147</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>MDC Process Object For Material</t>
+          <t>MDC Process Object For BP</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -25999,7 +26045,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__194</t>
+          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__147</t>
         </is>
       </c>
     </row>
@@ -26014,17 +26060,17 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>MDC_PROCESS_SRV__986</t>
+          <t>MDC_PROCESS_SRV__194</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>ZMDC_PROCESS_SRV__986</t>
+          <t>ZMDC_PROCESS_SRV__194</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Service for MDC business partner and relationships</t>
+          <t>MDC Process Object For Material</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -26045,7 +26091,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__986</t>
+          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__194</t>
         </is>
       </c>
     </row>
@@ -26060,17 +26106,17 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>MDC_TRACK_CHANGES_SRV__1405</t>
+          <t>MDC_PROCESS_SRV__986</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>ZMDC_TRACK_CHANGES_SRV__1405</t>
+          <t>ZMDC_PROCESS_SRV__986</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>MDC Service for Track Changes - Business Partner Relations</t>
+          <t>Service for MDC business partner and relationships</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -26079,19 +26125,19 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H360" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>UserContactCards, Processes</t>
+          <t>SOURCESet, SelectionSet, ROOTSet</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_TRACK_CHANGES_SRV__1405</t>
+          <t>/sap/opu/odata/sap/MDC_PROCESS_SRV__986</t>
         </is>
       </c>
     </row>
@@ -26106,17 +26152,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>MDC_TRACK_CHANGES_SRV__147</t>
+          <t>MDC_TRACK_CHANGES_SRV__1405</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>ZMDC_TRACK_CHANGES_SRV__147</t>
+          <t>ZMDC_TRACK_CHANGES_SRV__1405</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>MDC Service for Track Changes - Business Partner</t>
+          <t>MDC Service for Track Changes - Business Partner Relations</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -26137,7 +26183,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_TRACK_CHANGES_SRV__147</t>
+          <t>/sap/opu/odata/sap/MDC_TRACK_CHANGES_SRV__1405</t>
         </is>
       </c>
     </row>
@@ -26152,17 +26198,17 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>MDC_TRACK_CHANGES_SRV__194</t>
+          <t>MDC_TRACK_CHANGES_SRV__147</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>ZMDC_TRACK_CHANGES_SRV__194</t>
+          <t>ZMDC_TRACK_CHANGES_SRV__147</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>MDC Service for Track Changes - Material</t>
+          <t>MDC Service for Track Changes - Business Partner</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -26183,7 +26229,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MDC_TRACK_CHANGES_SRV__194</t>
+          <t>/sap/opu/odata/sap/MDC_TRACK_CHANGES_SRV__147</t>
         </is>
       </c>
     </row>
@@ -26198,17 +26244,17 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>MD_QC_PRODUCT_SRV</t>
+          <t>MDC_TRACK_CHANGES_SRV__194</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>ZMD_QC_PRODUCT_SRV</t>
+          <t>ZMDC_TRACK_CHANGES_SRV__194</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Product Master - Odata for Quick Create</t>
+          <t>MDC Service for Track Changes - Material</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -26220,16 +26266,16 @@
         <v>2</v>
       </c>
       <c r="H363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>C_QuickCreateProduct, C_QuickCreateProductUoM</t>
+          <t>UserContactCards, Processes</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MD_QC_PRODUCT_SRV</t>
+          <t>/sap/opu/odata/sap/MDC_TRACK_CHANGES_SRV__194</t>
         </is>
       </c>
     </row>
@@ -26244,17 +26290,17 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>UI_MODPRODSPEC_MANAGE</t>
+          <t>MD_QC_PRODUCT_SRV</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>ZUI_MODPRODSPEC_MANAGE</t>
+          <t>ZMD_QC_PRODUCT_SRV</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Model Product Specification - UI Service Binding</t>
+          <t>Product Master - Odata for Quick Create</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -26263,19 +26309,19 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H364" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>C_ModelProductSpecificationTP</t>
+          <t>C_QuickCreateProduct, C_QuickCreateProductUoM</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_MODPRODSPEC_MANAGE</t>
+          <t>/sap/opu/odata/sap/MD_QC_PRODUCT_SRV</t>
         </is>
       </c>
     </row>
@@ -26285,43 +26331,43 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PM - Maintenance</t>
+          <t>Master data - MDG</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>API_MAINTNOTIFICATION</t>
+          <t>UI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>API_MAINTNOTIFICATION</t>
+          <t>ZUI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Maintenance Notification</t>
+          <t>Model Product Specification - UI Service Binding</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Released API</t>
+          <t>Fiori app service</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H365" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>MaintenanceNotification, MaintNotificationEffectCode, MaintenanceNotificationItem, MaintenanceNotificationPartner, MaintNotificationItemActivity, MaintNotificationItemCause</t>
+          <t>C_ModelProductSpecificationTP</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/API_MAINTNOTIFICATION</t>
+          <t>/sap/opu/odata/sap/UI_MODPRODSPEC_MANAGE</t>
         </is>
       </c>
     </row>
@@ -26336,17 +26382,17 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>API_MAINTORDERCONFIRMATION</t>
+          <t>API_MAINTNOTIFICATION</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>API_MAINTORDERCONFIRMATION</t>
+          <t>API_MAINTNOTIFICATION</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Service Binding for Maint. Order Confirmation</t>
+          <t>Maintenance Notification</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -26355,19 +26401,19 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H366" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>MaintOrderConfirmation</t>
+          <t>MaintenanceNotification, MaintNotificationEffectCode, MaintenanceNotificationItem, MaintenanceNotificationPartner, MaintNotificationItemActivity, MaintNotificationItemCause</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/API_MAINTORDERCONFIRMATION</t>
+          <t>/sap/opu/odata/sap/API_MAINTNOTIFICATION</t>
         </is>
       </c>
     </row>
@@ -26382,38 +26428,38 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>DFS_MAINT_NOTIFICATION_SRV</t>
+          <t>API_MAINTORDERCONFIRMATION</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>DFS_MAINT_NOTIFICATION_SRV</t>
+          <t>API_MAINTORDERCONFIRMATION</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Extension for EAM_OBJPG_MAINTNOTIFICATION</t>
+          <t>Service Binding for Maint. Order Confirmation</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Fiori app service</t>
+          <t>Released API</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H367" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
+          <t>MaintOrderConfirmation</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_NOTIFICATION_SRV</t>
+          <t>/sap/opu/odata/sap/API_MAINTORDERCONFIRMATION</t>
         </is>
       </c>
     </row>
@@ -26428,17 +26474,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
+          <t>DFS_MAINT_NOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
+          <t>DFS_MAINT_NOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Extention of EAM_OBJPG_MAINTORDANDOPERATION</t>
+          <t>Extension for EAM_OBJPG_MAINTNOTIFICATION</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -26447,19 +26493,19 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H368" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
+          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_ORDANDOPERATION_SRV</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_NOTIFICATION_SRV</t>
         </is>
       </c>
     </row>
@@ -26474,17 +26520,17 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDER_SRV</t>
+          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>DFS_MAINT_ORDER_SRV</t>
+          <t>DFS_MAINT_ORDANDOPERATION_SRV</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Extension for EAM_OBJPG_MAINTENANCEORDER</t>
+          <t>Extention of EAM_OBJPG_MAINTORDANDOPERATION</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -26493,19 +26539,19 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H369" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintOrder</t>
+          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_ORDER_SRV</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_ORDANDOPERATION_SRV</t>
         </is>
       </c>
     </row>
@@ -26520,17 +26566,17 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
+          <t>DFS_MAINT_ORDER_SRV</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
+          <t>DFS_MAINT_ORDER_SRV</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Extension project for EAM_OBJPG_TECHNICALOBJECT</t>
+          <t>Extension for EAM_OBJPG_MAINTENANCEORDER</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -26539,19 +26585,19 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H370" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ObjPgMaintOrder</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/DFS_MAINT_TECHNICALOBJECT_SRV</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_ORDER_SRV</t>
         </is>
       </c>
     </row>
@@ -26566,17 +26612,17 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>EAM_MALFUNCTION_MANAGE</t>
+          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>EAM_MALFUNCTION_MANAGE</t>
+          <t>DFS_MAINT_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>F2023 "Respond to Breakdown" FIORI app</t>
+          <t>Extension project for EAM_OBJPG_TECHNICALOBJECT</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -26585,19 +26631,19 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H371" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>EmptyNotification, C_MaintNotifActivityTP, C_MaintNotificationCauseTP, C_MaintNotificationItemTP, C_MaintNotificationTP, C_MaintNotifLongTextTP, C_MaintOrderComponentTP, C_MaintOrderConfirmationTP, C_MaintOrderOperationTP, C_MaintOrderSubOperationTP, C_MaintOrderTP</t>
+          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_MALFUNCTION_MANAGE</t>
+          <t>/sap/opu/odata/sap/DFS_MAINT_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
     </row>
@@ -26612,17 +26658,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>EAM_NTF_CREATE</t>
+          <t>EAM_MALFUNCTION_MANAGE</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>EAM_NTF_CREATE</t>
+          <t>EAM_MALFUNCTION_MANAGE</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>EAM Notification Creation</t>
+          <t>F2023 "Respond to Breakdown" FIORI app</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -26631,19 +26677,19 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H372" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>NotificationHeaderSet, NotificationImageTypeCollection, LongTextSet</t>
+          <t>EmptyNotification, C_MaintNotifActivityTP, C_MaintNotificationCauseTP, C_MaintNotificationItemTP, C_MaintNotificationTP, C_MaintNotifLongTextTP, C_MaintOrderComponentTP, C_MaintOrderConfirmationTP, C_MaintOrderOperationTP, C_MaintOrderSubOperationTP, C_MaintOrderTP</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_NTF_CREATE</t>
+          <t>/sap/opu/odata/sap/EAM_MALFUNCTION_MANAGE</t>
         </is>
       </c>
     </row>
@@ -26658,17 +26704,17 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
+          <t>EAM_NTF_CREATE</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
+          <t>EAM_NTF_CREATE</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>F2175: Find Maintenance Order</t>
+          <t>EAM Notification Creation</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -26677,19 +26723,19 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H373" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>CreateWorkPackInput, C_ObjPgMaintOrder</t>
+          <t>NotificationHeaderSet, NotificationImageTypeCollection, LongTextSet</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTENANCEORDER_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_NTF_CREATE</t>
         </is>
       </c>
     </row>
@@ -26704,17 +26750,17 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTITEM_SRV</t>
+          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTITEM_SRV</t>
+          <t>EAM_OBJPG_MAINTENANCEORDER_SRV</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Maintenance Item for Object Page</t>
+          <t>F2175: Find Maintenance Order</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -26723,19 +26769,19 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H374" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>C_MaintenanceItemObjPg</t>
+          <t>CreateWorkPackInput, C_ObjPgMaintOrder</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTITEM_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTENANCEORDER_SRV</t>
         </is>
       </c>
     </row>
@@ -26750,17 +26796,17 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
+          <t>EAM_OBJPG_MAINTITEM_SRV</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
+          <t>EAM_OBJPG_MAINTITEM_SRV</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Maintenance Notification for Object Page</t>
+          <t>Maintenance Item for Object Page</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -26769,19 +26815,19 @@
         </is>
       </c>
       <c r="G375" t="n">
+        <v>1</v>
+      </c>
+      <c r="H375" t="n">
         <v>2</v>
       </c>
-      <c r="H375" t="n">
-        <v>16</v>
-      </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
+          <t>C_MaintenanceItemObjPg</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTITEM_SRV</t>
         </is>
       </c>
     </row>
@@ -26796,17 +26842,17 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
+          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
+          <t>EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>F2173: Find Maintenance Orders and Operations</t>
+          <t>Maintenance Notification for Object Page</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -26815,19 +26861,19 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H376" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
+          <t>C_ObjPgMaintNotification, I_MaintNotifAssignOrderInput</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTORDANDOPER_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTNOTIFICATION_SRV</t>
         </is>
       </c>
     </row>
@@ -26842,17 +26888,17 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
+          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
+          <t>EAM_OBJPG_MAINTORDANDOPER_SRV</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>OData service for EAM Technical Object Object Page</t>
+          <t>F2173: Find Maintenance Orders and Operations</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -26864,16 +26910,16 @@
         <v>4</v>
       </c>
       <c r="H377" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>ChangeAssignmentInput, CreateWorkPackInput, CreateTimeConfirmationInput, C_ObjPgMaintOrderAndOperation</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/EAM_OBJPG_TECHNICALOBJECT_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_MAINTORDANDOPER_SRV</t>
         </is>
       </c>
     </row>
@@ -26888,17 +26934,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
+          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>ZFAC_GL_MAINT_POSTING_PERIOD_SRV</t>
+          <t>EAM_OBJPG_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Maintain Posting Period</t>
+          <t>OData service for EAM Technical Object Object Page</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -26907,19 +26953,19 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H378" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>PostingPeriodScheduledJobsSet, PostingPeriodSet, PostingPeriodInCoCdSet</t>
+          <t>C_ObjPgTechnicalObject, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
+          <t>/sap/opu/odata/sap/EAM_OBJPG_TECHNICALOBJECT_SRV</t>
         </is>
       </c>
     </row>
@@ -26934,17 +26980,17 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
+          <t>FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
+          <t>ZFAC_GL_MAINT_POSTING_PERIOD_SRV</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>chart of account smaintainance</t>
+          <t>Maintain Posting Period</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -26960,12 +27006,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>ProposedFSVParamSet, CopyGLAccountInCOAParamSet, CopyGLAccountInCOCDParamSet</t>
+          <t>PostingPeriodScheduledJobsSet, PostingPeriodSet, PostingPeriodInCoCdSet</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
+          <t>/sap/opu/odata/sap/FAC_GL_MAINT_POSTING_PERIOD_SRV</t>
         </is>
       </c>
     </row>
@@ -26980,17 +27026,17 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>ICA_MATCH_METHOD_SRV</t>
+          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>ZICA_MATCH_METHOD_SRV</t>
+          <t>FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Inter-Company Match Method Maintenance</t>
+          <t>chart of account smaintainance</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -26999,19 +27045,19 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H380" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>MatchingMethodSet</t>
+          <t>ProposedFSVParamSet, CopyGLAccountInCOAParamSet, CopyGLAccountInCOCDParamSet</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/ICA_MATCH_METHOD_SRV</t>
+          <t>/sap/opu/odata/sap/FAC_MAINT_CHART_OF_ACCOUNTS_SRV</t>
         </is>
       </c>
     </row>
@@ -27026,17 +27072,17 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
+          <t>ICA_MATCH_METHOD_SRV</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_GROUP_MAINTAIN_SRV</t>
+          <t>ZICA_MATCH_METHOD_SRV</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Variant Configuration Characteristic Group Maintenance</t>
+          <t>Inter-Company Match Method Maintenance</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -27045,19 +27091,19 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H381" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>C_ConfignCharcGroupAllocTP, C_ConfignCharcGroupDescTP, C_ConfignCharcGroupTP</t>
+          <t>MatchingMethodSet</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/ICA_MATCH_METHOD_SRV</t>
         </is>
       </c>
     </row>
@@ -27072,17 +27118,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>MMIM_PI_CYC_MAINT_SRV</t>
+          <t>LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>ZMMIM_PI_CYC_MAINT_SRV</t>
+          <t>ZLO_VCHCLF_GROUP_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>OData Service of app Cycle Counting - Classification</t>
+          <t>Variant Configuration Characteristic Group Maintenance</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -27091,19 +27137,19 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H382" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>ClassificationReturnSet</t>
+          <t>C_ConfignCharcGroupAllocTP, C_ConfignCharcGroupDescTP, C_ConfignCharcGroupTP</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMIM_PI_CYC_MAINT_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_GROUP_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -27118,17 +27164,17 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>MMPUR_PROC_CAT_MAINT_SRV</t>
+          <t>MMIM_PI_CYC_MAINT_SRV</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>ZMMPUR_PROC_CAT_MAINT_SRV</t>
+          <t>ZMMIM_PI_CYC_MAINT_SRV</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Maintian procurement catalog call structure</t>
+          <t>OData Service of app Cycle Counting - Classification</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -27137,19 +27183,19 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H383" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>C_Proccatalogcalldetails, C_Proccatalogcallstruct</t>
+          <t>ClassificationReturnSet</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MMPUR_PROC_CAT_MAINT_SRV</t>
+          <t>/sap/opu/odata/sap/MMIM_PI_CYC_MAINT_SRV</t>
         </is>
       </c>
     </row>
@@ -27164,17 +27210,17 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>MM_PUR_PO_MAINT_V2_SRV</t>
+          <t>MMPUR_PROC_CAT_MAINT_SRV</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>MM_PUR_PO_MAINT_V2_SRV</t>
+          <t>ZMMPUR_PROC_CAT_MAINT_SRV</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Manage Purchase Orders (SmartTemplate)</t>
+          <t>Maintian procurement catalog call structure</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -27183,19 +27229,19 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H384" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>C_POSubcontractingComponentTP, C_PurchaseOrderItemNoteTP, C_PurchaseOrderItemReturnTP, C_PurchaseOrderItemSet, C_PurchaseOrderItemTP, C_PurchaseOrderNoteTP, C_PurchaseOrderPartnerTP, C_PurchaseOrderTP, C_PurOrdAcctAssignmentTP, C_PurOrdItmRetProcNxtPlantTP, C_PurOrdPricingElementTP, C_PurOrdScheduleLineTP, I_SeasonBasic</t>
+          <t>C_Proccatalogcalldetails, C_Proccatalogcallstruct</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PO_MAINT_V2_SRV</t>
+          <t>/sap/opu/odata/sap/MMPUR_PROC_CAT_MAINT_SRV</t>
         </is>
       </c>
     </row>
@@ -27210,17 +27256,17 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
+          <t>MM_PUR_PO_MAINT_V2_SRV</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
+          <t>MM_PUR_PO_MAINT_V2_SRV</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Profnl Purchase Requisition maintan</t>
+          <t>Manage Purchase Orders (SmartTemplate)</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -27229,19 +27275,19 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H385" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>C_PurchaseReqnAcctAssgmt, C_PurchaseReqnDelivAdd, C_PurchaseReqnHeader, C_PurchaseReqnHeaderNotes, C_PurchaseReqnItem, C_PurchaseReqnItemHierTP, C_PurchaseReqnItemText, I_Proccatalogcalldetails</t>
+          <t>C_POSubcontractingComponentTP, C_PurchaseOrderItemNoteTP, C_PurchaseOrderItemReturnTP, C_PurchaseOrderItemSet, C_PurchaseOrderItemTP, C_PurchaseOrderNoteTP, C_PurchaseOrderPartnerTP, C_PurchaseOrderTP, C_PurOrdAcctAssignmentTP, C_PurOrdItmRetProcNxtPlantTP, C_PurOrdPricingElementTP, C_PurOrdScheduleLineTP, I_SeasonBasic</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PO_MAINT_V2_SRV</t>
         </is>
       </c>
     </row>
@@ -27256,17 +27302,17 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>PP_DD_MASSMAINTPROD_SRV</t>
+          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>ZPP_DD_MASSMAINTPROD_SRV</t>
+          <t>MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Odata DDR: Mass Maintenance: Products (DD)</t>
+          <t>Profnl Purchase Requisition maintan</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -27275,19 +27321,19 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H386" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>MassEditActionSet, ChangeDDScopeActnSet, C_DemandDrivenProductTP</t>
+          <t>C_PurchaseReqnAcctAssgmt, C_PurchaseReqnDelivAdd, C_PurchaseReqnHeader, C_PurchaseReqnHeaderNotes, C_PurchaseReqnItem, C_PurchaseReqnItemHierTP, C_PurchaseReqnItemText, I_Proccatalogcalldetails</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_MASSMAINTPROD_SRV</t>
+          <t>/sap/opu/odata/sap/MM_PUR_PR_PROFNL_MAINTAIN_SRV</t>
         </is>
       </c>
     </row>
@@ -27302,17 +27348,17 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>PP_FCDM_MASS_MAINT</t>
+          <t>PP_DD_MASSMAINTPROD_SRV</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>ZPP_FCDM_MASS_MAINT</t>
+          <t>ZPP_DD_MASSMAINTPROD_SRV</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Demand Forecast Keyfigures and Mass Maintenance</t>
+          <t>Odata DDR: Mass Maintenance: Products (DD)</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -27321,19 +27367,19 @@
         </is>
       </c>
       <c r="G387" t="n">
+        <v>3</v>
+      </c>
+      <c r="H387" t="n">
         <v>2</v>
       </c>
-      <c r="H387" t="n">
-        <v>0</v>
-      </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>PlannedIndepRqmtItem, PlannedIndepRqmt</t>
+          <t>MassEditActionSet, ChangeDDScopeActnSet, C_DemandDrivenProductTP</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_FCDM_MASS_MAINT</t>
+          <t>/sap/opu/odata/sap/PP_DD_MASSMAINTPROD_SRV</t>
         </is>
       </c>
     </row>
@@ -27348,17 +27394,17 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>RSH_EAM_ANALYZE_SRV</t>
+          <t>PP_FCDM_MASS_MAINT</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>RSH_EAM_ANALYZE_SRV</t>
+          <t>ZPP_FCDM_MASS_MAINT</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Resource Scheduling for EAM</t>
+          <t>Demand Forecast Keyfigures and Mass Maintenance</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -27367,19 +27413,19 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H388" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>GlobalFilterTypeCollection, C_RSHEAMUserVariant, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
+          <t>PlannedIndepRqmtItem, PlannedIndepRqmt</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_ANALYZE_SRV</t>
+          <t>/sap/opu/odata/sap/PP_FCDM_MASS_MAINT</t>
         </is>
       </c>
     </row>
@@ -27394,17 +27440,17 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
+          <t>RSH_EAM_ANALYZE_SRV</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>ZRSH_EAM_MAINT_ASSET_BOARD_SRV</t>
+          <t>RSH_EAM_ANALYZE_SRV</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Maintenance Asset Board</t>
+          <t>Resource Scheduling for EAM</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -27413,19 +27459,19 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H389" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintOrder, C_RSHMaintenanceRevisionList</t>
+          <t>GlobalFilterTypeCollection, C_RSHEAMUserVariant, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_ANALYZE_SRV</t>
         </is>
       </c>
     </row>
@@ -27440,17 +27486,17 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
+          <t>RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
+          <t>ZRSH_EAM_MAINT_ASSET_BOARD_SRV</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Maintenance Scheduling Simulation</t>
+          <t>Maintenance Asset Board</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -27459,19 +27505,19 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H390" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>C_RSHEAMUserVariant, C_RSHMaintSchedActivityLog, C_RSHMaintSchedCollaborators, C_RSHMaintSchedRescheduledOp, C_RSHMaintSchedReviewers, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHMaintSchedSmltdOrdAndOp, C_RSHUserVariantWithTeam</t>
+          <t>C_ObjPgMaintOrder, C_RSHMaintenanceRevisionList</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_ASSET_BOARD_SRV</t>
         </is>
       </c>
     </row>
@@ -27486,17 +27532,17 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>RSH_EAM_ORDER_GANTT_SRV</t>
+          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>ZRSH_EAM_ORDER_GANTT_SRV</t>
+          <t>RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Maintenance Order Operation Gantt</t>
+          <t>Maintenance Scheduling Simulation</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -27505,19 +27551,19 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H391" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>C_ObjPgMaintOrder, C_RSHEAMUserVariant, C_RSHMaintenanceRevisionList, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
+          <t>C_RSHEAMUserVariant, C_RSHMaintSchedActivityLog, C_RSHMaintSchedCollaborators, C_RSHMaintSchedRescheduledOp, C_RSHMaintSchedReviewers, C_RSHMaintSchedSimulation, C_RSHMaintSchedSmltdOp, C_RSHMaintSchedSmltdOrdAndOp, C_RSHUserVariantWithTeam</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_ORDER_GANTT_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_MAINT_SCHED_SIMULATION_SRV</t>
         </is>
       </c>
     </row>
@@ -27532,17 +27578,17 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>RSH_EAM_RES_ASSIGNMENT_SRV</t>
+          <t>RSH_EAM_ORDER_GANTT_SRV</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>ZRSH_EAM_RES_ASSIGNMENT_SRV</t>
+          <t>ZRSH_EAM_ORDER_GANTT_SRV</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Resource Assignment</t>
+          <t>Maintenance Order Operation Gantt</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -27551,19 +27597,19 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H392" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>FEATURECollection, C_RSHEAMUserVariant, C_RSHMaintOpAssgmtResList, C_RSHMaintOperationAssignment, C_RSHUserVariantWithTeam</t>
+          <t>C_ObjPgMaintOrder, C_RSHEAMUserVariant, C_RSHMaintenanceRevisionList, C_RSHUserVariantWithTeam, C_RSHWorkCenterCapacityChangeSet, I_MaintOrderOperationTP, I_MaintOrderSubOperationTP, I_MaintOrderTP</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_EAM_RES_ASSIGNMENT_SRV</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_ORDER_GANTT_SRV</t>
         </is>
       </c>
     </row>
@@ -27578,17 +27624,17 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>RSH_SB_MAINTENANCE_ORDER</t>
+          <t>RSH_EAM_RES_ASSIGNMENT_SRV</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>ZRSH_SB_MAINTENANCE_ORDER</t>
+          <t>ZRSH_EAM_RES_ASSIGNMENT_SRV</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Service Binding for Maintenance Order</t>
+          <t>Resource Assignment</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -27597,19 +27643,19 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H393" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>C_RSHMaintenanceOrderTP, C_RSHMaintenanceOrdOperationTP, C_RSHMaintenanceOrdOpRelshpTP</t>
+          <t>FEATURECollection, C_RSHEAMUserVariant, C_RSHMaintOpAssgmtResList, C_RSHMaintOperationAssignment, C_RSHUserVariantWithTeam</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/RSH_SB_MAINTENANCE_ORDER</t>
+          <t>/sap/opu/odata/sap/RSH_EAM_RES_ASSIGNMENT_SRV</t>
         </is>
       </c>
     </row>
@@ -27624,17 +27670,17 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>UI_C_DFS_MAINT_PLATFORM</t>
+          <t>RSH_SB_MAINTENANCE_ORDER</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>ZUI_C_DFS_MAINT_PLATFORM</t>
+          <t>ZRSH_SB_MAINTENANCE_ORDER</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Service Binding for Platform Code</t>
+          <t>Service Binding for Maintenance Order</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -27643,19 +27689,19 @@
         </is>
       </c>
       <c r="G394" t="n">
+        <v>3</v>
+      </c>
+      <c r="H394" t="n">
         <v>1</v>
       </c>
-      <c r="H394" t="n">
-        <v>9</v>
-      </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>C_DFS_MaintPlatform</t>
+          <t>C_RSHMaintenanceOrderTP, C_RSHMaintenanceOrdOperationTP, C_RSHMaintenanceOrdOpRelshpTP</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_C_DFS_MAINT_PLATFORM</t>
+          <t>/sap/opu/odata/sap/RSH_SB_MAINTENANCE_ORDER</t>
         </is>
       </c>
     </row>
@@ -27665,22 +27711,22 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PP - Production</t>
+          <t>PM - Maintenance</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BILLOFMATERIALV2_SRV</t>
+          <t>UI_C_DFS_MAINT_PLATFORM</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>ZBILLOFMATERIALV2_SRV</t>
+          <t>ZUI_C_DFS_MAINT_PLATFORM</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>BOM Service for Draft 2.0</t>
+          <t>Service Binding for Platform Code</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -27689,19 +27735,19 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H395" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>C_BillOfMaterialItemTP, C_BillOfMaterialSubItemsTP, C_BillOfMaterialTP, C_MngUnassgdEngBOMChgRecd, I_ChangeRecordBsc</t>
+          <t>C_DFS_MaintPlatform</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/BILLOFMATERIALV2_SRV</t>
+          <t>/sap/opu/odata/sap/UI_C_DFS_MAINT_PLATFORM</t>
         </is>
       </c>
     </row>
@@ -27716,17 +27762,17 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BOMWHEREUSED_SRV</t>
+          <t>BILLOFMATERIALV2_SRV</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>ZBOMWHEREUSED_SRV</t>
+          <t>ZBILLOFMATERIALV2_SRV</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>BOM where used</t>
+          <t>BOM Service for Draft 2.0</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -27735,19 +27781,19 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H396" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>VersionBillOfMaterial, MRPAvailabilitySet, AdditionalControlDataCollection, C_BOMWhereUsedHeader</t>
+          <t>C_BillOfMaterialItemTP, C_BillOfMaterialSubItemsTP, C_BillOfMaterialTP, C_MngUnassgdEngBOMChgRecd, I_ChangeRecordBsc</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/BOMWHEREUSED_SRV</t>
+          <t>/sap/opu/odata/sap/BILLOFMATERIALV2_SRV</t>
         </is>
       </c>
     </row>
@@ -27762,17 +27808,17 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>C_MRPCTRLRBYAOR_SRV</t>
+          <t>BOMWHEREUSED_SRV</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>ZC_MRPCTRLRBYAOR_SRV</t>
+          <t>ZBOMWHEREUSED_SRV</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Service Binding C_MRPCtrlrByAreaOfRespy</t>
+          <t>BOM where used</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -27781,19 +27827,19 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H397" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>I_MRPAreaOfResponsibilityTP</t>
+          <t>VersionBillOfMaterial, MRPAvailabilitySet, AdditionalControlDataCollection, C_BOMWhereUsedHeader</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/C_MRPCTRLRBYAOR_SRV</t>
+          <t>/sap/opu/odata/sap/BOMWHEREUSED_SRV</t>
         </is>
       </c>
     </row>
@@ -27808,17 +27854,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>C_WORKCNTRGRPBYAOR_SRV</t>
+          <t>C_MRPCTRLRBYAOR_SRV</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>ZC_WORKCNTRGRPBYAOR_SRV</t>
+          <t>ZC_MRPCTRLRBYAOR_SRV</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Service Binding for WorkCenter Groups AOR</t>
+          <t>Service Binding C_MRPCtrlrByAreaOfRespy</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -27830,16 +27876,16 @@
         <v>1</v>
       </c>
       <c r="H398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>I_WorkCtrGrpByAreaOfRespyTP</t>
+          <t>I_MRPAreaOfResponsibilityTP</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/C_WORKCNTRGRPBYAOR_SRV</t>
+          <t>/sap/opu/odata/sap/C_MRPCTRLRBYAOR_SRV</t>
         </is>
       </c>
     </row>
@@ -27854,17 +27900,17 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
+          <t>C_WORKCNTRGRPBYAOR_SRV</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
+          <t>ZC_WORKCNTRGRPBYAOR_SRV</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Manage Event-Based Posting Errors</t>
+          <t>Service Binding for WorkCenter Groups AOR</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -27873,19 +27919,19 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H399" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>AnalysisResultCollection, PostingResultCollection</t>
+          <t>I_WorkCtrGrpByAreaOfRespyTP</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_EB_PRODN_COST_ERROR_SRV</t>
+          <t>/sap/opu/odata/sap/C_WORKCNTRGRPBYAOR_SRV</t>
         </is>
       </c>
     </row>
@@ -27900,17 +27946,17 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
+          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>ZFCO_PRODUCTION_COST_ANALYSIS_SRV</t>
+          <t>FCO_EB_PRODN_COST_ERROR_SRV</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Production Cost Analysis</t>
+          <t>Manage Event-Based Posting Errors</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -27919,19 +27965,19 @@
         </is>
       </c>
       <c r="G400" t="n">
+        <v>2</v>
+      </c>
+      <c r="H400" t="n">
         <v>5</v>
       </c>
-      <c r="H400" t="n">
-        <v>0</v>
-      </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>FilterBarCollection, FiscalYearPeriodCollection, ContactInformationCollection, FeatureToggleStatusCollection, C_ExceptionBaseRule</t>
+          <t>AnalysisResultCollection, PostingResultCollection</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
+          <t>/sap/opu/odata/sap/FCO_EB_PRODN_COST_ERROR_SRV</t>
         </is>
       </c>
     </row>
@@ -27946,17 +27992,17 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>FCO_WORKCENTER_COST_SRV</t>
+          <t>FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>ZFCO_WORKCENTER_COST_SRV</t>
+          <t>ZFCO_PRODUCTION_COST_ANALYSIS_SRV</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Analyze Cost by Work Center/Operation</t>
+          <t>Production Cost Analysis</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -27965,19 +28011,19 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>FiscalYearPeriodCollection, LaunchpadKPICollection</t>
+          <t>FilterBarCollection, FiscalYearPeriodCollection, ContactInformationCollection, FeatureToggleStatusCollection, C_ExceptionBaseRule</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_WORKCENTER_COST_SRV</t>
+          <t>/sap/opu/odata/sap/FCO_PRODUCTION_COST_ANALYSIS_SRV</t>
         </is>
       </c>
     </row>
@@ -27992,17 +28038,17 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>LO_VCHCLF</t>
+          <t>FCO_WORKCENTER_COST_SRV</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF</t>
+          <t>ZFCO_WORKCENTER_COST_SRV</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Variant Configuration and Classification Service</t>
+          <t>Analyze Cost by Work Center/Operation</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -28011,19 +28057,19 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H402" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>FiscalYearPeriodCollection, LaunchpadKPICollection</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF</t>
+          <t>/sap/opu/odata/sap/FCO_WORKCENTER_COST_SRV</t>
         </is>
       </c>
     </row>
@@ -28038,17 +28084,17 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
+          <t>LO_VCHCLF</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
+          <t>ZLO_VCHCLF</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Project for Key User Application</t>
+          <t>Variant Configuration and Classification Service</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -28057,19 +28103,19 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H403" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>C_ChFiExCharcAllocTP</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF</t>
         </is>
       </c>
     </row>
@@ -28084,17 +28130,17 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
+          <t>LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
+          <t>ZLO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Legacy appl. integration helper service for VCHCLF</t>
+          <t>Project for Key User Application</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -28103,19 +28149,19 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H404" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ChFiExCharcAllocTP</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_CFE_KEYUSERAPP_SRV</t>
         </is>
       </c>
     </row>
@@ -28130,17 +28176,17 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
+          <t>LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
+          <t>ZLO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Variant Configuration Assign Characteristic Group to Profile</t>
+          <t>Legacy appl. integration helper service for VCHCLF</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -28149,19 +28195,19 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H405" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>C_ConfignPrflCharcGroupAllocTP, C_ConfigurationProfileTP</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_INTEGRATION_LEGACY_SRV</t>
         </is>
       </c>
     </row>
@@ -28176,17 +28222,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>LO_VCHCLF_SIMULATION_SRV</t>
+          <t>LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>ZLO_VCHCLF_SIMULATION_SRV</t>
+          <t>ZLO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>VCH Simulation Environment</t>
+          <t>Variant Configuration Assign Characteristic Group to Profile</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -28195,19 +28241,19 @@
         </is>
       </c>
       <c r="G406" t="n">
+        <v>2</v>
+      </c>
+      <c r="H406" t="n">
         <v>4</v>
       </c>
-      <c r="H406" t="n">
-        <v>38</v>
-      </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>C_VariantConfigurationSimlnTP, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ConfignPrflCharcGroupAllocTP, C_ConfigurationProfileTP</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LO_VCHCLF_SIMULATION_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_PROFILE_ASSIGN_GROUP_SRV</t>
         </is>
       </c>
     </row>
@@ -28222,17 +28268,17 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>MPEACTIONSETTING_SRV</t>
+          <t>LO_VCHCLF_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>ZMPEACTIONSETTING_SRV</t>
+          <t>ZLO_VCHCLF_SIMULATION_SRV</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>MPE Action Setting</t>
+          <t>VCH Simulation Environment</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -28241,19 +28287,19 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H407" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>C_AddlRsnCodeGrpForMfgActnTP, C_MfgActionSettingTP, C_MfgActnHandlerToActnSttgTP</t>
+          <t>C_VariantConfigurationSimlnTP, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPEACTIONSETTING_SRV</t>
+          <t>/sap/opu/odata/sap/LO_VCHCLF_SIMULATION_SRV</t>
         </is>
       </c>
     </row>
@@ -28268,17 +28314,17 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>MPE_BUYOFFCYCLE_SRV</t>
+          <t>MPEACTIONSETTING_SRV</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>ZMPE_BUYOFFCYCLE_SRV</t>
+          <t>ZMPEACTIONSETTING_SRV</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>oData service for Buy Off Cycle</t>
+          <t>MPE Action Setting</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -28287,19 +28333,19 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H408" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>C_MfgBuyOffList</t>
+          <t>C_AddlRsnCodeGrpForMfgActnTP, C_MfgActionSettingTP, C_MfgActnHandlerToActnSttgTP</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_BUYOFFCYCLE_SRV</t>
+          <t>/sap/opu/odata/sap/MPEACTIONSETTING_SRV</t>
         </is>
       </c>
     </row>
@@ -28314,17 +28360,17 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>MPE_EXEC_RR_SRV</t>
+          <t>MPE_BUYOFFCYCLE_SRV</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>ZMPE_EXEC_RR_SRV</t>
+          <t>ZMPE_BUYOFFCYCLE_SRV</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Odata Service for Result Recording</t>
+          <t>oData service for Buy Off Cycle</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -28333,19 +28379,19 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H409" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>C_MfgOrdInspCharResultRec, C_MfgOrdPlanInspCharInfo, C_OpActyInstceInspCharcInfo, C_OpActyInstceInspCharcSqnc, C_SFIAtOpActyInspCharcInfo, C_SFIPlanInspCharInfo, C_SFIPlanInspCharResultRec</t>
+          <t>C_MfgBuyOffList</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_EXEC_RR_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_BUYOFFCYCLE_SRV</t>
         </is>
       </c>
     </row>
@@ -28360,17 +28406,17 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>MPE_MANAGE_PRODVER_SRV</t>
+          <t>MPE_EXEC_RR_SRV</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>ZMPE_MANAGE_PRODVER_SRV</t>
+          <t>ZMPE_EXEC_RR_SRV</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Manage Production Version</t>
+          <t>Odata Service for Result Recording</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -28379,19 +28425,19 @@
         </is>
       </c>
       <c r="G410" t="n">
+        <v>7</v>
+      </c>
+      <c r="H410" t="n">
         <v>2</v>
       </c>
-      <c r="H410" t="n">
-        <v>7</v>
-      </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>C_ProdnVersObjPgTP, C_ProdnVersRtgBOMVersObjPgTP</t>
+          <t>C_MfgOrdInspCharResultRec, C_MfgOrdPlanInspCharInfo, C_OpActyInstceInspCharcInfo, C_OpActyInstceInspCharcSqnc, C_SFIAtOpActyInspCharcInfo, C_SFIPlanInspCharInfo, C_SFIPlanInspCharResultRec</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_MANAGE_PRODVER_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_EXEC_RR_SRV</t>
         </is>
       </c>
     </row>
@@ -28406,17 +28452,17 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>MPE_OA_EXECUTION_SRV</t>
+          <t>MPE_MANAGE_PRODVER_SRV</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>ZMPE_OA_EXECUTION_SRV</t>
+          <t>ZMPE_MANAGE_PRODVER_SRV</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Operation Activity Execution</t>
+          <t>Manage Production Version</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -28425,19 +28471,19 @@
         </is>
       </c>
       <c r="G411" t="n">
+        <v>2</v>
+      </c>
+      <c r="H411" t="n">
         <v>7</v>
       </c>
-      <c r="H411" t="n">
-        <v>69</v>
-      </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>C_MfgOrderDefect, C_MfgOrderDefectRecord, UnplannedInspectionCharHtmlReturnCollect, UnplannedCompHtmlReturnCollection, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_ProdnVersObjPgTP, C_ProdnVersRtgBOMVersObjPgTP</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_OA_EXECUTION_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_MANAGE_PRODVER_SRV</t>
         </is>
       </c>
     </row>
@@ -28452,17 +28498,17 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>MPE_PRODORDER_OBJPG_SRV</t>
+          <t>MPE_OA_EXECUTION_SRV</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>ZMPE_PRODORDER_OBJPG_SRV</t>
+          <t>ZMPE_OA_EXECUTION_SRV</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Production Order Object Page SEGW Project</t>
+          <t>Operation Activity Execution</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -28471,19 +28517,19 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H412" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_MfgOrderDefect, C_MfgOrderDefectRecord, UnplannedInspectionCharHtmlReturnCollect, UnplannedCompHtmlReturnCollection, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_PRODORDER_OBJPG_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_OA_EXECUTION_SRV</t>
         </is>
       </c>
     </row>
@@ -28498,17 +28544,17 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>MPE_QUALIFICATIONS_SRV</t>
+          <t>MPE_PRODORDER_OBJPG_SRV</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>ZMPE_QUALIFICATIONS_SRV</t>
+          <t>ZMPE_PRODORDER_OBJPG_SRV</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>oData for HR Qualification Assignment</t>
+          <t>Production Order Object Page SEGW Project</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -28517,19 +28563,19 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H413" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>C_MfgQualifnMaterialAssgmtTP, C_MfgQualifnWrkCtrAssgmtTP</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_QUALIFICATIONS_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_PRODORDER_OBJPG_SRV</t>
         </is>
       </c>
     </row>
@@ -28544,17 +28590,17 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PLMI_PROCESS_ROUTE</t>
+          <t>MPE_QUALIFICATIONS_SRV</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>ZPLMI_PROCESS_ROUTE</t>
+          <t>ZMPE_QUALIFICATIONS_SRV</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Service for Process Route</t>
+          <t>oData for HR Qualification Assignment</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -28563,19 +28609,19 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H414" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>ProcessRouteDdlnRecipient, ProcessRouteObjAssignment, ProcessRouteTask, ProcessRouteTaskDcsnDSgntr, ProcessRouteTaskDecision, ProcessRouteTaskNote</t>
+          <t>C_MfgQualifnMaterialAssgmtTP, C_MfgQualifnWrkCtrAssgmtTP</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PLMI_PROCESS_ROUTE</t>
+          <t>/sap/opu/odata/sap/MPE_QUALIFICATIONS_SRV</t>
         </is>
       </c>
     </row>
@@ -28590,17 +28636,17 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>PLMI_RECIPE_FINDER</t>
+          <t>PLMI_PROCESS_ROUTE</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>ZPLMI_RECIPE_FINDER</t>
+          <t>ZPLMI_PROCESS_ROUTE</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Recipe Finder</t>
+          <t>Service for Process Route</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -28609,19 +28655,19 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H415" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>RecipeFinderCaches</t>
+          <t>ProcessRouteDdlnRecipient, ProcessRouteObjAssignment, ProcessRouteTask, ProcessRouteTaskDcsnDSgntr, ProcessRouteTaskDecision, ProcessRouteTaskNote</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PLMI_RECIPE_FINDER</t>
+          <t>/sap/opu/odata/sap/PLMI_PROCESS_ROUTE</t>
         </is>
       </c>
     </row>
@@ -28636,17 +28682,17 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>PLMI_SYNCUNITR2B_MANAGE</t>
+          <t>PLMI_RECIPE_FINDER</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>ZPLMI_SYNCUNITR2B_MANAGE</t>
+          <t>ZPLMI_RECIPE_FINDER</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Manage R2B Synchronization Units</t>
+          <t>Recipe Finder</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -28658,16 +28704,16 @@
         <v>1</v>
       </c>
       <c r="H416" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>I_BillOfMaterialTP</t>
+          <t>RecipeFinderCaches</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PLMI_SYNCUNITR2B_MANAGE</t>
+          <t>/sap/opu/odata/sap/PLMI_RECIPE_FINDER</t>
         </is>
       </c>
     </row>
@@ -28682,17 +28728,17 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>PMRP_FLXBLCSTRT_UI_SERVICE</t>
+          <t>PLMI_SYNCUNITR2B_MANAGE</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>ZPMRP_FLXBLCSTRT_UI_SERVICE</t>
+          <t>ZPLMI_SYNCUNITR2B_MANAGE</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Service for Flexible Constraint</t>
+          <t>Manage R2B Synchronization Units</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -28701,19 +28747,19 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H417" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>C_PMRPFlexibleConstraintPeriod, C_PMRPFlexibleConstraintText, C_PMRPFlxblConstraintProduct</t>
+          <t>I_BillOfMaterialTP</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PMRP_FLXBLCSTRT_UI_SERVICE</t>
+          <t>/sap/opu/odata/sap/PLMI_SYNCUNITR2B_MANAGE</t>
         </is>
       </c>
     </row>
@@ -28728,17 +28774,17 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>PMRP_RECEIPT_SERVICE</t>
+          <t>PMRP_FLXBLCSTRT_UI_SERVICE</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>ZPMRP_RECEIPT_SERVICE</t>
+          <t>ZPMRP_FLXBLCSTRT_UI_SERVICE</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>RAP: PMRP_RECEIPT_SERVICE generated at 20190415</t>
+          <t>Service for Flexible Constraint</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -28747,19 +28793,19 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H418" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>PMRPReceiptItem</t>
+          <t>C_PMRPFlexibleConstraintPeriod, C_PMRPFlexibleConstraintText, C_PMRPFlxblConstraintProduct</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PMRP_RECEIPT_SERVICE</t>
+          <t>/sap/opu/odata/sap/PMRP_FLXBLCSTRT_UI_SERVICE</t>
         </is>
       </c>
     </row>
@@ -28774,17 +28820,17 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>PMRP_SIMULATION_SERVICE</t>
+          <t>PMRP_RECEIPT_SERVICE</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>ZPMRP_SIMULATION_SERVICE</t>
+          <t>ZPMRP_RECEIPT_SERVICE</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>RAP: PMRP_SIMULATION_SERVICE generated at 20181203</t>
+          <t>RAP: PMRP_RECEIPT_SERVICE generated at 20190415</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -28796,16 +28842,16 @@
         <v>1</v>
       </c>
       <c r="H419" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>PMRPSimulationText</t>
+          <t>PMRPReceiptItem</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PMRP_SIMULATION_SERVICE</t>
+          <t>/sap/opu/odata/sap/PMRP_RECEIPT_SERVICE</t>
         </is>
       </c>
     </row>
@@ -28820,17 +28866,17 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PPDS_CAPA_UTIL_OBJ_SRV</t>
+          <t>PMRP_SIMULATION_SERVICE</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>ZPPDS_CAPA_UTIL_OBJ_SRV</t>
+          <t>ZPMRP_SIMULATION_SERVICE</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Capacity Utilization Object Page</t>
+          <t>RAP: PMRP_SIMULATION_SERVICE generated at 20181203</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -28842,16 +28888,16 @@
         <v>1</v>
       </c>
       <c r="H420" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>DowntimesSet</t>
+          <t>PMRPSimulationText</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PPDS_CAPA_UTIL_OBJ_SRV</t>
+          <t>/sap/opu/odata/sap/PMRP_SIMULATION_SERVICE</t>
         </is>
       </c>
     </row>
@@ -28866,17 +28912,17 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>PP_CFS_CAPEVAL_SRV</t>
+          <t>PPDS_CAPA_UTIL_OBJ_SRV</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>ZPP_CFS_CAPEVAL_SRV</t>
+          <t>ZPPDS_CAPA_UTIL_OBJ_SRV</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Production Planning: Capacity Evaluation App</t>
+          <t>Capacity Utilization Object Page</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -28885,19 +28931,19 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H421" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>RescheduleCollection, C_WorkCenterCapOverviewTP, C_WrkCtrAvailableCapacityTP, C_WrkCtrCapShiftIntervalTP</t>
+          <t>DowntimesSet</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_CFS_CAPEVAL_SRV</t>
+          <t>/sap/opu/odata/sap/PPDS_CAPA_UTIL_OBJ_SRV</t>
         </is>
       </c>
     </row>
@@ -28912,17 +28958,17 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PP_DD_BUFPOS_SRV</t>
+          <t>PP_CFS_CAPEVAL_SRV</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>ZPP_DD_BUFPOS_SRV</t>
+          <t>ZPP_CFS_CAPEVAL_SRV</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>OData DDR: Buffer Positioning</t>
+          <t>Production Planning: Capacity Evaluation App</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -28931,19 +28977,19 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H422" t="n">
         <v>9</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>MassActionCollection, ChangeDDScopeActnSet, C_ProdBufPositioningTP</t>
+          <t>RescheduleCollection, C_WorkCenterCapOverviewTP, C_WrkCtrAvailableCapacityTP, C_WrkCtrCapShiftIntervalTP</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_BUFPOS_SRV</t>
+          <t>/sap/opu/odata/sap/PP_CFS_CAPEVAL_SRV</t>
         </is>
       </c>
     </row>
@@ -28958,17 +29004,17 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PP_DD_MASSADJBUF_SRV</t>
+          <t>PP_DD_BUFPOS_SRV</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>ZPP_DD_MASSADJBUF_SRV</t>
+          <t>ZPP_DD_BUFPOS_SRV</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>OData PP: Mass Adjust Buffers</t>
+          <t>OData DDR: Buffer Positioning</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -28977,19 +29023,19 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H423" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>MassAdjiustActionSet</t>
+          <t>MassActionCollection, ChangeDDScopeActnSet, C_ProdBufPositioningTP</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_MASSADJBUF_SRV</t>
+          <t>/sap/opu/odata/sap/PP_DD_BUFPOS_SRV</t>
         </is>
       </c>
     </row>
@@ -29004,17 +29050,17 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PP_DD_STLM_SRV</t>
+          <t>PP_DD_MASSADJBUF_SRV</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>ZPP_DD_STLM_SRV</t>
+          <t>ZPP_DD_MASSADJBUF_SRV</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Odata DDR: Manage Buffer Levels</t>
+          <t>OData PP: Mass Adjust Buffers</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -29023,19 +29069,19 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H424" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>MassAdjiustActionSet, BufLvlActionsCollection, C_ProdBufLvlDmndAdjmtFctrTP, C_ProdBufLvlZnAdjmtFctrTP, C_ProductBufferLevelChartTP, C_ProductBufferLevelMgmtTP, C_ProductDailyDemandChartTP</t>
+          <t>MassAdjiustActionSet</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_DD_STLM_SRV</t>
+          <t>/sap/opu/odata/sap/PP_DD_MASSADJBUF_SRV</t>
         </is>
       </c>
     </row>
@@ -29050,17 +29096,17 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PP_MNTR_WRKCTR_SRV</t>
+          <t>PP_DD_STLM_SRV</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>ZPP_MNTR_WRKCTR_SRV</t>
+          <t>ZPP_DD_STLM_SRV</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Monitor Work Center Schedules</t>
+          <t>Odata DDR: Manage Buffer Levels</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -29069,19 +29115,19 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H425" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
+          <t>MassAdjiustActionSet, BufLvlActionsCollection, C_ProdBufLvlDmndAdjmtFctrTP, C_ProdBufLvlZnAdjmtFctrTP, C_ProductBufferLevelChartTP, C_ProductBufferLevelMgmtTP, C_ProductDailyDemandChartTP</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MNTR_WRKCTR_SRV</t>
+          <t>/sap/opu/odata/sap/PP_DD_STLM_SRV</t>
         </is>
       </c>
     </row>
@@ -29096,17 +29142,17 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PP_MPE_OPER_MANAGE</t>
+          <t>PP_MNTR_WRKCTR_SRV</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>ZPP_MPE_OPER_MANAGE</t>
+          <t>ZPP_MNTR_WRKCTR_SRV</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Manage Operations</t>
+          <t>Monitor Work Center Schedules</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -29115,19 +29161,19 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H426" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>C_MfgOrderDefectRecord</t>
+          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MPE_OPER_MANAGE</t>
+          <t>/sap/opu/odata/sap/PP_MNTR_WRKCTR_SRV</t>
         </is>
       </c>
     </row>
@@ -29142,17 +29188,17 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PP_MPE_ORDER_MANAGE</t>
+          <t>PP_MPE_OPER_MANAGE</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>ZPP_MPE_ORDER_MANAGE</t>
+          <t>ZPP_MPE_OPER_MANAGE</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Manage Orders</t>
+          <t>Manage Operations</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -29161,19 +29207,19 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H427" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_MfgOrderDefectRecord</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MPE_ORDER_MANAGE</t>
+          <t>/sap/opu/odata/sap/PP_MPE_OPER_MANAGE</t>
         </is>
       </c>
     </row>
@@ -29188,17 +29234,17 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PP_MRP_COCKPIT_SRV</t>
+          <t>PP_MPE_ORDER_MANAGE</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>ZPP_MRP_COCKPIT_SRV</t>
+          <t>ZPP_MPE_ORDER_MANAGE</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>MRP Cockpit</t>
+          <t>Manage Orders</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -29207,19 +29253,19 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H428" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>ChangeRequestProposals, ChangeRequestEMailTextCollection, ChangeRequests, SchedAgmtReleaseListItems, MMPurchaseOrderScheduleLines</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_MRP_COCKPIT_SRV</t>
+          <t>/sap/opu/odata/sap/PP_MPE_ORDER_MANAGE</t>
         </is>
       </c>
     </row>
@@ -29234,17 +29280,17 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PP_PROCESS_ORDER_MANAGE_SRV</t>
+          <t>PP_MRP_COCKPIT_SRV</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>ZPP_PROCESS_ORDER_MANAGE_SRV</t>
+          <t>ZPP_MRP_COCKPIT_SRV</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Manage Process Orders</t>
+          <t>MRP Cockpit</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -29253,19 +29299,19 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H429" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>C_PROC_ORD_MNG_GET_ENTITYSET</t>
+          <t>ChangeRequestProposals, ChangeRequestEMailTextCollection, ChangeRequests, SchedAgmtReleaseListItems, MMPurchaseOrderScheduleLines</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_PROCESS_ORDER_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/PP_MRP_COCKPIT_SRV</t>
         </is>
       </c>
     </row>
@@ -29280,17 +29326,17 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PP_SCHEDULEPRODUCTION_SRV</t>
+          <t>PP_PROCESS_ORDER_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>ZPP_SCHEDULEPRODUCTION_SRV</t>
+          <t>ZPP_PROCESS_ORDER_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Schedule Production</t>
+          <t>Manage Process Orders</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -29299,19 +29345,19 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H430" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
+          <t>C_PROC_ORD_MNG_GET_ENTITYSET</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_SCHEDULEPRODUCTION_SRV</t>
+          <t>/sap/opu/odata/sap/PP_PROCESS_ORDER_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -29326,17 +29372,17 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>PP_WORKCENTER_GROUP_SRV</t>
+          <t>PP_SCHEDULEPRODUCTION_SRV</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>ZPP_WORKCENTER_GROUP_SRV</t>
+          <t>ZPP_SCHEDULEPRODUCTION_SRV</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Manage Work Center Groups</t>
+          <t>Schedule Production</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -29345,19 +29391,19 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H431" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>WRKCTRGRPEDITFLAGCollection</t>
+          <t>IndustryTypeForAORCollection, UserSettingsCollection</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/PP_WORKCENTER_GROUP_SRV</t>
+          <t>/sap/opu/odata/sap/PP_SCHEDULEPRODUCTION_SRV</t>
         </is>
       </c>
     </row>
@@ -29372,17 +29418,17 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>UI_PRODUCTIONVERSION</t>
+          <t>PP_WORKCENTER_GROUP_SRV</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>ZUI_PRODUCTIONVERSION</t>
+          <t>ZPP_WORKCENTER_GROUP_SRV</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Odata Service for Production Version</t>
+          <t>Manage Work Center Groups</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -29391,19 +29437,19 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H432" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>ProdnVersConsistencyLog, ProductionVersion, RecmddProductionVersion</t>
+          <t>WRKCTRGRPEDITFLAGCollection</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_PRODUCTIONVERSION</t>
+          <t>/sap/opu/odata/sap/PP_WORKCENTER_GROUP_SRV</t>
         </is>
       </c>
     </row>
@@ -29418,17 +29464,17 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>UI_VARCNFCHARCEXCLMAN</t>
+          <t>UI_PRODUCTIONVERSION</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>ZUI_VARCNFCHARCEXCLMAN</t>
+          <t>ZUI_PRODUCTIONVERSION</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Manage Cstic Exclusion App V2</t>
+          <t>Odata Service for Production Version</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -29437,19 +29483,19 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H433" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>C_VarCnfExclCharcDetail</t>
+          <t>ProdnVersConsistencyLog, ProductionVersion, RecmddProductionVersion</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_VARCNFCHARCEXCLMAN</t>
+          <t>/sap/opu/odata/sap/UI_PRODUCTIONVERSION</t>
         </is>
       </c>
     </row>
@@ -29464,17 +29510,17 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>UI_WORKCENTERCAPLIST_02</t>
+          <t>UI_VARCNFCHARCEXCLMAN</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>ZUI_WORKCENTERCAPLIST_02</t>
+          <t>ZUI_VARCNFCHARCEXCLMAN</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Odata Service for Work Center Capacity</t>
+          <t>Manage Cstic Exclusion App V2</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -29483,19 +29529,19 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>CapCtrlrCapacityHeader, CapCtrlrCapacityList, CapCtrlrIntervalShifts</t>
+          <t>C_VarCnfExclCharcDetail</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_WORKCENTERCAPLIST_02</t>
+          <t>/sap/opu/odata/sap/UI_VARCNFCHARCEXCLMAN</t>
         </is>
       </c>
     </row>
@@ -29505,22 +29551,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PS - Projects</t>
+          <t>PP - Production</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>CA_RSM_TEAM_ACTION_SRV</t>
+          <t>UI_WORKCENTERCAPLIST_02</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>ZCA_RSM_TEAM_ACTION_SRV</t>
+          <t>ZUI_WORKCENTERCAPLIST_02</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Project for Manage Teams And Responsibilities</t>
+          <t>Odata Service for Work Center Capacity</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -29529,19 +29575,19 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H435" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>RSM_SEARCHSet</t>
+          <t>CapCtrlrCapacityHeader, CapCtrlrCapacityList, CapCtrlrIntervalShifts</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CA_RSM_TEAM_ACTION_SRV</t>
+          <t>/sap/opu/odata/sap/UI_WORKCENTERCAPLIST_02</t>
         </is>
       </c>
     </row>
@@ -29556,17 +29602,17 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CA_RSM_TEAM_SRV</t>
+          <t>CA_RSM_TEAM_ACTION_SRV</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>ZCA_RSM_TEAM_SRV</t>
+          <t>ZCA_RSM_TEAM_ACTION_SRV</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Project for Maintain Teams as Responsible</t>
+          <t>Project for Manage Teams And Responsibilities</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -29575,19 +29621,19 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H436" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>MASS_MEMBER_CHANGESet, C_RespyMgmtTeamAttributeTP, C_RespyMgmtTeamHeaderTP, C_RespyMgmtTeamMbrFuncTP, C_RespyMgmtTeamMemberTP, C_RespyMgmtTeamOrgUnitTP, C_RespyMgmtTeamOwnerTP</t>
+          <t>RSM_SEARCHSet</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CA_RSM_TEAM_SRV</t>
+          <t>/sap/opu/odata/sap/CA_RSM_TEAM_ACTION_SRV</t>
         </is>
       </c>
     </row>
@@ -29602,17 +29648,17 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
+          <t>CA_RSM_TEAM_SRV</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
+          <t>ZCA_RSM_TEAM_SRV</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Master Project Overview</t>
+          <t>Project for Maintain Teams as Responsible</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -29621,19 +29667,19 @@
         </is>
       </c>
       <c r="G437" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H437" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>I_ServiceEntrySheetItem</t>
+          <t>MASS_MEMBER_CHANGESet, C_RespyMgmtTeamAttributeTP, C_RespyMgmtTeamHeaderTP, C_RespyMgmtTeamMbrFuncTP, C_RespyMgmtTeamMemberTP, C_RespyMgmtTeamOrgUnitTP, C_RespyMgmtTeamOwnerTP</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CPD_MASTERPROJECT_OVERVIEW_SRV</t>
+          <t>/sap/opu/odata/sap/CA_RSM_TEAM_SRV</t>
         </is>
       </c>
     </row>
@@ -29643,22 +29689,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>QM - Quality</t>
+          <t>PS - Projects</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>CMD_QLTY_MANAGE_IMPORTS</t>
+          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>ZCMD_QLTY_MANAGE_IMPORTS</t>
+          <t>CPD_MASTERPROJECT_OVERVIEW_SRV</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Master Data Quality - oData Service for Manage Imports</t>
+          <t>Master Project Overview</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -29674,12 +29720,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>ImportUUIDsTypeCollection</t>
+          <t>I_ServiceEntrySheetItem</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/CMD_QLTY_MANAGE_IMPORTS</t>
+          <t>/sap/opu/odata/sap/CPD_MASTERPROJECT_OVERVIEW_SRV</t>
         </is>
       </c>
     </row>
@@ -29694,17 +29740,17 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
+          <t>CMD_QLTY_MANAGE_IMPORTS</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
+          <t>ZCMD_QLTY_MANAGE_IMPORTS</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Inspect WIP/Variance Posting</t>
+          <t>Master Data Quality - oData Service for Manage Imports</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -29713,19 +29759,19 @@
         </is>
       </c>
       <c r="G439" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H439" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>ErrorNumberCollection, PostingResultCollection, FiscalYearPeriodCollection, DateCollection</t>
+          <t>ImportUUIDsTypeCollection</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FCO_EBW_ORDER_INSPECTOR_SRV</t>
+          <t>/sap/opu/odata/sap/CMD_QLTY_MANAGE_IMPORTS</t>
         </is>
       </c>
     </row>
@@ -29740,17 +29786,17 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>MPE_EXEC_NON_CONFORMANCE_SRV</t>
+          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>ZMPE_EXEC_NON_CONFORMANCE_SRV</t>
+          <t>FCO_EBW_ORDER_INSPECTOR_SRV</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>oData service for defect recording</t>
+          <t>Inspect WIP/Variance Posting</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -29759,19 +29805,19 @@
         </is>
       </c>
       <c r="G440" t="n">
+        <v>4</v>
+      </c>
+      <c r="H440" t="n">
         <v>2</v>
       </c>
-      <c r="H440" t="n">
-        <v>1</v>
-      </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>AttachmentContentSet, C_MfgOrderDefect</t>
+          <t>ErrorNumberCollection, PostingResultCollection, FiscalYearPeriodCollection, DateCollection</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/MPE_EXEC_NON_CONFORMANCE_SRV</t>
+          <t>/sap/opu/odata/sap/FCO_EBW_ORDER_INSPECTOR_SRV</t>
         </is>
       </c>
     </row>
@@ -29786,17 +29832,17 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>QM_DEFECT_RECORD_SRV</t>
+          <t>MPE_EXEC_NON_CONFORMANCE_SRV</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>ZQM_DEFECT_RECORD_SRV</t>
+          <t>ZMPE_EXEC_NON_CONFORMANCE_SRV</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Record Defects</t>
+          <t>oData service for defect recording</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -29805,19 +29851,19 @@
         </is>
       </c>
       <c r="G441" t="n">
+        <v>2</v>
+      </c>
+      <c r="H441" t="n">
         <v>1</v>
       </c>
-      <c r="H441" t="n">
-        <v>43</v>
-      </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>C_DefectRecord</t>
+          <t>AttachmentContentSet, C_MfgOrderDefect</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_DEFECT_RECORD_SRV</t>
+          <t>/sap/opu/odata/sap/MPE_EXEC_NON_CONFORMANCE_SRV</t>
         </is>
       </c>
     </row>
@@ -29832,17 +29878,17 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>QM_FMEA_MNG_SRV</t>
+          <t>QM_DEFECT_RECORD_SRV</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>ZQM_FMEA_MNG_SRV</t>
+          <t>ZQM_DEFECT_RECORD_SRV</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Manage FMEA</t>
+          <t>Record Defects</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -29851,19 +29897,19 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H442" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>C_FMEAMng, C_FMEAMngCauseTask, C_FMEAMngNode, C_FMEAMngNodeText</t>
+          <t>C_DefectRecord</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_FMEA_MNG_SRV</t>
+          <t>/sap/opu/odata/sap/QM_DEFECT_RECORD_SRV</t>
         </is>
       </c>
     </row>
@@ -29878,17 +29924,17 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>QM_INFOREC_PROC_MANAGE_SRV</t>
+          <t>QM_FMEA_MNG_SRV</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>ZQM_INFOREC_PROC_MANAGE_SRV</t>
+          <t>ZQM_FMEA_MNG_SRV</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>OData QM: Manage Quality Info Records</t>
+          <t>Manage FMEA</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -29897,19 +29943,19 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H443" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>C_QltyFirstArticleInsp, C_QltyInProcurementManage</t>
+          <t>C_FMEAMng, C_FMEAMngCauseTask, C_FMEAMngNode, C_FMEAMngNodeText</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INFOREC_PROC_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_FMEA_MNG_SRV</t>
         </is>
       </c>
     </row>
@@ -29924,17 +29970,17 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>QM_INSPMETHOD_OBJECTPAGE_SRV</t>
+          <t>QM_INFOREC_PROC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>ZQM_INSPMETHOD_OBJECTPAGE_SRV</t>
+          <t>ZQM_INFOREC_PROC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>OData QM: Inspection Specification Object Page OData Service</t>
+          <t>OData QM: Manage Quality Info Records</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -29943,19 +29989,19 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H444" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_QltyFirstArticleInsp, C_QltyInProcurementManage</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSPMETHOD_OBJECTPAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INFOREC_PROC_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -29970,12 +30016,12 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>QM_INSPSPEC_OBJECTPAGE_SRV</t>
+          <t>QM_INSPMETHOD_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>ZQM_INSPSPEC_OBJECTPAGE_SRV</t>
+          <t>ZQM_INSPMETHOD_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -30001,7 +30047,7 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSPSPEC_OBJECTPAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSPMETHOD_OBJECTPAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30016,17 +30062,17 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>QM_INSPUSGDSC_MANAGE_SRV</t>
+          <t>QM_INSPSPEC_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>ZQM_INSPUSGDSC_MANAGE_SRV</t>
+          <t>ZQM_INSPSPEC_OBJECTPAGE_SRV</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>OData QM: Manage Usage Decision</t>
+          <t>OData QM: Inspection Specification Object Page OData Service</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -30035,19 +30081,19 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H446" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>C_InspUsgDesc</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSPUSGDSC_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSPSPEC_OBJECTPAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30062,17 +30108,17 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>QM_INSP_PLAN_SRV</t>
+          <t>QM_INSPUSGDSC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>ZQM_INSP_PLAN_SRV</t>
+          <t>ZQM_INSPUSGDSC_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Inspection Plan</t>
+          <t>OData QM: Manage Usage Decision</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -30081,19 +30127,19 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H447" t="n">
         <v>11</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>C_InspectionPlan, C_InspPlanDpndantCharc, C_InspPlanMatlAssgmt, C_InspPlanOpCharc, C_InspPlanOperation</t>
+          <t>C_InspUsgDesc</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_INSP_PLAN_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSPUSGDSC_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30108,17 +30154,17 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>QM_MLTPLRR_SRV</t>
+          <t>QM_INSP_PLAN_SRV</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>ZQM_MLTPLRR_SRV</t>
+          <t>ZQM_INSP_PLAN_SRV</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Record Multiple Results</t>
+          <t>Inspection Plan</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -30127,19 +30173,19 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H448" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>C_InspResultMltplRsltRec, C_InspRsltValueMltplRsltRec</t>
+          <t>C_InspectionPlan, C_InspPlanDpndantCharc, C_InspPlanMatlAssgmt, C_InspPlanOpCharc, C_InspPlanOperation</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_MLTPLRR_SRV</t>
+          <t>/sap/opu/odata/sap/QM_INSP_PLAN_SRV</t>
         </is>
       </c>
     </row>
@@ -30154,17 +30200,17 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>QM_QTASK_PROC_SRV</t>
+          <t>QM_MLTPLRR_SRV</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>ZQM_QTASK_PROC_SRV</t>
+          <t>ZQM_MLTPLRR_SRV</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Process Quality Tasks</t>
+          <t>Record Multiple Results</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -30173,19 +30219,19 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H449" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>C_QltyTskProcFllwActnTblParam, C_QualityTaskProcess, I_ChangeRecordBsc, I_ProbSolvingProcTP</t>
+          <t>C_InspResultMltplRsltRec, C_InspRsltValueMltplRsltRec</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_QTASK_PROC_SRV</t>
+          <t>/sap/opu/odata/sap/QM_MLTPLRR_SRV</t>
         </is>
       </c>
     </row>
@@ -30200,17 +30246,17 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>QM_RR_SRV</t>
+          <t>QM_QTASK_PROC_SRV</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>ZQM_RR_SRV</t>
+          <t>ZQM_QTASK_PROC_SRV</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>OData QM: Inspection Results Recording OData Service</t>
+          <t>Process Quality Tasks</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -30219,19 +30265,19 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H450" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>C_UnplndInspCharcRsltRecg, CharResultDetailsSet</t>
+          <t>C_QltyTskProcFllwActnTblParam, C_QualityTaskProcess, I_ChangeRecordBsc, I_ProbSolvingProcTP</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_RR_SRV</t>
+          <t>/sap/opu/odata/sap/QM_QTASK_PROC_SRV</t>
         </is>
       </c>
     </row>
@@ -30246,17 +30292,17 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>QM_SUBSET_RR_SRV</t>
+          <t>QM_RR_SRV</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>ZQM_SUBSET_RR_SRV</t>
+          <t>ZQM_RR_SRV</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Record Results for Inspection Points</t>
+          <t>OData QM: Inspection Results Recording OData Service</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -30265,19 +30311,19 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H451" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>C_InspSubsetCharcResult, C_InspSubsetResultValue, C_InspSubsetRsltRec</t>
+          <t>C_UnplndInspCharcRsltRecg, CharResultDetailsSet</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/QM_SUBSET_RR_SRV</t>
+          <t>/sap/opu/odata/sap/QM_RR_SRV</t>
         </is>
       </c>
     </row>
@@ -30292,17 +30338,17 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SIMDQ_SERVICES_SRV</t>
+          <t>QM_SUBSET_RR_SRV</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>ZSIMDQ_SERVICES_SRV</t>
+          <t>ZQM_SUBSET_RR_SRV</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Data Quality related services</t>
+          <t>Record Results for Inspection Points</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -30311,19 +30357,19 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H452" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>dqmmConfigCompleteResponseCollection, setCountryActiveCollection</t>
+          <t>C_InspSubsetCharcResult, C_InspSubsetResultValue, C_InspSubsetRsltRec</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SIMDQ_SERVICES_SRV</t>
+          <t>/sap/opu/odata/sap/QM_SUBSET_RR_SRV</t>
         </is>
       </c>
     </row>
@@ -30338,17 +30384,17 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>UI_INSPLOT_RSLTRECG</t>
+          <t>SIMDQ_SERVICES_SRV</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>ZUI_INSPLOT_RSLTRECG</t>
+          <t>ZSIMDQ_SERVICES_SRV</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Service Binding for inspection lot Result Recording</t>
+          <t>Data Quality related services</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -30357,19 +30403,19 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>InspChar, UnplannedCharacteristic, InspectionResultValue, InspectionLot</t>
+          <t>dqmmConfigCompleteResponseCollection, setCountryActiveCollection</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_INSPLOT_RSLTRECG</t>
+          <t>/sap/opu/odata/sap/SIMDQ_SERVICES_SRV</t>
         </is>
       </c>
     </row>
@@ -30379,22 +30425,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail (RFM)</t>
+          <t>QM - Quality</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>UI_RFM_ASSIGN_PROD_TO_DCS</t>
+          <t>UI_INSPLOT_RSLTRECG</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>ZUI_RFM_ASSIGN_PROD_TO_DCS</t>
+          <t>ZUI_INSPLOT_RSLTRECG</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Assign Product to Distribution Centers</t>
+          <t>Service Binding for inspection lot Result Recording</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -30403,19 +30449,19 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H454" t="n">
         <v>1</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>ProductDistrCtrListing</t>
+          <t>InspChar, UnplannedCharacteristic, InspectionResultValue, InspectionLot</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_ASSIGN_PROD_TO_DCS</t>
+          <t>/sap/opu/odata/sap/UI_INSPLOT_RSLTRECG</t>
         </is>
       </c>
     </row>
@@ -30430,17 +30476,17 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>UI_RFM_MNG_ASSTMT_MODULES</t>
+          <t>UI_RFM_ASSIGN_PROD_TO_DCS</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>ZUI_RFM_MNG_ASSTMT_MODULES</t>
+          <t>ZUI_RFM_ASSIGN_PROD_TO_DCS</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Manage Assortment Modules</t>
+          <t>Assign Product to Distribution Centers</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -30449,19 +30495,19 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H455" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>AssortmentModuleVersionText, AssortmentModuleText, AssortmentModule, AssortmentModuleVersion, AssortmentModuleUser, ProductToAssortmentModuleVers</t>
+          <t>ProductDistrCtrListing</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_MNG_ASSTMT_MODULES</t>
+          <t>/sap/opu/odata/sap/UI_RFM_ASSIGN_PROD_TO_DCS</t>
         </is>
       </c>
     </row>
@@ -30476,17 +30522,17 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>UI_RFM_POCNSLDTNRULE</t>
+          <t>UI_RFM_MNG_ASSTMT_MODULES</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>ZUI_RFM_POCNSLDTNRULE</t>
+          <t>ZUI_RFM_MNG_ASSTMT_MODULES</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Purchase Order Consolidation Rule</t>
+          <t>Manage Assortment Modules</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -30495,19 +30541,19 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H456" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>C_RFM_POCnsldtnRuleTP</t>
+          <t>AssortmentModuleVersionText, AssortmentModuleText, AssortmentModule, AssortmentModuleVersion, AssortmentModuleUser, ProductToAssortmentModuleVers</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_POCNSLDTNRULE</t>
+          <t>/sap/opu/odata/sap/UI_RFM_MNG_ASSTMT_MODULES</t>
         </is>
       </c>
     </row>
@@ -30522,17 +30568,17 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>UI_RFM_PROD_ASSGN_EXPL_ASM</t>
+          <t>UI_RFM_POCNSLDTNRULE</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>ZUI_RFM_PROD_ASSGN_EXPL_ASM</t>
+          <t>ZUI_RFM_POCNSLDTNRULE</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Service Binding for UI_RFM_PROD_ASSIGN_EXPL_ASM</t>
+          <t>Purchase Order Consolidation Rule</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -30544,16 +30590,16 @@
         <v>1</v>
       </c>
       <c r="H457" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>ProdToExplicitAsstmtMdl</t>
+          <t>C_RFM_POCnsldtnRuleTP</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_PROD_ASSGN_EXPL_ASM</t>
+          <t>/sap/opu/odata/sap/UI_RFM_POCNSLDTNRULE</t>
         </is>
       </c>
     </row>
@@ -30568,17 +30614,17 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>UI_RFM_SUPPLY_SORTRULE</t>
+          <t>UI_RFM_PROD_ASSGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>ZUI_RFM_SUPPLY_SORTRULE</t>
+          <t>ZUI_RFM_PROD_ASSGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>RAP: UI_RFM_SUPPLY_SORTRULE generated at 20190314</t>
+          <t>Service Binding for UI_RFM_PROD_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -30587,19 +30633,19 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H458" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>ArunStockSortDynAttrib, ARunSupplySortRule, ArunStockSortStaticAttrib, ArunStockSortStaticAtribVal</t>
+          <t>ProdToExplicitAsstmtMdl</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_SUPPLY_SORTRULE</t>
+          <t>/sap/opu/odata/sap/UI_RFM_PROD_ASSGN_EXPL_ASM</t>
         </is>
       </c>
     </row>
@@ -30614,17 +30660,17 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>UI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>UI_RFM_SUPPLY_SORTRULE</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>ZUI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>ZUI_RFM_SUPPLY_SORTRULE</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Service Binding for UI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>RAP: UI_RFM_SUPPLY_SORTRULE generated at 20190314</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -30633,19 +30679,19 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H459" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>UserToExplicitAsstmtMdl</t>
+          <t>ArunStockSortDynAttrib, ARunSupplySortRule, ArunStockSortStaticAttrib, ArunStockSortStaticAtribVal</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_RFM_USR_ASSIGN_EXPL_ASM</t>
+          <t>/sap/opu/odata/sap/UI_RFM_SUPPLY_SORTRULE</t>
         </is>
       </c>
     </row>
@@ -30655,22 +30701,22 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>SD - Sales</t>
+          <t>Retail (RFM)</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>FINS_TRR_PECRUN_SALES_SRV</t>
+          <t>UI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>ZFINS_TRR_PECRUN_SALES_SRV</t>
+          <t>ZUI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Odata service for Manage Revenue Recognition - sales</t>
+          <t>Service Binding for UI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -30682,16 +30728,16 @@
         <v>1</v>
       </c>
       <c r="H460" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>ErrorNumberCollection</t>
+          <t>UserToExplicitAsstmtMdl</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/FINS_TRR_PECRUN_SALES_SRV</t>
+          <t>/sap/opu/odata/sap/UI_RFM_USR_ASSIGN_EXPL_ASM</t>
         </is>
       </c>
     </row>
@@ -30706,17 +30752,17 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>LORD_ODATA_ORDER_SRV</t>
+          <t>FINS_TRR_PECRUN_SALES_SRV</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>LORD_ODATA_ORDER_SRV</t>
+          <t>ZFINS_TRR_PECRUN_SALES_SRV</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>OData Service for Sales Order</t>
+          <t>Odata service for Manage Revenue Recognition - sales</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -30728,16 +30774,16 @@
         <v>1</v>
       </c>
       <c r="H461" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>HeaderSet</t>
+          <t>ErrorNumberCollection</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/LORD_ODATA_ORDER_SRV</t>
+          <t>/sap/opu/odata/sap/FINS_TRR_PECRUN_SALES_SRV</t>
         </is>
       </c>
     </row>
@@ -30752,17 +30798,17 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SD_BIL_DOC_LIST_MANAGE_SRV</t>
+          <t>LORD_ODATA_ORDER_SRV</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>ZSD_BIL_DOC_LIST_MANAGE_SRV</t>
+          <t>LORD_ODATA_ORDER_SRV</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Manage billing documents lists / invoice lists</t>
+          <t>OData Service for Sales Order</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -30774,16 +30820,16 @@
         <v>1</v>
       </c>
       <c r="H462" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>dummyCollection</t>
+          <t>HeaderSet</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_BIL_DOC_LIST_MANAGE_SRV</t>
+          <t>/sap/opu/odata/sap/LORD_ODATA_ORDER_SRV</t>
         </is>
       </c>
     </row>
@@ -30798,17 +30844,17 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>SD_CRT_PROCFLOW_SRV</t>
+          <t>SD_BIL_DOC_LIST_MANAGE_SRV</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>ZSD_CRT_PROCFLOW_SRV</t>
+          <t>ZSD_BIL_DOC_LIST_MANAGE_SRV</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>SD Process Flow for Customer Return</t>
+          <t>Manage billing documents lists / invoice lists</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -30820,16 +30866,16 @@
         <v>1</v>
       </c>
       <c r="H463" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>C_InhRepairObjPg</t>
+          <t>dummyCollection</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_CRT_PROCFLOW_SRV</t>
+          <t>/sap/opu/odata/sap/SD_BIL_DOC_LIST_MANAGE_SRV</t>
         </is>
       </c>
     </row>
@@ -30844,17 +30890,17 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>SD_CUSTOMER_INVOICES_MANAGE</t>
+          <t>SD_CRT_PROCFLOW_SRV</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>ZSD_CUSTOMER_INVOICES_MANAGE</t>
+          <t>ZSD_CRT_PROCFLOW_SRV</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Manage Customer Invoices</t>
+          <t>SD Process Flow for Customer Return</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -30863,19 +30909,19 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H464" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_InhRepairObjPg</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_CUSTOMER_INVOICES_MANAGE</t>
+          <t>/sap/opu/odata/sap/SD_CRT_PROCFLOW_SRV</t>
         </is>
       </c>
     </row>
@@ -30890,17 +30936,17 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>SD_F1814_SO_FS_SRV</t>
+          <t>SD_CUSTOMER_INVOICES_MANAGE</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>ZSD_F1814_SO_FS_SRV</t>
+          <t>ZSD_CUSTOMER_INVOICES_MANAGE</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Sales Orders FactSheets - S4H SD FIORI</t>
+          <t>Manage Customer Invoices</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -30912,7 +30958,7 @@
         <v>3</v>
       </c>
       <c r="H465" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
@@ -30921,7 +30967,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F1814_SO_FS_SRV</t>
+          <t>/sap/opu/odata/sap/SD_CUSTOMER_INVOICES_MANAGE</t>
         </is>
       </c>
     </row>
@@ -30936,17 +30982,17 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>SD_F1871_QUOT_FS_SRV</t>
+          <t>SD_F1814_SO_FS_SRV</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>ZSD_F1871_QUOT_FS_SRV</t>
+          <t>ZSD_F1814_SO_FS_SRV</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Quotation FactSheet - S4H SD FIORI</t>
+          <t>Sales Orders FactSheets - S4H SD FIORI</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -30967,7 +31013,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F1871_QUOT_FS_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F1814_SO_FS_SRV</t>
         </is>
       </c>
     </row>
@@ -30982,17 +31028,17 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>SD_F1873_SO_WL_SRV</t>
+          <t>SD_F1871_QUOT_FS_SRV</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>SD_F1873_SO_WL_SRV</t>
+          <t>ZSD_F1871_QUOT_FS_SRV</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Odata for Work list for Sales Order</t>
+          <t>Quotation FactSheet - S4H SD FIORI</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -31001,19 +31047,19 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H467" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>C_SalesOrderWl_F1873</t>
+          <t>ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F1873_SO_WL_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F1871_QUOT_FS_SRV</t>
         </is>
       </c>
     </row>
@@ -31028,17 +31074,17 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SD_F2187_CUST360_SRV</t>
+          <t>SD_F1873_SO_WL_SRV</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>ZSD_F2187_CUST360_SRV</t>
+          <t>SD_F1873_SO_WL_SRV</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Customer 360</t>
+          <t>Odata for Work list for Sales Order</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -31050,7 +31096,7 @@
         <v>1</v>
       </c>
       <c r="H468" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -31059,7 +31105,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2187_CUST360_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F1873_SO_WL_SRV</t>
         </is>
       </c>
     </row>
@@ -31074,17 +31120,17 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>SD_F2499_CUSTOMER_MATERIAL_SRV</t>
+          <t>SD_F2187_CUST360_SRV</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>ZSD_F2499_CUSTOMER_MATERIAL_SRV</t>
+          <t>ZSD_F2187_CUST360_SRV</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Customer Material</t>
+          <t>Customer 360</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -31093,19 +31139,19 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H469" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>C_AdditionalCustomerMaterialTP, C_CustMatlAddrDepdntInfoTP, C_CustomerMaterialLongTextTP, C_CustomerMaterial_F2499, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
+          <t>C_SalesOrderWl_F1873</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2499_CUSTOMER_MATERIAL_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2187_CUST360_SRV</t>
         </is>
       </c>
     </row>
@@ -31120,17 +31166,17 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>SD_F2583_SLSITMPRPSL_SRV</t>
+          <t>SD_F2499_CUSTOMER_MATERIAL_SRV</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>ZSD_F2583_SLSITMPRPSL_SRV</t>
+          <t>ZSD_F2499_CUSTOMER_MATERIAL_SRV</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>OData Service for Sales Item Proposals</t>
+          <t>Customer Material</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -31139,19 +31185,19 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H470" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>C_SalesItemProposalItemTP, C_SalesItemProposalTP</t>
+          <t>C_AdditionalCustomerMaterialTP, C_CustMatlAddrDepdntInfoTP, C_CustomerMaterialLongTextTP, C_CustomerMaterial_F2499, ConfigurationContextSet, CharacteristicValueSet, ClassificationContextSet</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2583_SLSITMPRPSL_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2499_CUSTOMER_MATERIAL_SRV</t>
         </is>
       </c>
     </row>
@@ -31166,17 +31212,17 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>SD_F2650_CRT_EDIT_SRV</t>
+          <t>SD_F2583_SLSITMPRPSL_SRV</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>ZSD_F2650_CRT_EDIT_SRV</t>
+          <t>ZSD_F2583_SLSITMPRPSL_SRV</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>OData for Customer Returns Edit</t>
+          <t>OData Service for Sales Item Proposals</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -31185,19 +31231,19 @@
         </is>
       </c>
       <c r="G471" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H471" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg, C_CustomerReturnSerialNumber</t>
+          <t>C_SalesItemProposalItemTP, C_SalesItemProposalTP</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2650_CRT_EDIT_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2583_SLSITMPRPSL_SRV</t>
         </is>
       </c>
     </row>
@@ -31212,17 +31258,17 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SD_F2651_CRT_CREATE_SRV</t>
+          <t>SD_F2650_CRT_EDIT_SRV</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>ZSD_F2651_CRT_CREATE_SRV</t>
+          <t>ZSD_F2650_CRT_EDIT_SRV</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>OData for Create Customer Returns</t>
+          <t>OData for Customer Returns Edit</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -31231,19 +31277,19 @@
         </is>
       </c>
       <c r="G472" t="n">
+        <v>3</v>
+      </c>
+      <c r="H472" t="n">
         <v>2</v>
       </c>
-      <c r="H472" t="n">
-        <v>0</v>
-      </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg</t>
+          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg, C_CustomerReturnSerialNumber</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2651_CRT_CREATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2650_CRT_EDIT_SRV</t>
         </is>
       </c>
     </row>
@@ -31258,17 +31304,17 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>SD_F2652_CRT_REFUND_SRV</t>
+          <t>SD_F2651_CRT_CREATE_SRV</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>ZSD_F2652_CRT_REFUND_SRV</t>
+          <t>ZSD_F2651_CRT_CREATE_SRV</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>OData for Customer Returns Refund</t>
+          <t>OData for Create Customer Returns</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -31289,7 +31335,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_F2652_CRT_REFUND_SRV</t>
+          <t>/sap/opu/odata/sap/SD_F2651_CRT_CREATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31304,17 +31350,17 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>SD_MANAGE_SADVTNPRFL</t>
+          <t>SD_F2652_CRT_REFUND_SRV</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>ZSD_MANAGE_SADVTNPRFL</t>
+          <t>ZSD_F2652_CRT_REFUND_SRV</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Manage Deviation Profile</t>
+          <t>OData for Customer Returns Refund</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -31323,19 +31369,19 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>C_SalesSchedgAgrmtDvtnPrflTP</t>
+          <t>C_CustomerReturnItemOPg, C_CustomerReturnOPg</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MANAGE_SADVTNPRFL</t>
+          <t>/sap/opu/odata/sap/SD_F2652_CRT_REFUND_SRV</t>
         </is>
       </c>
     </row>
@@ -31350,17 +31396,17 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>SD_MCC_CCO_MASS_UPDATE_SRV</t>
+          <t>SD_MANAGE_SADVTNPRFL</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>ZSD_MCC_CCO_MASS_UPDATE_SRV</t>
+          <t>ZSD_MANAGE_SADVTNPRFL</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>OData for Mass Change Sales Contract</t>
+          <t>Manage Deviation Profile</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -31369,19 +31415,19 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>SlsDocReadReq, SlsDocReq</t>
+          <t>C_SalesSchedgAgrmtDvtnPrflTP</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_CCO_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MANAGE_SADVTNPRFL</t>
         </is>
       </c>
     </row>
@@ -31396,17 +31442,17 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>SD_MCC_CMR_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_CCO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>ZSD_MCC_CMR_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_CCO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Mass Change Credit Memo Request</t>
+          <t>OData for Mass Change Sales Contract</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -31427,7 +31473,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_CMR_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_CCO_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31442,17 +31488,17 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>SD_MCC_CR_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_CMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>ZSD_MCC_CR_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_CMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Mass change for Customer Return</t>
+          <t>Mass Change Credit Memo Request</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -31473,7 +31519,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_CR_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_CMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31488,17 +31534,17 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>SD_MCC_DMR_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_CR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>ZSD_MCC_DMR_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_CR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Debit Memo Requests OData Service</t>
+          <t>Mass change for Customer Return</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -31519,7 +31565,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_DMR_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_CR_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31534,17 +31580,17 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>SD_MCC_DOC_CAT_AUTH_SRV</t>
+          <t>SD_MCC_DMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>ZSD_MCC_DOC_CAT_AUTH_SRV</t>
+          <t>ZSD_MCC_DMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Authorization for Document Categories in Mass Change Cockpit</t>
+          <t>Debit Memo Requests OData Service</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -31553,19 +31599,19 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>DocCategoryAuthSet</t>
+          <t>SlsDocReadReq, SlsDocReq</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_DOC_CAT_AUTH_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_DMR_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31580,17 +31626,17 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>SD_MCC_SCH_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_DOC_CAT_AUTH_SRV</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SCH_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_DOC_CAT_AUTH_SRV</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Sales Order Scheduling Agreement</t>
+          <t>Authorization for Document Categories in Mass Change Cockpit</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -31599,19 +31645,19 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>SlsDocReadReq, SlsDocReq</t>
+          <t>DocCategoryAuthSet</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SCH_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_DOC_CAT_AUTH_SRV</t>
         </is>
       </c>
     </row>
@@ -31626,17 +31672,17 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>SD_MCC_SD_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SCH_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SD_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SCH_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Mass Change of Sales Document</t>
+          <t>Sales Order Scheduling Agreement</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -31657,7 +31703,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SD_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SCH_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31672,17 +31718,17 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>SD_MCC_SOW_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SD_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SOW_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SD_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Sales Order Without Charge</t>
+          <t>Mass Change of Sales Document</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -31703,7 +31749,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SOW_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SD_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31718,17 +31764,17 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>SD_MCC_SO_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SOW_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SO_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SOW_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Change cockpit for mass update sales order</t>
+          <t>Sales Order Without Charge</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -31749,7 +31795,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SO_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SOW_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31764,17 +31810,17 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>SD_MCC_SQ_MASS_UPDATE_SRV</t>
+          <t>SD_MCC_SO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>ZSD_MCC_SQ_MASS_UPDATE_SRV</t>
+          <t>ZSD_MCC_SO_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Mass Change Sales Quotations</t>
+          <t>Change cockpit for mass update sales order</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -31795,7 +31841,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_MCC_SQ_MASS_UPDATE_SRV</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SO_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31810,17 +31856,17 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>SD_SALESPLAN</t>
+          <t>SD_MCC_SQ_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>ZSD_SALESPLAN</t>
+          <t>ZSD_MCC_SQ_MASS_UPDATE_SRV</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Odata Service for C_SalesPlanTP</t>
+          <t>Mass Change Sales Quotations</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -31829,19 +31875,19 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H485" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>C_SalesPlanDimnSelectionTP, C_SalesPlanItemTP, C_SalesPlanTP</t>
+          <t>SlsDocReadReq, SlsDocReq</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALESPLAN</t>
+          <t>/sap/opu/odata/sap/SD_MCC_SQ_MASS_UPDATE_SRV</t>
         </is>
       </c>
     </row>
@@ -31856,17 +31902,17 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>SD_SALES_DOC_IMPORT</t>
+          <t>SD_SALESPLAN</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>ZSD_SALES_DOC_IMPORT</t>
+          <t>ZSD_SALESPLAN</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Import Sales Documents</t>
+          <t>Odata Service for C_SalesPlanTP</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -31875,19 +31921,19 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H486" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>SetAsCompletedReturnMessageCollection</t>
+          <t>C_SalesPlanDimnSelectionTP, C_SalesPlanItemTP, C_SalesPlanTP</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_DOC_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALESPLAN</t>
         </is>
       </c>
     </row>
@@ -31902,17 +31948,17 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>SD_SALES_ORDER_FOC_IMPORT</t>
+          <t>SD_SALES_DOC_IMPORT</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>ZSD_SALES_ORDER_FOC_IMPORT</t>
+          <t>ZSD_SALES_DOC_IMPORT</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Import Sales Orders Without Charge</t>
+          <t>Import Sales Documents</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -31921,19 +31967,19 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H487" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
+          <t>SetAsCompletedReturnMessageCollection</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_ORDER_FOC_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_DOC_IMPORT</t>
         </is>
       </c>
     </row>
@@ -31948,17 +31994,17 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>SD_SALES_ORDER_IMPORT</t>
+          <t>SD_SALES_ORDER_FOC_IMPORT</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>ZSD_SALES_ORDER_IMPORT</t>
+          <t>ZSD_SALES_ORDER_FOC_IMPORT</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Import Sales Order Service Project</t>
+          <t>Import Sales Orders Without Charge</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -31974,12 +32020,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
+          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_ORDER_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_ORDER_FOC_IMPORT</t>
         </is>
       </c>
     </row>
@@ -31994,17 +32040,17 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>SD_SALES_QTN_IMPORT</t>
+          <t>SD_SALES_ORDER_IMPORT</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>ZSD_SALES_QTN_IMPORT</t>
+          <t>ZSD_SALES_ORDER_IMPORT</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Import Sales Quotations</t>
+          <t>Import Sales Order Service Project</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -32020,12 +32066,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
+          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_QTN_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_ORDER_IMPORT</t>
         </is>
       </c>
     </row>
@@ -32040,17 +32086,17 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>SD_SALES_SA_IMPORT</t>
+          <t>SD_SALES_QTN_IMPORT</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>ZSD_SALES_SA_IMPORT</t>
+          <t>ZSD_SALES_QTN_IMPORT</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Import Sales Scheduling Agreements</t>
+          <t>Import Sales Quotations</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -32066,12 +32112,12 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
+          <t>DownloadToCloudReturnMessageCollection, SalesBusinessPartnerCollection, SetAsCompletedReturnMessageCollection</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SALES_SA_IMPORT</t>
+          <t>/sap/opu/odata/sap/SD_SALES_QTN_IMPORT</t>
         </is>
       </c>
     </row>
@@ -32086,17 +32132,17 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>SD_SA_EDIPROCGOPTN_WL</t>
+          <t>SD_SALES_SA_IMPORT</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>ZSD_SA_EDIPROCGOPTN_WL</t>
+          <t>ZSD_SALES_SA_IMPORT</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Manage EDI Processing Options</t>
+          <t>Import Sales Scheduling Agreements</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -32105,19 +32151,19 @@
         </is>
       </c>
       <c r="G491" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H491" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>C_DelivSchedEDIProcgOptnTP</t>
+          <t>DownloadToCloudReturnMessageCollection, SetAsCompletedReturnMessageCollection, SalesBusinessPartnerCollection</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SA_EDIPROCGOPTN_WL</t>
+          <t>/sap/opu/odata/sap/SD_SALES_SA_IMPORT</t>
         </is>
       </c>
     </row>
@@ -32132,17 +32178,17 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>SD_SA_SOLDTOPARTYDETN_WL</t>
+          <t>SD_SA_EDIPROCGOPTN_WL</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>ZSD_SA_SOLDTOPARTYDETN_WL</t>
+          <t>ZSD_SA_EDIPROCGOPTN_WL</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Assign Sold-to Parties for Delivery Schedules</t>
+          <t>Manage EDI Processing Options</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -32158,12 +32204,12 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>C_DelivSchedSoldToPartyDetnTP</t>
+          <t>C_DelivSchedEDIProcgOptnTP</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SA_SOLDTOPARTYDETN_WL</t>
+          <t>/sap/opu/odata/sap/SD_SA_EDIPROCGOPTN_WL</t>
         </is>
       </c>
     </row>
@@ -32178,17 +32224,17 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>SD_SOF</t>
+          <t>SD_SA_SOLDTOPARTYDETN_WL</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>ZSD_SOF</t>
+          <t>ZSD_SA_SOLDTOPARTYDETN_WL</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Sales Order Fulfillment Reuse Component</t>
+          <t>Assign Sold-to Parties for Delivery Schedules</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -32204,12 +32250,12 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>ItemCollection</t>
+          <t>C_DelivSchedSoldToPartyDetnTP</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SOF</t>
+          <t>/sap/opu/odata/sap/SD_SA_SOLDTOPARTYDETN_WL</t>
         </is>
       </c>
     </row>
@@ -32224,17 +32270,17 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
+          <t>SD_SOF</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
+          <t>ZSD_SOF</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Resolve Credit Block in Sales Orders</t>
+          <t>Sales Order Fulfillment Reuse Component</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -32243,19 +32289,19 @@
         </is>
       </c>
       <c r="G494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H494" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>SalesOrderCollection, DeliveryCollection</t>
+          <t>ItemCollection</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/SD_SOFM_CREDIT_BLOCK_SRV</t>
+          <t>/sap/opu/odata/sap/SD_SOF</t>
         </is>
       </c>
     </row>
@@ -32270,17 +32316,17 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>UI_CUSTOMER_CONTACT_MANAGE</t>
+          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>ZUI_CUSTOMER_CONTACT_MANAGE</t>
+          <t>SD_SOFM_CREDIT_BLOCK_SRV</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Manage Customer Contacts</t>
+          <t>Resolve Credit Block in Sales Orders</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -32292,16 +32338,16 @@
         <v>2</v>
       </c>
       <c r="H495" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>CustomerContactAttribute, CustomerContactRelation</t>
+          <t>SalesOrderCollection, DeliveryCollection</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_CUSTOMER_CONTACT_MANAGE</t>
+          <t>/sap/opu/odata/sap/SD_SOFM_CREDIT_BLOCK_SRV</t>
         </is>
       </c>
     </row>
@@ -32316,17 +32362,17 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>UI_MANAGEINHREPAIRS</t>
+          <t>UI_CUSTOMER_CONTACT_MANAGE</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>ZUI_MANAGEINHREPAIRS</t>
+          <t>ZUI_CUSTOMER_CONTACT_MANAGE</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>RAP: UI_MANAGEINHREPAIRS generated at 20190313</t>
+          <t>Manage Customer Contacts</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -32338,16 +32384,16 @@
         <v>2</v>
       </c>
       <c r="H496" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>C_InhRepairObjPg, C_InhRepairObjPgItem</t>
+          <t>CustomerContactAttribute, CustomerContactRelation</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>/sap/opu/odata/sap/UI_MANAGEINHREPAIRS</t>
+          <t>/sap/opu/odata/sap/UI_CUSTOMER_CONTACT_MANAGE</t>
         </is>
       </c>
     </row>
@@ -32362,43 +32408,89 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
+          <t>UI_MANAGEINHREPAIRS</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>ZUI_MANAGEINHREPAIRS</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>RAP: UI_MANAGEINHREPAIRS generated at 20190313</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>2</v>
+      </c>
+      <c r="H497" t="n">
+        <v>11</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>C_InhRepairObjPg, C_InhRepairObjPgItem</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>/sap/opu/odata/sap/UI_MANAGEINHREPAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>SD - Sales</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
           <t>UI_RETURNPROCESSING</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr">
+      <c r="D498" t="inlineStr">
         <is>
           <t>ZUI_RETURNPROCESSING</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr">
+      <c r="E498" t="inlineStr">
         <is>
           <t>Return Processing Service</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>Fiori app service</t>
-        </is>
-      </c>
-      <c r="G497" t="n">
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Fiori app service</t>
+        </is>
+      </c>
+      <c r="G498" t="n">
         <v>3</v>
       </c>
-      <c r="H497" t="n">
+      <c r="H498" t="n">
         <v>34</v>
       </c>
-      <c r="I497" t="inlineStr">
+      <c r="I498" t="inlineStr">
         <is>
           <t>CtnItem, RcvdPackggItem, RcvdPackggInCtn</t>
         </is>
       </c>
-      <c r="J497" t="inlineStr">
+      <c r="J498" t="inlineStr">
         <is>
           <t>/sap/opu/odata/sap/UI_RETURNPROCESSING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J497"/>
+  <autoFilter ref="A1:J498"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
